--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0668C533-E76C-49B7-9573-4159048F1CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7ADA152-4A2F-47C9-81D9-0ACCD08612DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2287,6 +2287,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="172" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2316,8 +2320,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2623,8 +2629,9 @@
   <dimension ref="A1:N302"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -11552,11 +11559,11 @@
       <c r="L203" t="s">
         <v>14</v>
       </c>
-      <c r="M203">
-        <v>3.2683</v>
-      </c>
-      <c r="N203">
-        <v>102.5485</v>
+      <c r="M203" s="1">
+        <v>3.347807</v>
+      </c>
+      <c r="N203" s="1">
+        <v>99.165592000000004</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
@@ -12256,11 +12263,11 @@
       <c r="L219" t="s">
         <v>14</v>
       </c>
-      <c r="M219">
-        <v>5.9551959999999999</v>
-      </c>
-      <c r="N219">
-        <v>102.255039</v>
+      <c r="M219" s="2">
+        <v>1.147497</v>
+      </c>
+      <c r="N219" s="1">
+        <v>104.00298100000001</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
@@ -12301,10 +12308,10 @@
         <v>14</v>
       </c>
       <c r="M220">
-        <v>10.033329999999999</v>
+        <v>-2.7387220000000001</v>
       </c>
       <c r="N220">
-        <v>105.78333000000001</v>
+        <v>107.63120600000001</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
@@ -12344,11 +12351,11 @@
       <c r="L221" t="s">
         <v>14</v>
       </c>
-      <c r="M221">
-        <v>10.033329999999999</v>
-      </c>
-      <c r="N221">
-        <v>105.78333000000001</v>
+      <c r="M221" s="1">
+        <v>-6.1452640000000001</v>
+      </c>
+      <c r="N221" s="1">
+        <v>106.815133</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
@@ -12388,11 +12395,11 @@
       <c r="L222" t="s">
         <v>14</v>
       </c>
-      <c r="M222">
-        <v>13.763400000000001</v>
-      </c>
-      <c r="N222">
-        <v>107.17953</v>
+      <c r="M222" s="1">
+        <v>-6.3836279999999999</v>
+      </c>
+      <c r="N222" s="1">
+        <v>106.923833</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
@@ -12432,11 +12439,11 @@
       <c r="L223" t="s">
         <v>14</v>
       </c>
-      <c r="M223">
-        <v>28.721323000000002</v>
-      </c>
-      <c r="N223">
-        <v>77.140479999999997</v>
+      <c r="M223" s="1">
+        <v>-6.1395819999999999</v>
+      </c>
+      <c r="N223" s="1">
+        <v>106.73066799999999</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
@@ -12477,10 +12484,10 @@
         <v>14</v>
       </c>
       <c r="M224">
-        <v>29.370752</v>
-      </c>
-      <c r="N224">
-        <v>-98.593203000000003</v>
+        <v>-2.7206999999999999E-2</v>
+      </c>
+      <c r="N224" s="1">
+        <v>109.341559</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
@@ -12520,11 +12527,11 @@
       <c r="L225" t="s">
         <v>14</v>
       </c>
-      <c r="M225">
-        <v>38.093449999999997</v>
-      </c>
-      <c r="N225">
-        <v>47.263919999999999</v>
+      <c r="M225" s="1">
+        <v>1.0379259999999999</v>
+      </c>
+      <c r="N225" s="1">
+        <v>104.057447</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
@@ -12564,11 +12571,11 @@
       <c r="L226" t="s">
         <v>14</v>
       </c>
-      <c r="M226">
-        <v>45.707909999999998</v>
-      </c>
-      <c r="N226">
-        <v>-1.021325</v>
+      <c r="M226" s="1">
+        <v>-6.2585220000000001</v>
+      </c>
+      <c r="N226" s="1">
+        <v>107.021265</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
@@ -12608,11 +12615,11 @@
       <c r="L227" t="s">
         <v>14</v>
       </c>
-      <c r="M227">
-        <v>47.522616999999997</v>
-      </c>
-      <c r="N227">
-        <v>14.143701999999999</v>
+      <c r="M227" s="1">
+        <v>-6.1595579999999996</v>
+      </c>
+      <c r="N227" s="1">
+        <v>106.90712499999999</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
@@ -12652,11 +12659,11 @@
       <c r="L228" t="s">
         <v>14</v>
       </c>
-      <c r="M228">
-        <v>53.069369999999999</v>
-      </c>
-      <c r="N228">
-        <v>6.0005839999999999</v>
+      <c r="M228" s="1">
+        <v>-5.1529150000000001</v>
+      </c>
+      <c r="N228" s="1">
+        <v>119.403639</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
@@ -12696,11 +12703,11 @@
       <c r="L229" t="s">
         <v>14</v>
       </c>
-      <c r="M229">
-        <v>53.202295300000003</v>
-      </c>
-      <c r="N229">
-        <v>6.5842704999999997</v>
+      <c r="M229" s="1">
+        <v>-5.4610089999999998</v>
+      </c>
+      <c r="N229" s="1">
+        <v>122.61952599999999</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
@@ -15916,7 +15923,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N302" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7ADA152-4A2F-47C9-81D9-0ACCD08612DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D3D338-51DC-4E50-B76F-BF3F798B2E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3627" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="1056">
   <si>
     <t>Store ID</t>
   </si>
@@ -2281,17 +2281,954 @@
   </si>
   <si>
     <t>0.791261</t>
+  </si>
+  <si>
+    <t>Google Maps Link</t>
+  </si>
+  <si>
+    <t>POPULATION</t>
+  </si>
+  <si>
+    <t>Daily Traffic (Est)</t>
+  </si>
+  <si>
+    <t>Monthly Traffic (Est)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LIPPO%20PLAZA%20KUPANG%20Jl.%20Veteran%2C%20Fatululi%2C%20Kec.%20Oebobo%2C%20Kota%20Kupang%2C%20Nusa%20Tenggara%20Tim.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20ACEH%20Jalan%20T.%20Hasan%20Dek%2C%20Beurawe%2C%20Kecamatan%20Kuta%20Alam%2C%20Kota%20Banda%20Aceh%2C%20Aceh%2023124%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SIDEWALK%20JIMBARAN%20Jl.%20Raya%20Uluwatu%20No.138A%2C%20Ungasan%2C%20Kec.%20Kuta%20Sel.%2C%20Kabupaten%20Badung%2C%20Bali%2080361%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENTRAL%20BELANJA%20MERAUKE%20FCX5%2BPRF%2C%20Klp.%20Lima%2C%20Kec.%20Merauke%2C%20Kabupaten%20Merauke%2C%20Papua%20Selatan%2099615%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DISCOVERY%20MALL%20BALI%20Jl.%20Kartika%20Plaza%2C%20Kuta%2C%20Kec.%20Kuta%2C%20Kabupaten%20Badung%2C%20Bali%2080361%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BEACH%20WALK%20MALL%20Jl.%20Pantai%20Kuta%2C%20Kuta%2C%20Kec.%20Kuta%2C%20Kabupaten%20Badung%2C%20Bali%2080361%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GAJAH%20MADA%20PLAZA%20MALANG%20Jl.%20Agus%20Salim%20No.18%2C%20Sukoharjo%2C%20Klojen%2C%20Malang%20City%2C%20East%20Java%2065119%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALANG%20TOWN%20SQUARE%20Jl.%20Veteran%20No.2%2C%20Penanggungan%2C%20Kec.%20Klojen%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065111%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20ARAYA%20MALANG%20Jl.%20Blimbing%20Indah%20Megah%20No.2%2C%20Purwodadi%2C%20Kec.%20Blimbing%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065126%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20MADIUN%20Jl.%20Pahlawan%20No.38-40%2C%20Pangongangan%2C%20Kec.%20Manguharjo%2C%20Kota%20Madiun%2C%20Jawa%20Timur%2063121%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAI%20MALL%20Jl.%20Beskalan%20No.73%2C%20Ngupasan%2C%20Kec.%20Gondomanan%2C%20Kota%20Yogyakarta%2C%20Daerah%20Istimewa%20Yogyakarta%2055122%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALIOBORO%20MALL%20Jl.%20Malioboro%20No.52-58%2C%20Suryatmajan%2C%20Kec.%20Danurejan%2C%20Kota%20Yogyakarta%2C%20DI%20Yogyakarta%2055213%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LIPPO%20PLAZA%20JOGJA%20Jl.%20Laksda%20Adisucipto%20No.32-34%2C%20Demangan%2C%20Kec.%20Gondokusuman%2C%20Kota%20Yogyakarta%2C%20DI%20Yogyakarta%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RING%20ROAD%20CITY%20WALK%20Jalan%20Arteri%20Ring%20Road%20%28Jalan%20Gagak%20Hitam%29%20No.28%2C%20Kelurahan%20Sunggal%2C%20Kecamatan%20Medan%20Sunggal%2C%20Kota%20Medan%2C%20Sumatera%20Utara%20%28Kode%20Pos%2020122%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Jatinangor%20Town%20Square%20Jl.%20Raya%20Jatinangor%20No.150%2C%20Cikeruh%2C%20Kec.%20Jatinangor%2C%20Kab.%20Sumedang%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20ASIA%20SUMEDANG%20Jl.%20Mayor%20Abdurrahman%20No.225%2C%20Kota%20Kaler%2C%20Kec.%20Sumedang%20Utara%2C%20Kab.%20Sumedang%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20JAMTOS%20Jalan%20Kapten%20A.%20Bakaruddin%20No.88%2C%20Kelurahan%20Simpang%20Tiga%20Sipin%2C%20Kecamatan%20Kota%20Baru%2C%20Kota%20Jambi%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SOLO%20GRAND%20MALL%20Jl.%20Brigjen%20Slamet%20Riyadi%20No.273%2C%20Penumping%2C%20Kec.%20Laweyan%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%2057141%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENTRA%20NIAGA%20SOLO%20Jl.%20Monginsidi%20No.107%2C%20Gilingan%2C%20Kec.%20Banjarsari%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20RANTAU%20PRAPAT%20Jl.%20SM.%20Raja%2C%20Bakaran%20Batu%2C%20Kec.%20Rantau%20Sel.%2C%20Kab.%20Labuhanbatu%2C%20Sumatera%20Utara%2021418%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MIKO%20MALL%20Jl.%20Kopo%20No.599%2C%20Cirangrang%2C%20Kec.%20Babakan%20Ciparay%2C%20Kota%20Bandung%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=METRO%20INDAH%20MALL%20Jl.%20Soekarno%20Hatta%20No.590%2C%20Sekejati%2C%20Kec.%20Buah%20Batu%2C%20Kota%20Bandung%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=JAMBI%20PRIMA%20MALL%20Jl.%20Jend.%20Sudirman%20No.90%2C%20Talang%20Jauh%2C%20Kec.%20Jelutung%2C%20Kota%20Jambi%2C%20Jambi%2036133%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20ANUGRAH%20SIDIMPUAN%20Jl.%20Jenderal%20Sudirman%20No.%201%2C%20Minggu%20II%2C%20Kecamatan%20Padangsidimpuan%20Utara%2C%20Kota%20Padang%20Sidempuan%2C%20Sumatera%20Utara%2022711%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MASPION%20SQUARE%20Jl.%20Ahmad%20Yani%20No.73%2C%20Margorejo%2C%20Kec.%20Wonocolo%2C%20Surabaya%2C%20Jawa%20Timur%2060238%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PAKUWON%20TRADE%20CENTER%20Jl.%20Pakuwon%20Indah%20No.2%2C%20Babatan%2C%20Kec.%20Wiyung%2C%20Surabaya%2C%20Jawa%20Timur%2060213%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DARMO%20TRADE%20CENTER%20Jl.%20Jagir%20Wonokromo%2C%20Jagir%2C%20Kec.%20Wonokromo%2C%20Surabaya%2C%20Jawa%20Timur%2060242%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MARVEL%20CITY%20MALL%20Jl.%20Ngagel%20No.123%2C%20Ngagel%2C%20Kec.%20Wonokromo%2C%20Surabaya%2C%20Jawa%20Timur%2060246%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Lagoon%20Avenue%20Jl.%20KH%20Abdul%20Wahab%20Siamin%20Surabaya%20No.Kav.%209-10%2C%20Putat%20Gede%2C%20Kec.%20Dukuhpakis%2C%20Surabaya%2C%20Jawa%20Timur%2060225%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20FOOD%20JUNCTION%20SURABAYA%20Jalan%20Grand%20Banjar%20Mutiara%20Asri%20No.1%2C%20Banjar%20Sugihan%2C%20Kec.%20Tandes%2C%20Surabaya%2C%20Jawa%20Timur%2060184%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20MEGA%20GROSIR%20Jl.%20Gembong%20No.20%20-%2030%2C%20Kapasan%2C%20Kec.%20Simokerto%2C%20Surabaya%2C%20Jawa%20Timur%2060141%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PASAR%20ATOM%20Jl.%20Bunguran%20No.45%2C%20Bongkaran%2C%20Kec.%20Pabean%20Cantian%2C%20Surabaya%2C%20Jawa%20Timur%2060161%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=JEMBATAN%20MERAH%20PLASA%20Jl.%20Taman%20Jayengrono%20No.2%2C%20Krembangan%20Sel.%2C%20Kec.%20Krembangan%2C%20Surabaya%2C%20Jawa%20Timur%2060175%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=THE%20PARK%20SEMARANG%20Jl.%20Madukoro%20Raya%20No.1%2C%20Tawangsari%2C%20Kec.%20Semarang%20Barat%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050144%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALANG%20PLAZA%20Jl.%20Agus%20Salim%20No.26%2C%20Sukoharjo%2C%20Kec.%20Klojen%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065118%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=UPTOWN%20MALL%20Jl.%20Rm.%20Hadisoebeno%20Sosro%20Wardoyo%2C%20Pesantren%2C%20Kec.%20Mijen%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050212%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20SIMPANG%20LIMA%20Jl.%20Ahmad%20Yani%20No.1%2C%20Karangkidul%2C%20Kec.%20Semarang%20Tengah%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=THEE%20MATIC%20Jl.%20Raya%20Majalaya%20-%20Rancaekek%2C%20Majasetra%2C%20Kec.%20Majalaya%2C%20Kabupaten%20Bandung%2C%20Jawa%20Barat%2040392%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RITA%20SUPERMALL%20TEGAL%20Jl.%20Kolonel%20Sugiono%20No.155%2C%20Pekauman%2C%20Kec.%20Tegal%20Barat%2C%20Kota%20Tegal%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ROXY%20SQUARE%20Jl.%20Brigjen%20Sudiarto%20No.760%2C%20Pedurungan%20Lor%2C%20Kec.%20Pedurungan%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MATAHARI%20PLAZA%20Jl.%20Ahmad%20Yani%20No.1%2C%20Karangkidul%2C%20Kec.%20Semarang%20Tengah%2C%20Kota%20Semarang%2C%20Jawa%20Tengah%2050136%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20BOEMI%20KEDATON%20Jalan%20Teuku%20Umar%20-%20Jalan%20Sultan%20Agung%20No.%201%2C%20Labuhan%20Ratu%2C%20Kecamatan%20Kedaton%2C%20Kota%20Bandar%20Lampung%2C%20Lampung%2035132%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SAGA%20SUPERMARKET%20%26%20DEPT%20STORE%20Jalan%20A.%20Yani%2C%20Ruko%20Kuda%20Laut%2C%20Klademak%2C%20Kecamatan%20Sorong%20Manoi%2C%20Kota%20Sorong%2C%20Papua%20Barat%20Daya%2098414%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20PARAHYANGAN%20Balonggede%2C%20Regol%2C%20Bandung%20City%2C%20West%20Java%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=YOGYA%20MALL%20PEKALONGAN%20Jl.%20KH%20Wahid%20Hasyim%20No.92%2C%20Kergon%2C%20Kec.%20Pekalongan%20Barat%2C%20Kota%20Pekalongan%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ASIA%20TOSERBA%20Jl.%20Karanggetas%20No.25-27%2C%20Panjunan%2C%20Kec.%20Lemahwungkuk%2C%20Kota%20Cirebon%2C%20Jawa%20Barat%2045112%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PUSAT%20GROSIR%20CIREBON%20Jl.%20Siliwangi%20No.239%2C%20Kebonbaru%2C%20Kec.%20Kejaksan%2C%20Kota%20Cirebon%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MORO%20MALL%20Jl.%20Perintis%20Kemerdekaan%20No.7%2C%20Kongsen%2C%20Purwokerto%20Kulon%2C%20Kec.%20Purwokerto%20Sel.%2C%20Kabupaten%20Banyumas%2C%20Jawa%20Tengah%2053141%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=HARTONO%20MALL%20SOLO%20Jl.%20Ir.%20Soekarno%2C%20Madegondo%2C%20Kec.%20Grogol%2C%20Kab.%20Sukoharjo%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BOGOR%20TRADE%20MALL%20Jl.%20Ir.%20H.%20Juanda%20No.68%2C%20RT.01/RW.13%2C%20Paledang%2C%20Kecamatan%20Bogor%20Tengah%2C%20Kota%20Bogor%2C%20Jawa%20Barat%2016122%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LIPPO%20PLAZA%20BOGOR%20Jl.%20Malabar%202%20No.17A%2C%20RT.03/RW.08%2C%20Babakan%2C%20Kecamatan%20Bogor%20Tengah%2C%20Kota%20Bogor%2C%20Jawa%20Barat%2016129%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20STS%20terminal%20square%28sts%2C%20Sadang%20lantai%202%2C%20Ciwangi%2C%20Kec.%20Bungursari%2C%20Kabupaten%20Purwakarta%2C%20Jawa%20Barat%2014118%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LOTTEMART%20BOGOR%20Kedung%20Waringin%2C%20Jl.%20Sholeh%20Iskandar%2C%20RT.05/RW.04%2C%20Cibadak%2C%20Tanah%20Sareal%2C%20Kota%20Bogor%2C%20Jawa%20Barat%2016164%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CHADSTONE%20Jl.%20Raya%20Cikarang%20-%20Cibarusah%20No.78%20Blok%20A%2C%20Pasirsari%2C%20Cikarang%20Selatan%2C%20Bekasi%20Regency%2C%20West%20Java%2017530%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SOLO%20SQUARE%20Jl.%20Brigjen%20Slamet%20Riyadi%20No.451-455%2C%20Pajang%2C%20Kec.%20Laweyan%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%2057146%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SINGOSAREN%20PLAZA%20Jl.%20Gatot%20Subroto%20No.79%2C%20Kemlayan%2C%20Kec.%20Serengan%2C%20Kota%20Surakarta%2C%20Jawa%20Tengah%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20CIKAMPEK%20Jl.%20Ahmad%20Yani%20No.76%2C%20Dawuan%20Tim.%2C%20Kec.%20Cikampek%2C%20Karawang%2C%20Jawa%20Barat%2041373%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20KARAWANG%20ELECTRONIC%20CENTRE%20Jl%20Tuparev.16%20%28Depan%20Perlintasan%20Kereta%20Api%20Tuparev%2C%20Nagasari%2C%20Kec.%20Karawang%20Bar.%2C%20Karawang%2C%20Jawa%20Barat%2041312%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20CIBUBUR%20Jalan%20Alternatif%20Cibubur%20-%20Cileungsi%20%28Jalan%20Transyogi%29%20KM%202-3%2C%20Jatikarya%2C%20Kecamatan%20Jatisampurna%2C%20Kota%20Bekasi%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PAMULANG%20SQUARE%20l.%20Siliwangi%20No.7%2C%20Pamulang%20Barat%2C%20Kecamatan%20Pamulang%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015417%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ONE%20BELPARK%20MALL%20Jl.%20RS.%20Fatmawati%20Raya%20No.%201%2C%20RT.1/RW.1%2C%20Pondok%20Labu%2C%20Kecamatan%20Cilandak%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012450.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20RAMAYANA%20KARAWANG%20Jl.%20Tuparev%20No.1%2C%20Nagasari%2C%20Kec.%20Karawang%20Barat%2C%20Kab.%20Karawang%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=THE%20GRAND%20OUTLET%20Jl.%20Trans%20Hexa%20Karawang%2C%20Wanasari%2C%20Kec.%20Telukjambe%20Bar.%2C%20Karawang%2C%20Jawa%20Barat%2041361%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20GALUH%20MAS%20Jl.%20Galuh%20Mas%20Raya%2C%20Sukaharja%2C%20Telukjambe%20Timur%2C%20Karawang%2C%20Jawa%20Barat%2041361%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=COURT%20BINTARO%20BXC-Mall1%20South%20Lobby%2C%20Basement%201%2C%20Banten%2C%20Pondok%20Aren%2C%20South%20Tangerang%20City%2C%20Banten%2015220%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20PANDEGLANG%20Jl.%20Ahmad%20Yani%2C%20Pandeglang%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TERAS%20KOTA%20MALL%20Jl.%20Pahlawan%20Seribu%20CBD%20Lot%20VII%20B%2C%20Lengkong%20Gudang%2C%20Serpong%2C%20Tangerang%20Selatan%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BLOK%20M%20SQUARE%20Blok%20M%20Square%2C%20Jl.%20Melawai%205%2C%20RT.3/RW.1%2C%20Melawai%2C%20Kecamatan%20Kebayoran%20Baru%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012160%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Living%20World%20Grand%20Wisata%20Esplanade%20Ave%2C%20Lambangjaya%2C%20Tambun%20Selatan%2C%20Bekasi%20Regency%2C%20West%20Java%2017510%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CILANDAK%20TOWN%20SQUARE%20Jl.%20TB%20Simatupang%20Kav.%2017%2C%20RT.6/RW.9%2C%20Cilandak%20Barat%2C%20Kecamatan%20Cilandak%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012430.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=EASTVARA%20%28NEW%29%20Jalan%20BSD%20Boulevard%20Utara%2C%20Cijantra%2C%20Kecamatan%20Pagedangan%2C%20Kabupaten%20Tangerang%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PONDOK%20INDAH%20MALL%20Jl.%20Metro%20Pondok%20Indah%20No.%20Kav.%204%2C%20RT.1/RW.16%2C%20Pondok%20Pinang%2C%20Kebayoran%20Lama%2C%20Jakarta%20Selatan%2012310%2C%20DKI%20Jakarta%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TAMINI%20SQUARE%20Tamini%20Square%2C%20Jl.%20Taman%20Mini%20I%20No.%201%2C%20RT.3/RW.2%2C%20Pinang%20Ranti%2C%20Kecamatan%20Makasar%2C%20Jakarta%20Timur%2013560%2C%20DKI%20Jakarta%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PEJATEN%20VILLAGE%20Jl.%20Warung%20Jati%20Barat%20No.%2039%2C%20RT.1/RW.5%2C%20Jati%20Padang%2C%20Kecamatan%20Pasar%20Minggu%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012540.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANSPARK%20BINTARO%20Jl.%20Boulevard%20Bintaro%20Jaya%2C%20Kelurahan%20Pondok%20Jaya%2C%20Kecamatan%20Pondok%20Aren%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015220%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LOTTEMART%20BINTARO%20Jl.%20M.H.%20Thamrin%2C%20CBD%20Area%20Kavling%20Blok%20B7/01-06%2C%20Bintaro%20Jaya%20Sektor%207%2C%20Kelurahan%20Pondok%20Jaya%2C%20Kecamatan%20Pondok%20Aren%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015224%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20KALIBATA%20Jl.%20Raya%20Kalibata%20No.%20141%2C%20RT.3/RW.2%2C%20Rawajati%2C%20Kecamatan%20Pancoran%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012750%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANSMART%20CILANDAK%20Jl.%20Raya%20Cilandak%20KKO%20No.27%2C%20RT.1/RW.5%2C%20Cilandak%20Tim.%2C%20Ps.%20Minggu%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2012560%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20FATMAWATI%20Jl.%20ITC%20Fatmawati%20No.%2039%2C%20RT.1/RW.5%2C%20Cipete%20Utara%2C%20Kecamatan%20Kebayoran%20Baru%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012150%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PUSAT%20GROSIR%20CILILITAN%20Jl.%20Mayjen%20Sutoyo%20No.%2076%2C%20Cililitan%2C%20Kecamatan%20Kramat%20Jati%2C%20Kota%20Jakarta%20Timur%2C%20DKI%20Jakarta%2013640%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BLUE%20MALL%20Jalan%20Chairil%20Anwar%20No.%2027-36%2C%20RT.004/RW.009%0AKelurahan%20Margahayu%2C%20Kecamatan%20Bekasi%20Timur%0AKota%20Bekasi%2C%20Jawa%20Barat%2017113%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=POINT%20SQUARE%20LEBAK%20BULUS%20Jl.%20R.A.%20Kartini%20No.%201%2C%20RT.9/RW.7%2C%20Lebak%20Bulus%2C%20Kecamatan%20Cilandak%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012440.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ERAFONE%20DIGITAL%20CENTER%20Jalan%20HR.%20Rasuna%20Said%20Kavling%20BB-15%2C%20Salembaran%2C%20Kec.%20Kosambi%2C%20Kabupaten%20Tangerang%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GRAND%20DADAP%20CITY%20Jl.%20Villa%20Taman%20Bandara%2C%20Dadap%2C%20Kec.%20Kosambi%2C%20Kabupaten%20Tangerang%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BEKASI%20CYBERPARK%20Jl.%20KH.%20Noer%20Ali%20No.177%2C%20RT.001/RW.005%2C%20Kayuringin%20Jaya%2C%20Kec.%20Bekasi%20Sel.%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017144%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=UBERTOS%20MALL%20Ubertos%20Mall%20Lt.2%2C%20Pakemitana%2C%20Jl.%20AH.%20Nasution%20Lantai%202%2C%20Pakemitan%2C%20Kec.%20Cinambo%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2045474%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20CIPINANG%20INDAH%20Jl.%20Laksamana%20Malahayati%20No.%2018%20%28Kalimalang%29%2C%20RT.18/RW.3%2C%20Pondok%20Bambu%2C%20Kec.%20Duren%20Sawit%2C%20Kota%20Jakarta%20Timur%2C%20DKI%20Jakarta%2013430%2C%20Indonesia%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20CIPULIR%20Jl.%20Ciledug%20Raya%20No.%201%2C%20Cipulir%2C%20Kec.%20Kebayoran%20Lama%2C%20Kota%20Jakarta%20Selatan%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BLOK%20M%20PLAZA%20Jl.%20Bulungan%20No.%2076%2C%20RT.6/RW.6%2C%20Kramat%20Pela%2C%20Kecamatan%20Kebayoran%20Baru%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012130.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=METROPOLITAN%20MALL%20Jl.%20KH.%20Noer%20Ali%20No.2%2C%20RT.008/RW.002%2C%20Pekayon%20Jaya%2C%20Kec.%20Bekasi%20Sel.%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017141%2C%20Indonesia%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ASTHA%20DISTRICT%20Jl.%20Senopati%20No.%2083%2C%20Senayan%2C%20Kecamatan%20Kebayoran%20Baru%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012190%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CBD%20BINTARO%20Jl.%20Boulevard%20Bintaro%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RATU%20PLAZA%20Jl.%20Jenderal%20Sudirman%20Blok%20Kav%20No.9%2C%20RT.1/RW.3%2C%20Gelora%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010270%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUPERMALL%20CIANJUR%20Supermall%2C%20Jl.%20KH%20Abdullah%20Bin%20Nuh%20No.1%2C%20Pamoyanan%2C%20Kec.%20Cianjur%2C%20Kabupaten%20Cianjur%2C%20Jawa%20Barat%2043211%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20SENAYAN%20Jl.%20Asia%20Afrika%20No.8%2C%20RT.1/RW.3%2C%20Gelora%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010270%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PACIFIC%20PLACE%20Jl.%20Jend.%20Sudirman%20Kav.%2052%E2%80%9353%2C%20RT.5/RW.3%2C%20Senayan%2C%20Kecamatan%20Kebayoran%20Baru%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012190%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=KUNINGAN%20CITY%20Jl.%20Prof.%20Dr.%20Satrio%20Kav.%2018%2C%20Karet%20Kuningan%2C%20Kecamatan%20Setiabudi%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012940.%20Mall%20ini%20berada%20di%20kawasan%20bisnis%20Kuningan%2C%20Jakarta%20Selatan.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENAYAN%20CITY%20Jl.%20Asia%20Afrika%20No.%2019%2C%20RT.1/RW.3%2C%20Gelora%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20DKI%20Jakarta%2010270%2C%20Indonesia%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20FESTIVAL%20Jl.%20H.%20R.%20Rasuna%20Said%20No.22%20Kav.%20C%2C%20RT.2/RW.5%2C%20Karet%20Kuningan%2C%20Kecamatan%20Setiabudi%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012940.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20SEMANGGI%20Jalan%20Jenderal%20Sudirman%20No.%20Kav%2050%2C%20RT.1/RW.4%2C%20Karet%20Semanggi%2C%20Kecamatan%20Setiabudi%2C%20Jakarta%20Selatan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=EPIWALK%20%28NEW%29%20Jl.%20Epicentrum%20Boulevard%20Barat%2C%20RT.2/RW.5%2C%20Karet%20Kuningan%2C%20Kecamatan%20Setiabudi%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012940.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PTC%20Jl.%20Bekasi%20Raya%20Km.21%2C%20Jakarta%20Timur%2C%20RW.3%2C%20Rw.%20Terate%2C%20Jakarta%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013920%2C%20Indonesia%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PONDOK%20KELAPA%20TOWN%20SQUARE%20Jl.%20Pd.%20Kelapa%20Raya%20No.16%2C%20RT.16/RW.2%2C%20Pd.%20Klp.%2C%20Kec.%20Duren%20Sawit%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013450%2C%20Indonesia%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CIPLAZ%20KLENDER%20%28RAMAYANA%29%20Jalan%20I%20Gusti%20Ngurah%20Rai%20No.4%2C%20RT.7/RW.6%2C%20Klender%2C%20Kecamatan%20Duren%20Sawit%2C%20Kota%20Jakarta%20Timur%2C%20DKI%20Jakarta%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITY%20PLAZA%20JATINEGARA%20Jl.%20Matraman%20Raya%20No.%20173%E2%80%93175%2C%20RT.7/RW.6%2C%20Bali%20Mester%2C%20Kecamatan%20Jatinegara%2C%20Kota%20Jakarta%20Timur%2C%20DKI%20Jakarta%2013310%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CBD%20CILEDUG%20Jalan%20HOS%20Cokroaminoto%20No.%2093%2C%20Kelurahan%20Karang%20Tengah%2C%20Kecamatan%20Karang%20Tengah%2C%20Kota%20Tangerang%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SETIABUDI%20ONE%20Jl.%20H.%20R.%20Rasuna%20Said%20Kav.%2062%2C%20RT.18/RW.2%2C%20Kuningan%2C%20Karet%20Kuningan%2C%20Kecamatan%20Setiabudi%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012920%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20PERMATA%20HIJAU%20ITC%20Permata%20Hijau%2C%20Jl.%20Arteri%20Permata%20Hijau%20No.%2011%2C%20Grogol%20Utara%2C%20Kecamatan%20Kebayoran%20Lama%2C%20Jakarta%20Selatan%2012210%2C%20DKI%20Jakarta%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20MANDAU%20KOTA%20DURI%20Jalan%20Jendral%20Sudirman%20Kav.%20109%2C%20Kelurahan%20Babussalam%2C%20Kecamatan%20Mandau%2C%20Kota%20Duri%2C%20Kabupaten%20Bengkalis%2C%20Provinsi%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITY%20WALK%20SUDIRMAN%20Jl.%20K.H.%20Mas%20Mansyur%20No.%20Kav.%20121%2C%20RT.10/RW.11%2C%20Karet%20Tengsin%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20DKI%20Jakarta%2010220%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20INDONESIA%20Jl.%20M.H.%20Thamrin%20No.28-30%2C%20RT.9/RW.5%2C%20Gondangdia%2C%20Kec.%20Menteng%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010350%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SLIPI%20JAYA%20PLAZA%20Jl.%20Letjen%20S.%20Parman%20No.Kav%2017-18%2C%20RT.14/RW.1%2C%20Kemanggisan%2C%20Kec.%20Palmerah%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011480%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANSMART%20GRAHA%20RAYA%20l.%20Boulevard%20Graha%20Raya%2C%20Bintaro%2C%20Paku%20Jaya%2C%20Kec.%20Serpong%20Utara%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20BSD%20Jl.%20Pahlawan%20Seribu%20No.%2012%2C%20Lengkong%20Wetan%2C%20Kecamatan%20Serpong%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20CEMPAKA%20MAS%20Jl.%20Letjen%20Suprapto%20No.1%2C%20RW.8%2C%20Sumur%20Batu%2C%20Kec.%20Kemayoran%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010640%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GREEN%20SEDAYU%20Blk.%20B17%2C%20Jl.%20Taman%20Palem%20Lestari%20No.2%2C%20RT.7/RW.13%2C%20Cengkareng%20Bar.%2C%20Kecamatan%20Cengkareng%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011730%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=NEO%20SOHO%20Jl.%20Letjen%20S.%20Parman%20No.28%2C%20RT.3/RW.5%2C%20Tj.%20Duren%20Sel.%2C%20Kec.%20Grogol%20petamburan%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011470%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20ROXY%20MAS%20Jl.%20Kh%20Hasyim%20Ashari%20No.125%2C%20RT.6/RW.8%2C%20Cideng%2C%20Kecamatan%20Gambir%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010150%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20ALAM%20SUTERA%20Jl.%20Jalur%20Sutera%20Bar.%20No.Kav.%2016%2C%20RT.002/RW.003%2C%20Panunggangan%20Tim.%2C%20Kec.%20Pinang%2C%20Kota%20Tangerang%2C%20Banten%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITRA%20RAYA%20SQUARE%201%20Jalan%20Raya%20Serang%0AKelurahan%20Pasir%20Gadung%2C%20Cikupa%0ATangerang%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MATAHARI%20MALL%20KALIDERES%20Jl.%20Daan%20Mogot%20No.24%2C%20RT.3/RW.8%2C%20Kalideres%2C%20Kec.%20Kalideres%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011840%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DAAN%20MOGOT%20MALL%20Jl.%20Daan%20Mogot%20No.24%2C%20RT.3/RW.8%2C%20Kalideres%2C%20Kec.%20Kalideres%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011840%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GRAND%20PARAGON%20MALL%2012%2C%20Jl.%20Keamanan%20No.8%2C%20RT.13/RW.8%2C%20Keagungan%2C%20Kec.%20Taman%20Sari%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011130%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GLODOK%20PLAZA%20Jl.%20Pinangsia%20Raya%20No.1%2C%20RT.1/RW.6%2C%20Mangga%20Besar%2C%20Kec.%20Taman%20Sari%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011180%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MANGGA%20DUA%20MALL%20Jl.%20Mangga%20Dua%20Raya%20No.1%2C%20RT.1/RW.12%2C%20Mangga%20Dua%20Sel.%2C%20Kecamatan%20Sawah%20Besar%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010730%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=HARCO%20MANGGA%20DUA%20Jl.%20Semangat%2C%20RT.17/RW.11%2C%20Mangga%20Dua%20Sel.%2C%20Kecamatan%20Sawah%20Besar%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010730%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ANCOL%20BEACH%20CITY%20Beach%20City%20International%20Stadium%2C%20Jl.%20Kw.%20Wisata%20Ancol%2C%20Ancol%2C%20Pademangan%2C%20North%20Jakarta%20City%2C%20Jakarta%2014430%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUNTER%20MALL%20Jl.%20Danau%20Sunter%20Utara%20Kav.%20II%20Blok%20G7%2C%20RT.1/RW.13%2C%20Sunter%20Agung%2C%20Tanjung%20Priok%2C%20North%20Jakarta%20City%2C%20Jakarta%2014350%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20LOKASARI%20Jl.%20Mangga%20Besar%20IX%20No.6%2C%20RT.6/RW.2%2C%20Tangki%2C%20Kec.%20Taman%20Sari%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011170%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LOTTEMART%20SERANG%20Jl.%20Mayor%20Syafei%20Kpg.%20Kepandean%2C%20Kel.%20Kagungan%2C%20Kec.%20Serang%2C%20Serang%20%2842114%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BAYWALK%20MALL%20l.%20Pluit%20Karang%20Ayu%20Barat%20Utara%20No.B1%2C%20RT.20/RW.2%2C%20Pluit%2C%20Kecamatan%20Penjaringan%2C%20Jakarta%20Utara%2C%20DKI%20Jakarta%2014450%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PIK%20AVENUE%20Jl.%20Pantai%20Indah%20Kapuk%20Boulevard%2C%20RT.6/RW.2%2C%20Kamal%20Muara%2C%20Kecamatan%20Penjaringan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014470%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUPERMALL%20CILEGON%20Jl%20Sultan%20Ageng%20Tirtayasa%20Simpang%20Tiga%2C%20Cilegon%2C%20Banten%2042431%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20MALL/CILEGON%20Jalan%20Raya%20Serang%20No.%202%2C%20Sukmajaya%2C%20Kecamatan%20Jombang%2C%20Kota%20Cilegon%2C%20Banten%2042416%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANSMART%20CILEGON%20Jalan%20KH.%20Yasin%20Beji%20No.2%2C%20Kebondalem%2C%20Kecamatan%20Purwakarta%2C%20Kota%20Cilegon%2C%20Banten%2042433%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SIMPUR%20CENTRE%20Jalan%20Raden%20Intan%20No.32%2C%20Tanjung%20Karang%2C%20Enggal%2C%20Kota%20Bandar%20Lampung%2C%20Lampung%2035111%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20LOTUS%20Jl.%20Raden%20Intan%20No.73%2C%20Enggal%2C%20Enggal%2C%20Bandar%20Lampung%2035118%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GRAHA%20CIJANTUNG%20Graha%20Cijantung%2C%20Jl.%20Pendidikan%20I%20No.%201%2C%20Cijantung%2C%20Kecamatan%20Pasar%20Rebo%2C%20Jakarta%20Timur%2013770%2C%20DKI%20Jakarta%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20KAREBOSI%20LINK%20Jl.%20Ahmad%20Yani%2C%20Baru%2C%20Ujung%20Pandang%2C%20Makassar%20City%2C%20South%20Sulawesi%2090174%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DIANA%20MALL%20Jl.%20Budi%20Utomo%20No.8%2C%20Kwamki%2C%20Kec.%20Mimika%20Baru%2C%20Kabupaten%20Mimika%2C%20Papua%2099971%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20MANDONGA%20JL.%20Abdullah%20Silondae%2C%20Korumba%2C%20Kec.%20Mandonga%2C%20Kota%20Kendari%2C%20Sulawesi%20Tenggara%2093111%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BAJUIN%20PLAZA%20Jl.%20Kemakmuran%2C%20Pelaihari%2C%20Kec.%20Pelaihari%2C%20Kabupaten%20Tanah%20Laut%2C%20Kalimantan%20Selatan%2070812%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BENGKULU%20INDAH%20MALL%20%28%20RENAMED%20TO%20BENCOOLEN%20MALL%20%29%20Jl.%20Pariwisata%20No.1%2C%20Kelurahan%20Penurunan%2C%20Kecamatan%20Ratu%20Samban%2C%20Kota%20Bengkulu%2C%20Bengkulu%2038223%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=AMBON%20PLAZA%20Ambon%20Plaza%2C%20Jl.%20Sam%20Ratulangi%2C%20Kel%20Honipopu%2C%20Sirimau%2C%20Kota%20Ambon%2C%20Maluku%2097126%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=AMBON%20CITY%20CENTER%20Jl.%20Wolter%20Monginsidi%2C%20Passo%2C%20Kec.%20Baguala%2C%20Kota%20Ambon%2C%20Maluku%2097232%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITIMALL%20PRABUMULIH%20Jalan%20Lingkar%20Timur%2C%20Kelurahan%20Gunung%20Ibul%2C%20Kecamatan%20Prabumulih%20Timur%2C%20Kota%20Prabumulih%2C%20Sumatera%20Selatan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MASOHI%20PLAZA%20Jl.%20Abdullah%20Solisa%2C%20Namaelo%2C%20Kota%20Masohi%2C%20Central%20Maluku%20Regency%2C%20Maluku%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PALEMBANG%20CITY%20CENTER%20Jalan%20Radial%20No.4%2C%2026%20Ilir%2C%20Kecamatan%20Bukit%20Kecil%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030127%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20MALL/PALEMBANG%20Komplek%20Ilir%20Barat%20Permai%2C%20Jalan%20Letkol%20Iskandar%20Nomor%20448%2C%20Kelurahan%2024%20Ilir%2C%20Kecamatan%20Bukit%20Kecil%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=INTERNASIONAL%20PLAZA%20Jalan%20Jenderal%20Sudirman%20No.%2018%20Ilir%2C%20Kecamatan%20Ilir%20Timur%20I%2C%20Kota%20Palembang%2C%20Sumatera%20Selatan%2030114%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SAGU%20INDAH%20PLAZA%20Jl.%20Ahmad%20Yani%20No.50%2C%20Gurabesi%2C%20Kec.%20Jayapura%20Utara%2C%20Kota%20Jayapura%2C%20Papua%2099221%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20JAYAPURA%20Jl.%20Samratulangi%2C%20Bayangkara%2C%20Kec.%20Jayapura%20Utara%2C%20Kota%20Jayapura%2C%20Papua%2099112%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANSMART%20PANGKAL%20PINANG%20Jl.%20Jendral%20Sudirman%20No.8%2C%20Taman%20Bunga%2C%20Kec.%20Gerunggang%2C%20Kota%20Pangkal%20Pinang%2C%20Kepulauan%20Bangka%20Belitung%2033684%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PUNCAK%20MALL%20Jl.%20Sriwijaya%20No.10-F%2C%20Gedung%20Nasional%2C%20Kec.%20Taman%20Sari%2C%20Kota%20Pangkal%20Pinang%2C%20Kepulauan%20Bangka%20Belitung%2033684%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BTC%20PANGKAL%20PINANG%20Jalan%20Letkol%20Rusli%20Romli%2C%20Kelurahan%20Pasar%20Padi%2C%20Kecamatan%20Girimaya%2C%20Kota%20Pangkalpinang%2C%20Kepulauan%20Bangka%20Belitung%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20BTC%20Pasar%20Padi%2C%20Rangkui%2C%20Pangkal%20Pinang%20City%2C%20Bangka%20Belitung%20Islands%2033684%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20PANGKAL%20PINANG%20JL.%20SUDIRMAN%20NO.%208%20PANGKAL%20PINANG%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20KANDILO%20Kandilo%20Bahari%2076251%20Tanah%20Grogot%20East%20Kalimantan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SP%20PLAZA%20Jalan%20Letjen%20R.%20Suprapto%2C%20Kelurahan%20Tembesi%2C%20Kecamatan%20Sagulung%2C%20Kota%20Batam%20%28daerah%20Batu%20Aji%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SAGA%20MALL%20Kota%20Baru%2C%20Kec.%20Abepura%2C%20Kota%20Jayapura%2C%20Papua%2099351%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=WTC%20JAMBI%20Jalan%20Sultan%20Thaha%20No.%2017%2C%20Pasar%20Jambi%2C%20Kecamatan%20Pasar%20Jambi%2C%20Kota%20Jambi%2C%20Jambi%2036123%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GAJAH%20MADA%20SQUARE%20Jalan%20Gajah%20Mada%2C%20Patam%20Lestari%2C%20Kecamatan%20Sekupang%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BTC%20BALIKPAPAN%20Jalan%20Jenderal%20Sudirman%2020%2076114%20Balikpapan%20East%20Kalimantan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BALIKPAPAN%20PLAZA%20Jl.%20Jenderal%20Sudirman%201%2076113%20Balikpapan%20Kota%20Kalimantan%20Timur%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BALIKPAPAN%20SUPERBLOCK%20Jl%20Jenderal%20Sudirman%20No.%2047%2076114%20Balikpapan%20Kota%20Kalimantan%20Timur%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20KEBUN%20SAYUR%20Jl.%20Letjen%20Suprapto%2C%20Baru%20Ilir%2C%20Kec.%20Balikpapan%20Bar.%2C%20Kota%20Balikpapan%2C%20Kalimantan%20Timur%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAPAK%20PLAZA%20BALIKPAPAN%20Jalan%20Soekarno-Hatta%2076125%20Balikpapan%20Utara%20East%20Kalimantan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENTRA%20NIAGA%20CIBITUNG%20Cibitung%20hanya%20ada%20Plaza%20Metropolitan%20dan%20City%20Plaza%20Ramayana%20CIbitung%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=THAMRIN%20CITY%20Jl.%20H.%20M.%20Saleh%20Ishak%20%28Thamrin%20Boulevard%29%2C%20Kebon%20Melati%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20DKI%20Jakarta%2010230%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=FX%20SUDIRMAN%20Jl.%20Jenderal%20Sudirman%2C%20RT.1/RW.3%2C%20Gelora%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20DKI%20Jakarta%2010270%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENAYAN%20PARK%20Jl.%20Gerbang%20Pemuda%20No.%203%2C%20RT.1/RW.3%2C%20Gelora%2C%20Kecamatan%20Tanah%20Abang%2C%20Kota%20Jakarta%20Pusat%2C%20DKI%20Jakarta%2010270%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANS%20MART%20Jl.%20Khatib%20Sulaiman%20No.85%2C%20Ulak%20Karang%20Selatan%2C%20Kecamatan%20Padang%20Utara%2C%20Kota%20Padang%2C%20Sumatera%20Barat%2025137.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MEGA%20MALL%20SORONG%20Jalan%20Basuki%20Rahmat%20Klabulu%2C%20Malaimsimsa%2C%20Malaingkedi%2C%20Kec.%20Sorong%20Utara%2C%20Kota%20Sorong%2C%20Papua%20Barat%20Daya%2098412%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20LEMBUSWANA%20Jl.%20S.%20Parman%2C%20Gn.%20Kelua%2C%20Kec.%20Samarinda%20Ulu%2C%20Kota%20Samarinda%2C%20Kalimantan%20Timur%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20BUKIT%20TINGGI%20Plaza%20Bukittinggi%2C%20Jalan%20Ahmad%20Yani%20No.1%2C%20Benteng%20Ps.%20Atas%2C%20Kecamatan%20Guguk%20Panjang%2C%20Kota%20Bukittinggi%2C%20Sumatera%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BASKO%20GRAND%20MALL%20Jl.%20Prof.Dr.Hamka%20No.2A%2C%20Air%20Tawar%20Barat%2C%20Kec.%20Padang%20Utara%2C%20Kota%20Padang%2C%20Sumatera%20Barat.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITIMALL%20BONTANG%20Jalan%20Kalimantan%2075321%20Bontang%20Barat%20East%20Kalimantan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20GIANT%20PEKANBARU%20Jl.%20SDM.%20Soebrantas%20No.KM.%2012%2C%20Kelurahan%20Simpang%20Baru%2C%20Kecamatan%20Tuah%20Madani%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TRANSMART%20PEKANBARU%20Jalan%20Musyawarah%20Nomor%2011%2C%20Kelurahan%20Labuh%20Baru%20Timur%2C%20Kecamatan%20Payung%20Sekaki%2C%20Kota%20Pekanbaru%2C%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PEKANBARU%20XCHANGE%20Jalan%20Riau%20Nomor%20147%2C%20Kelurahan%20Padang%20Terubuk%2C%20Kecamatan%20Senapelan%2C%20Kota%20Pekanbaru%2C%20Riau%2028155%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20CIPUTRA%20SERAYA%20Jalan%20Riau%20No.%2058%2C%20Kelurahan%20Kampung%20Baru%2C%20Kecamatan%20Senapelan%2C%20Kota%20Pekanbaru%2C%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TOP%20LINE%20CITY%20CENTER%20Jalan%20Raya%20Dompak%2C%20Batu%208%2C%20Kota%20Tanjungpinang%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TANJUNG%20PINANG%20CENTRE%20Jl.%20Raya%20Dompak%2C%20Batu%208%20Atas%2C%20Sei%20Jang%2C%20Kecamatan%20Bukit%20Bestari%2C%20Kota%20Tanjung%20Pinang%2C%20Kepulauan%20Riau%202911%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BINTAN%20MALL%20Jalan%20Pos%2C%20kawasan%20Kota%20Lama%20Tanjungpinang%2C%20Kepulauan%20Riau%2C%20dekat%20Pelabuhan%20Sri%20Bintan%20Pura%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENAPELAN%20PLAZA%20Jalan%20Teuku%20Umar%2C%20Kelurahan%20Rintis%2C%20Kecamatan%20Lima%20Puluh%2C%20Kota%20Pekanbaru%2C%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20TUNAS%20REGENCY%20Tunas%20Regency%2C%20sungai%20Binti%2C%20Kec.%20Sagulung%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%2C29425%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20AVIARI%20jalan%20Pahlawan%20Bukit%20Tempayan%20Batu%20Aji%20batam%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GRAND%20BATAM%20MALL%20Jl.%20Pembangunan%2C%20Batu%20Selicin%2C%20Kecamatan%20Lubuk%20Baja%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MEGA%20MALL%20BATAM%20Jalan%20Engku%20Putri%20No.1%2C%20Belian%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DC%20MALL%20l.%20Duyung%2C%20Batu%20Selicin%2C%20Kec.%20Lubuk%20Baja%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BATAM%20CITY%20SQUARE%20Jalan%20Bunga%20Raya%2C%20Kelurahan%20Batu%20Selicin%2C%20Kecamatan%20Lubuk%20Baja%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=AVAVA%20PLAZA%20Jalan%20Kompleks%20Business%20Centre%2C%20Jodoh%2C%20Lubuk%20Baja%20Kota%2C%20Kecamatan%20Lubuk%20Baja%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20BTC%20bida%20Ayu%20Pintu%201%2C%20Kelurahan%20Mangsang%2C%20Kecamatan%20Sei%20Beduk%2C%20Kota%20Batam.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ONE%20BATAM%20MALL%20Jalan%20Raja%20M.%20Tahir%20%28atau%20Jalan%20Raja%20Haji%20Fisabilillah%29%2C%20Teluk%20Tering%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%2029444%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BENGKONG%20SHOPPING%20CENTRE%20Jalan%20Bengkong%20Laut%2C%20Kecamatan%20Bengkong%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=IT%20CENTER%20Jl.%20Piere%20Tendean%2C%20Wenang%20Utara%2C%20Kec.%20Wenang%2C%20Kota%20Manado%2C%20Sulawesi%20Utara%2095111%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GRAND%20KAWANUA%20Kayuwatu%2C%20Jl.%20A.A.%20Maramis%2C%20Kairagi%20Dua%2C%20Kec.%20Mapanget%2C%20Kota%20Manado%2C%20Sulawesi%20Utara%2095254%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20BAGAN%20BATU%20Jl.%20Jenderal%20Sudirman%2C%20Bagan%20Batu%2C%20Kecamatan%20Bagan%20Sinembah%2C%20Kabupaten%20Rokan%20Hilir%2C%20Riau%2028992%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITIMALL%20DUMAI%20Jalan%20Bukit%20Datuk%2C%20Kelurahan%20Bukit%20Datuk%2C%20Kecamatan%20Dumai%20Barat%2C%20Kota%20Dumai%2C%20Riau%2028826%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20CENTRAL%20A.YANI%20Jalan%20Jenderal%20Ahmad%20Yani%20Nomor%2042A%2C%20Padang%20Bulan%2C%20Kecamatan%20Senapelan%2C%20Kota%20Pekanbaru%2C%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20KABANJAHE%20Jalan%20Jenderal%20Sudirman%20%2C%20Padang%20Mas%2C%20Kecamatan%20Kabanjahe%2C%20Kabupaten%20Karo%2C%20Sumatera%20Utara.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20TEBING%20TINGGI%20Jl.%20Jend.%20Sudirman%2C%20Tj.%20Marulak%20Hilir%2C%20Kec.%20Rambutan%2C%20Kota%20Tebing%20Tinggi%2C%20Sumatera%20Utara%2020627%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BEKASI%20SQUARE%20/%20REVOTOWN%20Jl.%20Ahmad%20Yani%20No.Kav.%201%2C%20RT.005/RW.002%2C%20Pekayon%20Jaya%2C%20Kec.%20Bekasi%20Sel.%2C%20Kota%20Bks%2C%20Jawa%20Barat%2017148%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BRASTAGI%20SUPERMARKET%20GATOT%20SUBROTO%20Jl.%20Gatot%20Subroto%20No.288%2C%20Sei%20Putih%20Tengah%2C%20Kec.%20Medan%20Petisah%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020113%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20MARELAN%20Jl.%20Marelan%20Raya%20No.207%2C%20Tanah%20Enam%20Ratus%2C%20Kec.%20Medan%20Marelan%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020243%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20JOHOR%20MEDAN%20%28%20NEW%20MALL%20%29%20Jalan%20Karya%20Wisata%20No.65%2C%20Kelurahan%20Gedung%20Johor%2C%20Kecamatan%20Medan%20Johor%2C%20Kota%20Medan%2C%20Sumatera%20Utara%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=FOCAL%20POINT%20MALL%20Focal%20Point%20Medan%20berlokasi%20diJalan%20Arteri%20Ring%20Road%20%28Jalan%20Gagak%20Hitam%29%2C%20Kelurahan%20Asam%20Kumbang%2C%20Kecamatan%20Medan%20Selayang%2C%20Kota%20MedaN%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BRASTAGI%20SUPERMARKET%20CEMARA%20Jalan%20Cemara%20No.57%20%28bersebelahan%20dengan%20dealer%20Honda%20IDK%20Cemara%29%2C%20Pulo%20Brayan%20Darat%20II%2C%20Kecamatan%20Medan%20Timur%2C%20Kota%20Medan%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MEDAN%20MALL%20Jalan%20MT%20Haryono%20No.8%2C%20Pusat%20Pasar%2C%20Kecamatan%20Medan%20Kota%2C%20Kota%20Medan%2C%20Sumatera%20Utara%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CAMBRIDGE%20CITY%20SQUARE%20Jl.%20S.%20Parman%20No.217%2C%20Petisah%20Tengah%2C%20Kec.%20Medan%20Petisah%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020152%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=THAMRIN%20PLAZA%20alan%20MH%20Thamrin%20No.75-R%2C%20Kelurahan%20Pandau%20Hulu%20I%2C%20Kecamatan%20Medan%20Kota%2C%20Kota%20Medan%2C%20Sumatera%20Utara%28kode%20pos%2020214%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUN%20PLAZA%20Jl.%20KH.%20Zainul%20Arifin%20No.7%2C%20Kelurahan%20Madras%20Hulu%2C%20Kecamatan%20Medan%20Polonia%2C%20Kota%20Medan%2C%20Sumatera%20Utara%2020152%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20MEULABOH%20jalan%20Nasional%2C%20Desa%20Ujung%20Kalak%20%28atau%20Ujung%20Baroh%29%2C%20Kecamatan%20Johan%20Pahlawan%2C%20Kabupaten%20Aceh%20Barat%2C%20Provinsi%20Ace%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20LANGSA%20Jalan%20Ahmad%20Yani%20No.%202%2C%20Paya%20Bujok%20Seuleumak%2C%20Kecamatan%20Langsa%20Baro%2C%20Kota%20Langsa%2C%20Aceh%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20LHOKSEUMAWE%20Jl.%20Samudera%20Baru%20No.1%2C%20Simpang%20Empat%2C%20Kec.%20Banda%20Sakti%2C%20Kota%20Lhokseumawe%2C%20Aceh%2024355%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20BIREUEN%20Jalan%20Malikussaleh%2C%20Simpang%20Empat%2C%20Kecamatan%20Kota%20Juang%2C%20Kabupaten%20Bireuen%2C%20Aceh%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20SIMPANG%20LIMA%20BANDA%20ACEH%20Jl.%20H.%20Dimurthala%20Kuta%20Alam%20No.1%2C%20Kuta%20Alam%2C%20Kec.%20Kuta%20Alam%2C%20Kota%20Banda%20Aceh%2C%20Aceh%2023127%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TOP%20100%20JODOH%20Jalan%20Raya%20Ali%20Haji%2C%20Kompleks%20Batam%20Sentosa%2C%20Kelurahan%20Lubuk%20Baja%20Kota%2C%20Kecamatan%20Lubuk%20Baja%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%28Kode%20Pos%2029444%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BARATA%20DEPT.%20STORE%20CAN%20NOT%20FIND%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITY%20WALK%20GAJAH%20MADA%20CAN%20NOT%20FIND%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITRA%20GRAND%20CIBUBUR%20MALL%20Under%20kak%20Vio%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20TAMAN%20PALEM%20INDAH%20Jl.%20Outer%20Ring%20Road%2C%20RT.13/RW.10%2C%20Cengkareng%20Tim.%2C%20Kecamatan%20Cengkareng%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011730%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=KHATULISTIWA%20PLAZA%20Jl.%20H.%20Agus%20Salim%2C%20Darat%20Sekip%2C%20Kec.%20Pontianak%20Kota%2C%20Kota%20Pontianak%2C%20Kalimantan%20Barat%2078243%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20BIDA%20AYU%20alan%20Bida%20Ayu%20Pintu%201%2C%20Mangsang%2C%20Kecamatan%20Sei%20Beduk%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BEKASI%20TRADE%20CENTRE%20Jl.%20H.%20M.%20Joyomartono%2C%20Bulak%20Kapal%2C%20Bekasi%20Timur%2017113%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LA%20PIAZZA%20%3E%20GAFOY%20Sentra%20Kelapa%20Gading%2C%20North%20Jakarta%2C%20at%20Jl.%20Boulevard%20Raya%20Blok%20M%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PHINISI%20POINT%20MAL%20Jl.%20Metro%20Tj.%20Bunga%20No.2%2C%20Panambungan%2C%20Kec.%20Mariso%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090121%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20LIPPO%20PLAZA%20BUTON%20Jl.%20Sultan%20Hasanuddin%2C%20Batulo%2C%20Wolio%2C%20Bau-Bau%20City%2C%20South%20East%20Sulawesi%2093716%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SLEMAN%20CITY%20HALL%20Jl.%20Magelang%20Jl.%20Gito%20Gati%20No.KM%209%2C%20Denggung%2C%20Tridadi%2C%20Kec.%20Sleman%2C%20Kabupaten%20Sleman%2C%20Daerah%20Istimewa%20Yogyakarta%2055511%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=JOGJATRONIK%20MALL%2059V9%2BHRJ%20Jogjatronik%2C%20Jl.%20Brigjen%20Katamso%2C%20Prawirodirjan%2C%20Kec.%20Gondomanan%2C%20Kota%20Yogyakarta%2C%20Daerah%20Istimewa%20Yogyakarta%2055121%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CIHAMPELAS%20WALK%20Jl.%20Cihampelas%20No.160%2C%20Cipaganti%2C%20Kec.%20Coblong%2C%20Kota%20Bandung%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20KEBON%20KALAPA%20Jl.%20Moch.%20Toha%20Jl.%20Pungkur%2C%20Pungkur%2C%20Kec.%20Regol%2C%20Kota%20Bandung%2C%20Jawa%20Barat%2040252%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=KINGS%20SHOPPING%20CENTRE%20Jl.%20Kepatihan%20No.11-17%2C%20Balonggede%2C%20Kec.%20Regol%2C%20Kota%20Bandung%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20IBCC%20Jl.%20Ahmad%20Yani%20No.296%2C%20Kacapiring%2C%20Kec.%20Batununggal%2C%20Kota%20Bandung%2C%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUKABUMI%20SUPERMALL%20Jl.%20A.%20Yani%20No.119%2C%20Gunungparang%2C%20Kec.%20Cikole%2C%20Kota%20Sukabumi%2C%20Jawa%20Barat%2043111%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITIMALL%20GARUT%20Jl.%20Jendral%20Sudirman%20No.31%2C%20Sucikaler%2C%20Kec.%20Karangpawitan%2C%20Kabupaten%20Garut%2C%20Jawa%20Barat%2044182%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DHOHO%20PLAZA%20Jl.%20Brigjen%20Katamso%20No.1A%2C%20Kp.%20Dalem%2C%20Kec.%20Kota%2C%20Kota%20Kediri%2C%20Jawa%20Timur%2064129%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUN%20CITY%20MALL%20Jl.%20Sun%20City%20No.8%2C%20Oro-oro%20Ombo%2C%20Kec.%20Kartoharjo%2C%20Kota%20Madiun%2C%20Jawa%20Timur%2063119%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BANYUWANGI%20ROXY%20SQUARE%20Jl.%20Jenderal%20Ahmad%20Yani%20No.21%20-%2023%2C%20Penganjuran%2C%20Kec.%20Banyuwangi%2C%20Kabupaten%20Banyuwangi%2C%20Jawa%20Timur%2068416%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BG%20JUNCTION%20Jl.%20Bubutan%20No.1-7%2C%20Bubutan%2C%20Kec.%20Bubutan%2C%20Surabaya%2C%20Jawa%20Timur%2060174%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CENTRAL%20MALL%20Jl.%20Tidar%20No.350%2C%20Tembok%20Dukuh%2C%20Kec.%20Bubutan%2C%20Surabaya%2C%20Jawa%20Timur%2060173%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20MALL/SIDOARJO%20Jl.%20Diponegoro%20No.2%2C%20Rw5%2C%20Sidokumpul%2C%20Kec.%20Sidoarjo%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061213%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=HITECH%20MALL%20Jl.%20Kusuma%20Bangsa%2C%20Tambaksari%2C%20Kec.%20Tambaksari%2C%20Surabaya%2C%20Jawa%20Timur%2060136%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=FLOBAMORA%20MALL%20Oebufu%2C%20Kec.%20Oebobo%2C%20Kota%20Kupang%2C%20Nusa%20Tenggara%20Tim.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MATARAM%20MALL%20Jl.%20Cilinaya%20No.7%2C%20Cilinaya%2C%20Kec.%20Cakranegara%2C%20Kota%20Mataram%2C%20Nusa%20Tenggara%20Bar.%2083239%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUN%20CITY%20PLAZA%20Jl.%20Pahlawan%20No.1%2C%20Rw6%2C%20Sidokumpul%2C%20Kec.%20Sidoarjo%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061213%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LIPPO%20PLAZA%20JEMBER%20Jl.%20Gajah%20Mada%20No.106%2C%20Kb.%20Kidul%2C%20Jember%20Kidul%2C%20Kec.%20Kaliwates%2C%20Kabupaten%20Jember%2C%20Jawa%20Timur%2068131%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LIPPO%20PLAZA%20BATU%20Jl.%20Diponegoro%20No.1%2C%20Sisir%2C%20Kec.%20Batu%2C%20Kota%20Batu%2C%20Jawa%20Timur%2065314%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=HARTONO%20Jl.%20Dr.%20Ir.%20H.%20Soekarno%20No.35%2C%20Klampis%20Ngasem%2C%20Kec.%20Sukolilo%2C%20Surabaya%2C%20Jawa%20Timur%2060282%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20MALANG%20CITY%20POINT%20Jl.%20Terusan%20Dieng%20No.%2032%2C%20Mall%20No.8A%20Lt.%20GS%2C%20Pisang%20Candi%2C%20Kec.%20Sukun%2C%20Kota%20Malang%2C%20Jawa%20Timur%2065115%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MEGA%20MALL%20ABEPURA%20Jl.%20Raya%20Abepura%20-%20Sentani%20No.10%2C%20Kota%20Baru%2C%20Kec.%20Abepura%2C%20Kota%20Jayapura%2C%20Papua%2099351%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20MATAHARI%20Jl.%20Pahlawan%20No.840%2C%20Pangongangan%2C%20Kec.%20Manguharjo%2C%20Kota%20Madiun%2C%20Jawa%20Timur%2063121%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUNCITY%20MALL%20SIDOARJO%20Jl.%20Pahlawan%2C%20Rw6%2C%20Sidokumpul%2C%20Kec.%20Sidoarjo%2C%20Kabupaten%20Sidoarjo%2C%20Jawa%20Timur%2061213%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SENTRA%20GROSIR%20CIKARANG%20Jl.%20Re.%20Martadinata%2095%2017530%20Cikarang%20Utara%20Jawa%20Barat%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=VIVO%20MALL%20SENTUL%20Jl.%20Raya%20Jakarta-Bogor%20No.Km.50%2C%20Cimandala%2C%20Kec.%20Sukaraja%2C%20Kabupaten%20Bogor%2C%20Jawa%20Barat%2016710%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20CIBINONG%20Jl.%20Raya%20Mayor%20Oking%20Jaya%20Atmaja%20No.28%2C%20Cibinong%2C%20Kec.%20Cibinong%2C%20Kabupaten%20Bogor%2C%20Jawa%20Barat%2016911%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SARINAH%20Jl.%20M.H.%20Thamrin%20No.11%2C%20RT.8/RW.4%2C%20Gondangdia%2C%20Kec.%20Menteng%2C%20Kota%20Jakarta%20Pusat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2010350%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DEPOK%20TOWN%20SQUARE%20Jl.%20Margonda%20Raya%20No.1%2C%20Pondok%20Cina%2C%20Kecamatan%20Beji%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016424%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=DEPOK%20TOWN%20CENTER%20Jl.%20Raya%20Sawangan%20No.1%2C%20Rangkapan%20Jaya%2C%20Kec.%20Pancoran%20Mas%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016435%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PESONA%20SQUARE%20DEPOK%20Jl.%20Ir.%20H.%20Juanda%20No.22a%2C%20Bakti%20Jaya%2C%20Kec.%20Sukmajaya%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016418%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20DEPOK%20Jl.%20Margonda%20No.56%2C%20Depok%2C%20Kec.%20Pancoran%20Mas%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016431%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=CITY%20PLAZA%20DEPOK%20Jl.%20Margonda%2C%20Depok%2C%20Kec.%20Pancoran%20Mas%2C%20Kota%20Depok%2C%20Jawa%20Barat%2016431%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GRAND%20CAKUNG%20Jl.%20Sri%20Sultan%20Hamengkubuwono%20IX%20No.KM.%2025%2C%20Ujung%20Menteng%2C%20Kec.%20Cakung%2C%20Kota%20Jakarta%20Timur%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2013960%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20CIJANTUNG%20Jl.%20Pendidikan%2C%20RT.1/RW.4%2C%20Cijantung%2C%20Kecamatan%20Pasar%20Rebo%2C%20Kota%20Jakarta%20Timur%2C%20DKI%20Jakarta%2013770%2C%20Indonesia%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MANGGA%20DUA%20SQUARE%20Jl.%20Gn.%20Sahari%20No.1%2C%20RT.11/RW.6%2C%20Ancol%2C%20Kec.%20Pademangan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014420%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=KOJA%20TRADE%20MALL%20Jl.%20Kramat%20Jaya%20Raya%20No.30%2C%20RT.2/RW.17%2C%20Tugu%20Utara%2C%20Kec.%20Koja%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014260%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GREEN%20BAY%20PLUIT%20Jl.%20Pluit%20Karang%20Ayu%20Barat%20Blok%20B1%2C%20RT.20/RW.2%2C%20Pluit%2C%20Kecamatan%20Penjaringan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014450%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=ITC%20MANGGA%20DUA%20Jl.%20Mangga%20Dua%20Raya%2C%20RT.11/RW.5%2C%20Ancol%2C%20Kec.%20Pademangan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014430%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PASAR%20PAGI%20MANGGA%20DUA%20Jl.%20Mangga%20Dua%20Raya%2C%20RT.9/RW.4%2C%20Ancol%2C%20Kec.%20Pademangan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014430%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MAHAKA%20SQUARE%20Jl.%20Raya%20Kelapa%20Nias%20No.6%2C%20RT.8/RW.6%2C%20Klp.%20Gading%20Bar.%2C%20Kec.%20Klp.%20Gading%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014240%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLUIT%20JUNCTION%20Penjaringan%2C%20Kecamatan%20Penjaringan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014440%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=BELLA%20TERRA%20LIFESTYLE%20CENTER%20Ruko%20Kirana%20Boutique%2C%20Jl.%20Boulevard%20Raya%20No.1%2C%20Klp.%20Gading%20Tim.%2C%20Kec.%20Klp.%20Gading%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014240%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLUIT%20VILLAGE%20Jl.%20Pluit%20Indah%2C%20RT.6/RW.4%2C%20Pluit%2C%20Kecamatan%20Penjaringan%2C%20Jkt%20Utara%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2014450%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20MALL/SERANG%20gJl.%20Veteran%20No.17%2C%20Kotabaru%2C%20Kec.%20Serang%2C%20Kota%20Serang%2C%20Banten%2042113%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LOTTE%20MART%20FATMAWATI%20Jl.%20RS.%20Fatmawati%20Raya%20No.%2015%2C%20Komplek%20Golden%20Fatmawati%2C%20RT.8/RW.6%2C%20Gandaria%20Selatan%2C%20Kecamatan%20Cilandak%2C%20Kota%20Jakarta%20Selatan%2C%20DKI%20Jakarta%2012420%2C%20Indonesia.%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=WTC%20MATAHARI%20Jl.%20Raya%20Serpong%20No.39%2C%20Pd.%20Jagung%2C%20Kec.%20Serpong%20Utara%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015326%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PARADISE%20WALK%20Jl.%20Puspiptek%20Raya%2C%20Kelurahan%20Babakan%2C%20Kecamatan%20Setu%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015315%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20CIPUTAT%20Jl.%20Dewi%20Sartika%20No.1%2C%20Cipayung%2C%20Kec.%20Ciputat%2C%20Kota%20Tangerang%20Selatan%2C%20Banten%2015412%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=Q%20BIG%20MALL%20Jl.%20BSD%20Raya%20Utama%2C%20Lengkong%20Kulon%2C%20Kecamatan%20Pagedangan%2C%20Kabupaten%20Tangerang%2C%20Banten%2015331%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SEASONS%20CITY%20Jl.%20Prof.%20Dr.%20Latumeten%20No.33%2C%20RT.001/RW.005%2C%20Jemb.%20Besi%2C%20Kec.%20Tambora%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011320%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=HUBLIFE%20MALL%20Jl.%20Tj.%20Duren%20Timur%202%2C%20RT.12/RW.1%2C%20Tj.%20Duren%20Sel.%2C%20Kec.%20Grogol%20petamburan%2C%20Kota%20Jakarta%20Barat%2C%20Daerah%20Khusus%20Ibukota%20Jakarta%2011470%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=GOTTA%20PLAZA%20Jl.%20Jend%20Sudirman%2C%20Langgur%2C%20Kel.%20Ohoijang%20Watdek%2C%20Kei%20Kecil%2C%20Sotheast%20Maluku%20Regency%2C%20Maluku%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20JATILAND%20Jl.%20Pahlawan%20Revolusi%2C%20Gamalama%2C%20Kec.%20Ternate%20Tengah%2C%20Kota%20Ternate%2C%20Maluku%20Utara%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MTC%20KAREBOSI%20Jl.%20Ahmad%20Yani%20No.49%2C%20Pattunuang%2C%20Kec.%20Wajo%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090174%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MAKASSAR%20TOWN%20SQUARE%20Jl.%20Perintis%20Kemerdekaan%20No.26%2C%20Tamalanrea%20Jaya%2C%20Kec.%20Tamalanrea%2C%20Kota%20Makassar%2C%20Sulawesi%20Selatan%2090245%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20TRANSMART%20JAMBI%20Jl.%20Jend.%20Sudirman%20No.11%2C%20Tambak%20Sari%2C%20Kecamatan%20Jambi%20Selatan%2C%20Kota%20Jambi%2C%20Jambi%2036122%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LUCKY%20PLAZA%20Jl.%20Imam%20Bonjol%2C%20Lubuk%20Baja%20Kota%2C%20Batam%20%28Blok%20F/4-5%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=NAGOYA%20HILL%20MALL%20Jl.%20Teuku%20Umar%2C%20Lubuk%20Baja%20Kota%2C%20Kecamatan%20Lubuk%20Baja%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029432%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=POLLUX%20MEISTERSTADT%20Jalan%20Jenderal%20Ahmad%20Yani%2C%20Kelurahan%20Teluk%20Tering%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%28area%20Batam%20Center%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MITRA%20MALL%20Jalan%20Bunga%20Raya%2C%20Bukit%20Tempayan%2C%20Kecamatan%20Batu%20Aji%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20BOTANIA%202%20Jalan%20Raja%20Alikelana%2C%20Kelurahan%20Belian%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029464%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PAMBIL%20MALL%20Jalan%20Ahmad%20Yani%2C%20Muka%20Kuning%2C%20Kecamatan%20Sei%20Beduk%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029433%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20MUSTAFA%20Raja%20Alikelana%2C%20Kelurahan%20Belian%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PANBILL%20MALL%20Jalan%20Ahmad%20Yani%2C%20Kawasan%20Komersial%20Panbil%2C%20Muka%20Kuning%2C%20Kecamatan%20Sei%20Beduk%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029433%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20BOTANIA%20Jl.%20Tengku%20Sulung%2C%20Belian%2C%20Kec.%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%2029465%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=STC%20MALL%20Jalan%20Mesjid%20Baiturrahman%2C%20Sungai%20Harapan%2C%20Kecamatan%20Sekupang%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=TOP%20100%20TEMBESI%20Komplek%20Pertokoan%20Mall%20Top%20100%2C%20Jalan%20Letnan%20Jenderal%20R.%20Soeprapto%2C%20Kelurahan%20Tembesi%2C%20Kecamatan%20Sagulung%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029439%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=RAMAYANA%20MALL/BATAM%20Jalan%20Kawasan%20Komersil%20Muka%20Kuning%2C%20Kabil%2C%20Kecamatan%20Nongsa%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%2829433%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=LIPPO%20PLAZA%20JAMBI%20Jl.%20Mayor%20Abd.%20Karta%20Wirana%20No.RT.15%2C%20Budiman%2C%20Kec.%20Jambi%20Tim.%2C%20Kota%20Jambi%2C%20Jambi%2036123%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=IRIAN%20SUPERMARKET%20KISARAN%20Jalan%20Imam%20Bonjol%20No.%20149%2C%20Kelurahan%20Kisaran%20Timur%2C%20Kecamatan%20Kota%20Kisaran%20Timur%2C%20Kabupaten%20Asahan%2C%20Sumatera%20Utara%28Kode%20Pos%3A%2021211%29%20-</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/?api=1&amp;query=SUZUYA%20MALL%20TANJUNG%20MORAWA%20Jl.%20Medan-Lubuk%20Pakam%20Dusun%20IV%20Km.%2017%2C5%2C%20Tanjung%20Morawa%20A%2C%20Kecamatan%20Tanjung%20Morawa%2C%20Kabupaten%20Deli%20Serdang%2C%20Sumatera%20Utara%2020362%20-</t>
+  </si>
+  <si>
+    <t>12,000-20,000</t>
+  </si>
+  <si>
+    <t>360,000-600,000</t>
+  </si>
+  <si>
+    <t>5,000-8,000</t>
+  </si>
+  <si>
+    <t>150,000-240,000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="172" formatCode="0.000000"/>
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2317,15 +3254,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{9439849F-60B4-4DE9-A960-9C164DDE9542}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2626,15 +3570,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N302"/>
+  <dimension ref="A1:R302"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="51.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2677,8 +3622,20 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="P1" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>749</v>
+      </c>
+      <c r="R1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2721,8 +3678,20 @@
       <c r="N2">
         <v>119.25480899999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" t="s">
+        <v>751</v>
+      </c>
+      <c r="P2" s="4">
+        <v>443349</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2765,8 +3734,20 @@
       <c r="N3">
         <v>115.1720833</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>752</v>
+      </c>
+      <c r="P3" s="4">
+        <v>257315</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2809,8 +3790,20 @@
       <c r="N4">
         <v>115.139672</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" t="s">
+        <v>753</v>
+      </c>
+      <c r="P4" s="4">
+        <v>526029</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2853,8 +3846,20 @@
       <c r="N5">
         <v>140.39454900000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" t="s">
+        <v>754</v>
+      </c>
+      <c r="P5" s="4">
+        <v>240609</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2897,8 +3902,20 @@
       <c r="N6">
         <v>115.238422</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" t="s">
+        <v>755</v>
+      </c>
+      <c r="P6" s="4">
+        <v>526029</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2941,8 +3958,20 @@
       <c r="N7">
         <v>115.238422</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" t="s">
+        <v>756</v>
+      </c>
+      <c r="P7" s="4">
+        <v>526029</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2985,8 +4014,20 @@
       <c r="N8">
         <v>112.6326371</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>757</v>
+      </c>
+      <c r="P8" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3029,8 +4070,20 @@
       <c r="N9">
         <v>112.634158</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>758</v>
+      </c>
+      <c r="P9" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3073,8 +4126,20 @@
       <c r="N10">
         <v>112.6507252</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>759</v>
+      </c>
+      <c r="P10" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -3117,8 +4182,20 @@
       <c r="N11">
         <v>112.02496379999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" t="s">
+        <v>760</v>
+      </c>
+      <c r="P11" s="4">
+        <v>201992</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -3161,8 +4238,20 @@
       <c r="N12">
         <v>110.364373</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" t="s">
+        <v>761</v>
+      </c>
+      <c r="P12" s="4">
+        <v>413784</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -3205,8 +4294,20 @@
       <c r="N13">
         <v>110.36608</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>762</v>
+      </c>
+      <c r="P13" s="4">
+        <v>413784</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -3249,8 +4350,20 @@
       <c r="N14">
         <v>110.38809430000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" t="s">
+        <v>763</v>
+      </c>
+      <c r="P14" s="4">
+        <v>413784</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3293,8 +4406,20 @@
       <c r="N15">
         <v>110.366238</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" t="s">
+        <v>764</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3337,8 +4462,20 @@
       <c r="N16">
         <v>110.39472000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" t="s">
+        <v>765</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1197301</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -3381,8 +4518,20 @@
       <c r="N17">
         <v>110.39472000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" t="s">
+        <v>766</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1197301</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -3425,8 +4574,20 @@
       <c r="N18">
         <v>112.67</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" t="s">
+        <v>767</v>
+      </c>
+      <c r="P18" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -3469,8 +4630,20 @@
       <c r="N19">
         <v>110.79686239999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" t="s">
+        <v>768</v>
+      </c>
+      <c r="P19" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -3513,8 +4686,20 @@
       <c r="N20">
         <v>110.8103874</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" t="s">
+        <v>769</v>
+      </c>
+      <c r="P20" s="4">
+        <v>908228</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -3557,8 +4742,20 @@
       <c r="N21">
         <v>110.212641</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" t="s">
+        <v>770</v>
+      </c>
+      <c r="P21" s="4">
+        <v>506673</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -3601,8 +4798,20 @@
       <c r="N22">
         <v>108.2607</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" t="s">
+        <v>771</v>
+      </c>
+      <c r="P22" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -3645,8 +4854,20 @@
       <c r="N23">
         <v>108.2607</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" t="s">
+        <v>772</v>
+      </c>
+      <c r="P23" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -3689,8 +4910,20 @@
       <c r="N24">
         <v>108.3422722</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" t="s">
+        <v>773</v>
+      </c>
+      <c r="P24" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R24" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -3733,8 +4966,20 @@
       <c r="N25">
         <v>108.3215921</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" t="s">
+        <v>774</v>
+      </c>
+      <c r="P25" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -3777,8 +5022,20 @@
       <c r="N26">
         <v>112.7325051</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" t="s">
+        <v>775</v>
+      </c>
+      <c r="P26" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -3821,8 +5078,20 @@
       <c r="N27">
         <v>112.6894997</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" t="s">
+        <v>776</v>
+      </c>
+      <c r="P27" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3865,8 +5134,20 @@
       <c r="N28">
         <v>112.7392222</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" t="s">
+        <v>777</v>
+      </c>
+      <c r="P28" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -3909,8 +5190,20 @@
       <c r="N29">
         <v>112.7392222</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" t="s">
+        <v>778</v>
+      </c>
+      <c r="P29" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -3953,8 +5246,20 @@
       <c r="N30">
         <v>112.7174334</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" t="s">
+        <v>779</v>
+      </c>
+      <c r="P30" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R30" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -3997,8 +5302,20 @@
       <c r="N31">
         <v>112.6716934</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" t="s">
+        <v>780</v>
+      </c>
+      <c r="P31" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -4041,8 +5358,20 @@
       <c r="N32">
         <v>112.7476266</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" t="s">
+        <v>781</v>
+      </c>
+      <c r="P32" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -4085,8 +5414,20 @@
       <c r="N33">
         <v>112.74504829999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" t="s">
+        <v>782</v>
+      </c>
+      <c r="P33" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -4129,8 +5470,20 @@
       <c r="N34">
         <v>112.73487249999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" t="s">
+        <v>783</v>
+      </c>
+      <c r="P34" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -4173,8 +5526,20 @@
       <c r="N35">
         <v>110.431178</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" t="s">
+        <v>784</v>
+      </c>
+      <c r="P35" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -4217,8 +5582,20 @@
       <c r="N36">
         <v>112.61239999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" t="s">
+        <v>785</v>
+      </c>
+      <c r="P36" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -4261,8 +5638,20 @@
       <c r="N37">
         <v>110.41083</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" t="s">
+        <v>786</v>
+      </c>
+      <c r="P37" s="4">
+        <v>1243381</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R37" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -4305,8 +5694,20 @@
       <c r="N38">
         <v>110.4435859</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" t="s">
+        <v>787</v>
+      </c>
+      <c r="P38" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R38" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -4349,8 +5750,20 @@
       <c r="N39">
         <v>107.7592616</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" t="s">
+        <v>788</v>
+      </c>
+      <c r="P39" s="4">
+        <v>3723181</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R39" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -4393,8 +5806,20 @@
       <c r="N40">
         <v>109.19860799999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" t="s">
+        <v>789</v>
+      </c>
+      <c r="P40" s="4">
+        <v>291806</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R40" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -4437,8 +5862,20 @@
       <c r="N41">
         <v>110.40374199999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" t="s">
+        <v>790</v>
+      </c>
+      <c r="P41" s="4">
+        <v>908228</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -4481,8 +5918,20 @@
       <c r="N42">
         <v>110.38950269999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" t="s">
+        <v>791</v>
+      </c>
+      <c r="P42" s="4">
+        <v>1693034</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R42" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -4525,8 +5974,20 @@
       <c r="N43">
         <v>110.4267007</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" t="s">
+        <v>792</v>
+      </c>
+      <c r="P43" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R43" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -4569,8 +6030,20 @@
       <c r="N44">
         <v>112.8549</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" t="s">
+        <v>793</v>
+      </c>
+      <c r="P44" s="4">
+        <v>283366</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R44" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -4613,8 +6086,20 @@
       <c r="N45">
         <v>107.6137269</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" t="s">
+        <v>794</v>
+      </c>
+      <c r="P45" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -4657,8 +6142,20 @@
       <c r="N46">
         <v>109.67203000000001</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" t="s">
+        <v>795</v>
+      </c>
+      <c r="P46" s="4">
+        <v>317534</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -4701,8 +6198,20 @@
       <c r="N47">
         <v>108.5629101</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" t="s">
+        <v>796</v>
+      </c>
+      <c r="P47" s="4">
+        <v>348911</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -4745,8 +6254,20 @@
       <c r="N48">
         <v>108.5591812</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" t="s">
+        <v>797</v>
+      </c>
+      <c r="P48" s="4">
+        <v>348911</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R48" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -4789,8 +6310,20 @@
       <c r="N49">
         <v>106.80831910000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" t="s">
+        <v>798</v>
+      </c>
+      <c r="P49" s="4">
+        <v>413784</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -4833,8 +6366,20 @@
       <c r="N50">
         <v>110.6722</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" t="s">
+        <v>799</v>
+      </c>
+      <c r="P50" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R50" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -4877,8 +6422,20 @@
       <c r="N51">
         <v>106.79667000000001</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" t="s">
+        <v>800</v>
+      </c>
+      <c r="P51" s="4">
+        <v>1122771</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -4921,8 +6478,20 @@
       <c r="N52">
         <v>106.8022709</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" t="s">
+        <v>801</v>
+      </c>
+      <c r="P52" s="4">
+        <v>1122771</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -4965,8 +6534,20 @@
       <c r="N53">
         <v>107.444568</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" t="s">
+        <v>802</v>
+      </c>
+      <c r="P53" s="4">
+        <v>1029561</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R53" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -5009,8 +6590,20 @@
       <c r="N54">
         <v>106.77626429999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" t="s">
+        <v>803</v>
+      </c>
+      <c r="P54" s="4">
+        <v>1122771</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -5053,8 +6646,20 @@
       <c r="N55">
         <v>107.0750972</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" t="s">
+        <v>804</v>
+      </c>
+      <c r="P55" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R55" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -5097,8 +6702,20 @@
       <c r="N56">
         <v>105.88436</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O56" t="s">
+        <v>805</v>
+      </c>
+      <c r="P56" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R56" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -5141,8 +6758,20 @@
       <c r="N57">
         <v>105.88436</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O57" t="s">
+        <v>806</v>
+      </c>
+      <c r="P57" s="4">
+        <v>586166</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R57" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -5185,8 +6814,20 @@
       <c r="N58">
         <v>107.4566172</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" t="s">
+        <v>807</v>
+      </c>
+      <c r="P58" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R58" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -5229,8 +6870,20 @@
       <c r="N59">
         <v>107.44395299999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" t="s">
+        <v>808</v>
+      </c>
+      <c r="P59" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -5273,8 +6926,20 @@
       <c r="N60">
         <v>106.9781505</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O60" t="s">
+        <v>809</v>
+      </c>
+      <c r="P60" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R60" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -5317,8 +6982,20 @@
       <c r="N61">
         <v>106.738321</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O61" t="s">
+        <v>810</v>
+      </c>
+      <c r="P61" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R61" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -5361,8 +7038,20 @@
       <c r="N62">
         <v>106.83929910000001</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" t="s">
+        <v>811</v>
+      </c>
+      <c r="P62" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q62" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -5405,8 +7094,20 @@
       <c r="N63">
         <v>107.33363799999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O63" t="s">
+        <v>812</v>
+      </c>
+      <c r="P63" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q63" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -5449,8 +7150,20 @@
       <c r="N64">
         <v>107.33363799999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O64" t="s">
+        <v>813</v>
+      </c>
+      <c r="P64" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q64" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R64" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -5493,8 +7206,20 @@
       <c r="N65">
         <v>107.2898017</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O65" t="s">
+        <v>814</v>
+      </c>
+      <c r="P65" s="4">
+        <v>2519882</v>
+      </c>
+      <c r="Q65" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R65" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -5537,8 +7262,20 @@
       <c r="N66">
         <v>106.7031657</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O66" t="s">
+        <v>815</v>
+      </c>
+      <c r="P66" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q66" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R66" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -5581,8 +7318,20 @@
       <c r="N67">
         <v>106.107681</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O67" t="s">
+        <v>816</v>
+      </c>
+      <c r="P67" s="4">
+        <v>1392049</v>
+      </c>
+      <c r="Q67" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R67" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -5625,8 +7374,20 @@
       <c r="N68">
         <v>106.665938</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" t="s">
+        <v>817</v>
+      </c>
+      <c r="P68" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q68" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R68" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -5669,8 +7430,20 @@
       <c r="N69">
         <v>106.80144060000001</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" t="s">
+        <v>818</v>
+      </c>
+      <c r="P69" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q69" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R69" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -5713,8 +7486,20 @@
       <c r="N70">
         <v>107.04671879999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" t="s">
+        <v>819</v>
+      </c>
+      <c r="P70" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q70" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R70" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -5757,8 +7542,20 @@
       <c r="N71">
         <v>106.779111</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" t="s">
+        <v>820</v>
+      </c>
+      <c r="P71" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q71" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R71" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -5801,8 +7598,20 @@
       <c r="N72">
         <v>106.64834140000001</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" t="s">
+        <v>821</v>
+      </c>
+      <c r="P72" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q72" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R72" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -5845,8 +7654,20 @@
       <c r="N73">
         <v>106.780438</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" t="s">
+        <v>822</v>
+      </c>
+      <c r="P73" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q73" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R73" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -5889,8 +7710,20 @@
       <c r="N74">
         <v>106.878243</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" t="s">
+        <v>823</v>
+      </c>
+      <c r="P74" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q74" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R74" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -5933,8 +7766,20 @@
       <c r="N75">
         <v>106.82941580000001</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" t="s">
+        <v>824</v>
+      </c>
+      <c r="P75" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q75" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R75" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -5977,8 +7822,20 @@
       <c r="N76">
         <v>106.7240236</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" t="s">
+        <v>825</v>
+      </c>
+      <c r="P76" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q76" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R76" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -6021,8 +7878,20 @@
       <c r="N77">
         <v>106.75119460000001</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" t="s">
+        <v>826</v>
+      </c>
+      <c r="P77" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q77" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R77" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -6065,8 +7934,20 @@
       <c r="N78">
         <v>106.83106359999999</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" t="s">
+        <v>827</v>
+      </c>
+      <c r="P78" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q78" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R78" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -6109,8 +7990,20 @@
       <c r="N79">
         <v>106.805572</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" t="s">
+        <v>828</v>
+      </c>
+      <c r="P79" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q79" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R79" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -6153,8 +8046,20 @@
       <c r="N80">
         <v>106.7987329</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" t="s">
+        <v>829</v>
+      </c>
+      <c r="P80" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q80" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R80" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -6197,8 +8102,20 @@
       <c r="N81">
         <v>106.864919</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" t="s">
+        <v>830</v>
+      </c>
+      <c r="P81" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q81" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R81" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -6241,8 +8158,20 @@
       <c r="N82">
         <v>107.00797900000001</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" t="s">
+        <v>831</v>
+      </c>
+      <c r="P82" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q82" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R82" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -6285,8 +8214,20 @@
       <c r="N83">
         <v>106.8692576</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" t="s">
+        <v>832</v>
+      </c>
+      <c r="P83" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q83" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R83" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -6329,8 +8270,20 @@
       <c r="N84">
         <v>106.58333</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" t="s">
+        <v>833</v>
+      </c>
+      <c r="P84" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q84" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R84" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -6373,8 +8326,20 @@
       <c r="N85">
         <v>106.58333</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" t="s">
+        <v>834</v>
+      </c>
+      <c r="P85" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q85" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R85" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -6417,8 +8382,20 @@
       <c r="N86">
         <v>106.98446819999999</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" t="s">
+        <v>835</v>
+      </c>
+      <c r="P86" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q86" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R86" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -6461,8 +8438,20 @@
       <c r="N87">
         <v>106.990959</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" t="s">
+        <v>836</v>
+      </c>
+      <c r="P87" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q87" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R87" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -6505,8 +8494,20 @@
       <c r="N88">
         <v>106.9108174</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" t="s">
+        <v>837</v>
+      </c>
+      <c r="P88" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q88" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R88" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -6549,8 +8550,20 @@
       <c r="N89">
         <v>106.77985940000001</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" t="s">
+        <v>838</v>
+      </c>
+      <c r="P89" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q89" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R89" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -6593,8 +8606,20 @@
       <c r="N90">
         <v>106.79969389999999</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" t="s">
+        <v>839</v>
+      </c>
+      <c r="P90" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q90" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R90" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -6637,8 +8662,20 @@
       <c r="N91">
         <v>106.98876</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" t="s">
+        <v>840</v>
+      </c>
+      <c r="P91" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q91" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R91" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -6681,8 +8718,20 @@
       <c r="N92">
         <v>106.8086057</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" t="s">
+        <v>841</v>
+      </c>
+      <c r="P92" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q92" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R92" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>14</v>
       </c>
@@ -6725,8 +8774,20 @@
       <c r="N93">
         <v>106.6909737</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" t="s">
+        <v>842</v>
+      </c>
+      <c r="P93" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q93" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R93" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>14</v>
       </c>
@@ -6769,8 +8830,20 @@
       <c r="N94">
         <v>106.8012609</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" t="s">
+        <v>843</v>
+      </c>
+      <c r="P94" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q94" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R94" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>14</v>
       </c>
@@ -6813,8 +8886,20 @@
       <c r="N95">
         <v>106.606928</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" t="s">
+        <v>844</v>
+      </c>
+      <c r="P95" s="4">
+        <v>2516417</v>
+      </c>
+      <c r="Q95" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R95" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>14</v>
       </c>
@@ -6857,8 +8942,20 @@
       <c r="N96">
         <v>106.7995999</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" t="s">
+        <v>845</v>
+      </c>
+      <c r="P96" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q96" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R96" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -6901,8 +8998,20 @@
       <c r="N97">
         <v>106.810351</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" t="s">
+        <v>846</v>
+      </c>
+      <c r="P97" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q97" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R97" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>14</v>
       </c>
@@ -6945,8 +9054,20 @@
       <c r="N98">
         <v>106.82950099999999</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" t="s">
+        <v>847</v>
+      </c>
+      <c r="P98" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q98" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R98" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>14</v>
       </c>
@@ -6989,8 +9110,20 @@
       <c r="N99">
         <v>106.798213</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" t="s">
+        <v>848</v>
+      </c>
+      <c r="P99" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q99" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R99" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>14</v>
       </c>
@@ -7033,8 +9166,20 @@
       <c r="N100">
         <v>106.8322373</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" t="s">
+        <v>849</v>
+      </c>
+      <c r="P100" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q100" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R100" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>14</v>
       </c>
@@ -7077,8 +9222,20 @@
       <c r="N101">
         <v>106.81459220000001</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" t="s">
+        <v>850</v>
+      </c>
+      <c r="P101" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q101" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R101" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>14</v>
       </c>
@@ -7121,8 +9278,20 @@
       <c r="N102">
         <v>106.8355559</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" t="s">
+        <v>851</v>
+      </c>
+      <c r="P102" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q102" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R102" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>14</v>
       </c>
@@ -7165,8 +9334,20 @@
       <c r="N103">
         <v>106.904841</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" t="s">
+        <v>852</v>
+      </c>
+      <c r="P103" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q103" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R103" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>14</v>
       </c>
@@ -7209,8 +9390,20 @@
       <c r="N104">
         <v>106.904841</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" t="s">
+        <v>853</v>
+      </c>
+      <c r="P104" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q104" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R104" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>14</v>
       </c>
@@ -7253,8 +9446,20 @@
       <c r="N105">
         <v>106.904841</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" t="s">
+        <v>854</v>
+      </c>
+      <c r="P105" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q105" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R105" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>14</v>
       </c>
@@ -7297,8 +9502,20 @@
       <c r="N106">
         <v>106.904841</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" t="s">
+        <v>855</v>
+      </c>
+      <c r="P106" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q106" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R106" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>14</v>
       </c>
@@ -7341,8 +9558,20 @@
       <c r="N107">
         <v>106.708834</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" t="s">
+        <v>856</v>
+      </c>
+      <c r="P107" s="4">
+        <v>1899515</v>
+      </c>
+      <c r="Q107" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R107" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>14</v>
       </c>
@@ -7385,8 +9614,20 @@
       <c r="N108">
         <v>106.8300413</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" t="s">
+        <v>857</v>
+      </c>
+      <c r="P108" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q108" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R108" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>14</v>
       </c>
@@ -7429,8 +9670,20 @@
       <c r="N109">
         <v>106.7777897</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" t="s">
+        <v>858</v>
+      </c>
+      <c r="P109" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q109" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R109" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>14</v>
       </c>
@@ -7473,8 +9726,20 @@
       <c r="N110">
         <v>106.82175340000001</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" t="s">
+        <v>859</v>
+      </c>
+      <c r="P110" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q110" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R110" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>14</v>
       </c>
@@ -7517,8 +9782,20 @@
       <c r="N111">
         <v>106.8180323</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" t="s">
+        <v>860</v>
+      </c>
+      <c r="P111" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q111" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R111" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>14</v>
       </c>
@@ -7561,8 +9838,20 @@
       <c r="N112">
         <v>106.82261750000001</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" t="s">
+        <v>861</v>
+      </c>
+      <c r="P112" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q112" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R112" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>14</v>
       </c>
@@ -7605,8 +9894,20 @@
       <c r="N113">
         <v>106.79639589999999</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" t="s">
+        <v>862</v>
+      </c>
+      <c r="P113" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q113" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R113" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -7649,8 +9950,20 @@
       <c r="N114">
         <v>106.64505800000001</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" t="s">
+        <v>863</v>
+      </c>
+      <c r="P114" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q114" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R114" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>14</v>
       </c>
@@ -7693,8 +10006,20 @@
       <c r="N115">
         <v>106.64505800000001</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O115" t="s">
+        <v>864</v>
+      </c>
+      <c r="P115" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q115" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R115" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>14</v>
       </c>
@@ -7737,8 +10062,20 @@
       <c r="N116">
         <v>106.838787</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" t="s">
+        <v>865</v>
+      </c>
+      <c r="P116" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q116" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R116" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>14</v>
       </c>
@@ -7781,8 +10118,20 @@
       <c r="N117">
         <v>106.753204</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" t="s">
+        <v>866</v>
+      </c>
+      <c r="P117" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q117" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R117" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>14</v>
       </c>
@@ -7825,8 +10174,20 @@
       <c r="N118">
         <v>106.77590120000001</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O118" t="s">
+        <v>867</v>
+      </c>
+      <c r="P118" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q118" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R118" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>14</v>
       </c>
@@ -7869,8 +10230,20 @@
       <c r="N119">
         <v>106.819005</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" t="s">
+        <v>868</v>
+      </c>
+      <c r="P119" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q119" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R119" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>14</v>
       </c>
@@ -7913,8 +10286,20 @@
       <c r="N120">
         <v>106.64029650000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" t="s">
+        <v>869</v>
+      </c>
+      <c r="P120" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q120" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R120" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>14</v>
       </c>
@@ -7957,8 +10342,20 @@
       <c r="N121">
         <v>106.593571</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" t="s">
+        <v>870</v>
+      </c>
+      <c r="P121" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q121" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R121" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>14</v>
       </c>
@@ -8001,8 +10398,20 @@
       <c r="N122">
         <v>106.7829603</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" t="s">
+        <v>871</v>
+      </c>
+      <c r="P122" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q122" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R122" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>14</v>
       </c>
@@ -8045,8 +10454,20 @@
       <c r="N123">
         <v>106.7829603</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" t="s">
+        <v>872</v>
+      </c>
+      <c r="P123" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q123" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R123" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>14</v>
       </c>
@@ -8089,8 +10510,20 @@
       <c r="N124">
         <v>106.8145528</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" t="s">
+        <v>873</v>
+      </c>
+      <c r="P124" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q124" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R124" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>14</v>
       </c>
@@ -8133,8 +10566,20 @@
       <c r="N125">
         <v>106.74662720000001</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" t="s">
+        <v>874</v>
+      </c>
+      <c r="P125" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q125" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R125" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>14</v>
       </c>
@@ -8177,8 +10622,20 @@
       <c r="N126">
         <v>106.8223536</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" t="s">
+        <v>875</v>
+      </c>
+      <c r="P126" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q126" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R126" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>14</v>
       </c>
@@ -8221,8 +10678,20 @@
       <c r="N127">
         <v>106.8223536</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" t="s">
+        <v>876</v>
+      </c>
+      <c r="P127" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q127" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R127" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>14</v>
       </c>
@@ -8265,8 +10734,20 @@
       <c r="N128">
         <v>106.89971199999999</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" t="s">
+        <v>877</v>
+      </c>
+      <c r="P128" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q128" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R128" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>14</v>
       </c>
@@ -8309,8 +10790,20 @@
       <c r="N129">
         <v>106.89971199999999</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O129" t="s">
+        <v>878</v>
+      </c>
+      <c r="P129" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q129" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R129" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>14</v>
       </c>
@@ -8353,8 +10846,20 @@
       <c r="N130">
         <v>106.813289</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" t="s">
+        <v>879</v>
+      </c>
+      <c r="P130" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q130" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R130" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>14</v>
       </c>
@@ -8397,8 +10902,20 @@
       <c r="N131">
         <v>106.164677</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" t="s">
+        <v>880</v>
+      </c>
+      <c r="P131" s="4">
+        <v>730530</v>
+      </c>
+      <c r="Q131" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R131" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>14</v>
       </c>
@@ -8441,8 +10958,20 @@
       <c r="N132">
         <v>106.7568754</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" t="s">
+        <v>881</v>
+      </c>
+      <c r="P132" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q132" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R132" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>14</v>
       </c>
@@ -8485,8 +11014,20 @@
       <c r="N133">
         <v>106.7604133</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" t="s">
+        <v>882</v>
+      </c>
+      <c r="P133" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q133" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R133" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>14</v>
       </c>
@@ -8529,8 +11070,20 @@
       <c r="N134">
         <v>106.0537688</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" t="s">
+        <v>883</v>
+      </c>
+      <c r="P134" s="4">
+        <v>464716</v>
+      </c>
+      <c r="Q134" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R134" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>14</v>
       </c>
@@ -8573,8 +11126,20 @@
       <c r="N135">
         <v>106.0537688</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" t="s">
+        <v>884</v>
+      </c>
+      <c r="P135" s="4">
+        <v>464716</v>
+      </c>
+      <c r="Q135" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R135" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>14</v>
       </c>
@@ -8617,8 +11182,20 @@
       <c r="N136">
         <v>106.04861</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" t="s">
+        <v>885</v>
+      </c>
+      <c r="P136" s="4">
+        <v>464716</v>
+      </c>
+      <c r="Q136" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R136" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>14</v>
       </c>
@@ -8661,8 +11238,20 @@
       <c r="N137">
         <v>105.25821569999999</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" t="s">
+        <v>886</v>
+      </c>
+      <c r="P137" s="4">
+        <v>1096935</v>
+      </c>
+      <c r="Q137" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R137" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>14</v>
       </c>
@@ -8705,8 +11294,20 @@
       <c r="N138">
         <v>105.258031</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" t="s">
+        <v>887</v>
+      </c>
+      <c r="P138" s="4">
+        <v>411280</v>
+      </c>
+      <c r="Q138" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R138" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>14</v>
       </c>
@@ -8749,8 +11350,20 @@
       <c r="N139">
         <v>119.50704930000001</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" t="s">
+        <v>888</v>
+      </c>
+      <c r="P139" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q139" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R139" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>14</v>
       </c>
@@ -8793,8 +11406,20 @@
       <c r="N140">
         <v>119.40956370000001</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" t="s">
+        <v>889</v>
+      </c>
+      <c r="P140" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q140" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R140" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>14</v>
       </c>
@@ -8837,8 +11462,20 @@
       <c r="N141">
         <v>136.83976419999999</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" t="s">
+        <v>890</v>
+      </c>
+      <c r="P141" s="4">
+        <v>313016</v>
+      </c>
+      <c r="Q141" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R141" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>14</v>
       </c>
@@ -8881,8 +11518,20 @@
       <c r="N142">
         <v>122.5135677</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" t="s">
+        <v>891</v>
+      </c>
+      <c r="P142" s="4">
+        <v>347380</v>
+      </c>
+      <c r="Q142" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R142" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>14</v>
       </c>
@@ -8925,8 +11574,20 @@
       <c r="N143">
         <v>114.7842497</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" t="s">
+        <v>892</v>
+      </c>
+      <c r="P143" s="4">
+        <v>360966</v>
+      </c>
+      <c r="Q143" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R143" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>14</v>
       </c>
@@ -8969,8 +11630,20 @@
       <c r="N144">
         <v>102.2623797</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" t="s">
+        <v>893</v>
+      </c>
+      <c r="P144" s="4">
+        <v>385511</v>
+      </c>
+      <c r="Q144" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R144" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -9013,8 +11686,20 @@
       <c r="N145">
         <v>128.22067999999999</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" t="s">
+        <v>894</v>
+      </c>
+      <c r="P145" s="4">
+        <v>354052</v>
+      </c>
+      <c r="Q145" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R145" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>14</v>
       </c>
@@ -9057,8 +11742,20 @@
       <c r="N146">
         <v>128.24610999999999</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" t="s">
+        <v>895</v>
+      </c>
+      <c r="P146" s="4">
+        <v>354052</v>
+      </c>
+      <c r="Q146" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R146" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>14</v>
       </c>
@@ -9101,8 +11798,20 @@
       <c r="N147">
         <v>104.261447</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" t="s">
+        <v>896</v>
+      </c>
+      <c r="P147" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q147" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R147" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>14</v>
       </c>
@@ -9145,8 +11854,20 @@
       <c r="N148">
         <v>128.951334</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" t="s">
+        <v>897</v>
+      </c>
+      <c r="P148" s="4">
+        <v>429797</v>
+      </c>
+      <c r="Q148" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R148" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>14</v>
       </c>
@@ -9189,8 +11910,20 @@
       <c r="N149">
         <v>104.734354</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" t="s">
+        <v>898</v>
+      </c>
+      <c r="P149" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q149" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R149" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>14</v>
       </c>
@@ -9233,8 +11966,20 @@
       <c r="N150">
         <v>104.734354</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" t="s">
+        <v>899</v>
+      </c>
+      <c r="P150" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q150" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R150" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>14</v>
       </c>
@@ -9277,8 +12022,20 @@
       <c r="N151">
         <v>104.7483479</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" t="s">
+        <v>900</v>
+      </c>
+      <c r="P151" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q151" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R151" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>14</v>
       </c>
@@ -9321,8 +12078,20 @@
       <c r="N152">
         <v>140.70373889999999</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" t="s">
+        <v>901</v>
+      </c>
+      <c r="P152" s="4">
+        <v>403861</v>
+      </c>
+      <c r="Q152" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R152" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>14</v>
       </c>
@@ -9365,8 +12134,20 @@
       <c r="N153">
         <v>140.70373889999999</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" t="s">
+        <v>902</v>
+      </c>
+      <c r="P153" s="4">
+        <v>403861</v>
+      </c>
+      <c r="Q153" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R153" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>14</v>
       </c>
@@ -9409,8 +12190,20 @@
       <c r="N154">
         <v>115.24462440000001</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" t="s">
+        <v>903</v>
+      </c>
+      <c r="P154" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q154" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R154" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>14</v>
       </c>
@@ -9453,8 +12246,20 @@
       <c r="N155">
         <v>106.11183800000001</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" t="s">
+        <v>904</v>
+      </c>
+      <c r="P155" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q155" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R155" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>14</v>
       </c>
@@ -9497,8 +12302,20 @@
       <c r="N156">
         <v>106.11972</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" t="s">
+        <v>905</v>
+      </c>
+      <c r="P156" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q156" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R156" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>14</v>
       </c>
@@ -9541,8 +12358,20 @@
       <c r="N157">
         <v>106.1463724</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" t="s">
+        <v>906</v>
+      </c>
+      <c r="P157" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q157" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R157" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>14</v>
       </c>
@@ -9585,8 +12414,20 @@
       <c r="N158">
         <v>106.138741</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" t="s">
+        <v>907</v>
+      </c>
+      <c r="P158" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q158" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R158" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>14</v>
       </c>
@@ -9629,8 +12470,20 @@
       <c r="N159">
         <v>116.1993677</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" t="s">
+        <v>908</v>
+      </c>
+      <c r="P159" s="4">
+        <v>298996</v>
+      </c>
+      <c r="Q159" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R159" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>14</v>
       </c>
@@ -9673,8 +12526,20 @@
       <c r="N160">
         <v>116.198714</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" t="s">
+        <v>909</v>
+      </c>
+      <c r="P160" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q160" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R160" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>14</v>
       </c>
@@ -9717,8 +12582,20 @@
       <c r="N161">
         <v>103.6017514</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" t="s">
+        <v>910</v>
+      </c>
+      <c r="P161" s="4">
+        <v>403861</v>
+      </c>
+      <c r="Q161" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R161" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>14</v>
       </c>
@@ -9761,8 +12638,20 @@
       <c r="N162">
         <v>103.61540100000001</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" t="s">
+        <v>911</v>
+      </c>
+      <c r="P162" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q162" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R162" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>14</v>
       </c>
@@ -9805,8 +12694,20 @@
       <c r="N163">
         <v>116.41994</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" t="s">
+        <v>912</v>
+      </c>
+      <c r="P163" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q163" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R163" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>14</v>
       </c>
@@ -9849,8 +12750,20 @@
       <c r="N164">
         <v>116.8552771</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" t="s">
+        <v>913</v>
+      </c>
+      <c r="P164" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q164" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R164" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>14</v>
       </c>
@@ -9893,8 +12806,20 @@
       <c r="N165">
         <v>116.8577604</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" t="s">
+        <v>914</v>
+      </c>
+      <c r="P165" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q165" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R165" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>14</v>
       </c>
@@ -9937,8 +12862,20 @@
       <c r="N166">
         <v>116.846166</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" t="s">
+        <v>915</v>
+      </c>
+      <c r="P166" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q166" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R166" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>14</v>
       </c>
@@ -9981,8 +12918,20 @@
       <c r="N167">
         <v>116.81581920000001</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" t="s">
+        <v>916</v>
+      </c>
+      <c r="P167" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q167" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R167" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>14</v>
       </c>
@@ -10025,8 +12974,20 @@
       <c r="N168">
         <v>116.8409571</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" t="s">
+        <v>917</v>
+      </c>
+      <c r="P168" s="4">
+        <v>733397</v>
+      </c>
+      <c r="Q168" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R168" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>14</v>
       </c>
@@ -10069,8 +13030,20 @@
       <c r="N169">
         <v>116.849977</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" t="s">
+        <v>918</v>
+      </c>
+      <c r="P169" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q169" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R169" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>14</v>
       </c>
@@ -10113,8 +13086,20 @@
       <c r="N170">
         <v>101.97233199999999</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" t="s">
+        <v>919</v>
+      </c>
+      <c r="P170" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q170" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R170" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>14</v>
       </c>
@@ -10157,8 +13142,20 @@
       <c r="N171">
         <v>101.97233199999999</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" t="s">
+        <v>920</v>
+      </c>
+      <c r="P171" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q171" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R171" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>14</v>
       </c>
@@ -10201,8 +13198,20 @@
       <c r="N172">
         <v>101.97233199999999</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" t="s">
+        <v>921</v>
+      </c>
+      <c r="P172" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q172" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R172" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>14</v>
       </c>
@@ -10245,8 +13254,20 @@
       <c r="N173">
         <v>100.36126489999999</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" t="s">
+        <v>922</v>
+      </c>
+      <c r="P173" s="4">
+        <v>928539</v>
+      </c>
+      <c r="Q173" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R173" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>14</v>
       </c>
@@ -10289,8 +13310,20 @@
       <c r="N174">
         <v>131.3081554</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" t="s">
+        <v>923</v>
+      </c>
+      <c r="P174" s="4">
+        <v>283366</v>
+      </c>
+      <c r="Q174" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R174" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>14</v>
       </c>
@@ -10333,8 +13366,20 @@
       <c r="N175">
         <v>117.1139871</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" t="s">
+        <v>924</v>
+      </c>
+      <c r="P175" s="4">
+        <v>856361</v>
+      </c>
+      <c r="Q175" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R175" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>14</v>
       </c>
@@ -10377,8 +13422,20 @@
       <c r="N176">
         <v>100.382971</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" t="s">
+        <v>925</v>
+      </c>
+      <c r="P176" s="4">
+        <v>257315</v>
+      </c>
+      <c r="Q176" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R176" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>14</v>
       </c>
@@ -10421,8 +13478,20 @@
       <c r="N177">
         <v>100.1546</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" t="s">
+        <v>926</v>
+      </c>
+      <c r="P177" s="4">
+        <v>1761461</v>
+      </c>
+      <c r="Q177" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R177" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>14</v>
       </c>
@@ -10465,8 +13534,20 @@
       <c r="N178">
         <v>117.463376</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" t="s">
+        <v>927</v>
+      </c>
+      <c r="P178" s="4">
+        <v>187446</v>
+      </c>
+      <c r="Q178" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R178" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>14</v>
       </c>
@@ -10509,8 +13590,20 @@
       <c r="N179">
         <v>101.37624839999999</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" t="s">
+        <v>928</v>
+      </c>
+      <c r="P179" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q179" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R179" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>14</v>
       </c>
@@ -10553,8 +13646,20 @@
       <c r="N180">
         <v>101.42177649999999</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" t="s">
+        <v>929</v>
+      </c>
+      <c r="P180" s="4">
+        <v>205288</v>
+      </c>
+      <c r="Q180" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R180" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>14</v>
       </c>
@@ -10597,8 +13702,20 @@
       <c r="N181">
         <v>101.43940600000001</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" t="s">
+        <v>930</v>
+      </c>
+      <c r="P181" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q181" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R181" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>14</v>
       </c>
@@ -10641,8 +13758,20 @@
       <c r="N182">
         <v>101.43194</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" t="s">
+        <v>931</v>
+      </c>
+      <c r="P182" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q182" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R182" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>14</v>
       </c>
@@ -10685,8 +13814,20 @@
       <c r="N183">
         <v>104.4900001</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" t="s">
+        <v>932</v>
+      </c>
+      <c r="P183" s="4">
+        <v>233406</v>
+      </c>
+      <c r="Q183" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R183" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>14</v>
       </c>
@@ -10729,8 +13870,20 @@
       <c r="N184">
         <v>104.44508</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" t="s">
+        <v>933</v>
+      </c>
+      <c r="P184" s="4">
+        <v>135489</v>
+      </c>
+      <c r="Q184" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R184" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>14</v>
       </c>
@@ -10773,8 +13926,20 @@
       <c r="N185">
         <v>104.4823208</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" t="s">
+        <v>934</v>
+      </c>
+      <c r="P185" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q185" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R185" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>14</v>
       </c>
@@ -10817,8 +13982,20 @@
       <c r="N186">
         <v>102.9842</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" t="s">
+        <v>935</v>
+      </c>
+      <c r="P186" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q186" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R186" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>14</v>
       </c>
@@ -10861,8 +14038,20 @@
       <c r="N187">
         <v>103.988912</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" t="s">
+        <v>936</v>
+      </c>
+      <c r="P187" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q187" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R187" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>14</v>
       </c>
@@ -10905,8 +14094,20 @@
       <c r="N188">
         <v>103.988912</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O188" t="s">
+        <v>937</v>
+      </c>
+      <c r="P188" s="4">
+        <v>928539</v>
+      </c>
+      <c r="Q188" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R188" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>14</v>
       </c>
@@ -10949,8 +14150,20 @@
       <c r="N189">
         <v>104.0574111</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O189" t="s">
+        <v>938</v>
+      </c>
+      <c r="P189" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q189" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R189" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>14</v>
       </c>
@@ -10993,8 +14206,20 @@
       <c r="N190">
         <v>104.0574111</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O190" t="s">
+        <v>939</v>
+      </c>
+      <c r="P190" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q190" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R190" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>14</v>
       </c>
@@ -11037,8 +14262,20 @@
       <c r="N191">
         <v>104.0574111</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O191" t="s">
+        <v>940</v>
+      </c>
+      <c r="P191" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q191" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R191" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>14</v>
       </c>
@@ -11081,8 +14318,20 @@
       <c r="N192">
         <v>104.0574111</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O192" t="s">
+        <v>941</v>
+      </c>
+      <c r="P192" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q192" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R192" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>14</v>
       </c>
@@ -11125,8 +14374,20 @@
       <c r="N193">
         <v>104.01670679999999</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O193" t="s">
+        <v>942</v>
+      </c>
+      <c r="P193" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q193" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R193" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>14</v>
       </c>
@@ -11169,8 +14430,20 @@
       <c r="N194">
         <v>104.11216899999999</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O194" t="s">
+        <v>943</v>
+      </c>
+      <c r="P194" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q194" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R194" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>14</v>
       </c>
@@ -11213,8 +14486,20 @@
       <c r="N195">
         <v>104.008849</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O195" t="s">
+        <v>944</v>
+      </c>
+      <c r="P195" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q195" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R195" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>14</v>
       </c>
@@ -11257,8 +14542,20 @@
       <c r="N196">
         <v>104.0255715</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O196" t="s">
+        <v>945</v>
+      </c>
+      <c r="P196" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q196" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R196" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>14</v>
       </c>
@@ -11301,8 +14598,20 @@
       <c r="N197">
         <v>124.8386173</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O197" t="s">
+        <v>946</v>
+      </c>
+      <c r="P197" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q197" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R197" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>14</v>
       </c>
@@ -11345,8 +14654,20 @@
       <c r="N198">
         <v>124.8977675</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O198" t="s">
+        <v>947</v>
+      </c>
+      <c r="P198" s="4">
+        <v>478194</v>
+      </c>
+      <c r="Q198" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R198" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>14</v>
       </c>
@@ -11389,8 +14710,20 @@
       <c r="N199">
         <v>100.41246339999999</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O199" t="s">
+        <v>948</v>
+      </c>
+      <c r="P199" s="4">
+        <v>186957</v>
+      </c>
+      <c r="Q199" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R199" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>14</v>
       </c>
@@ -11433,8 +14766,20 @@
       <c r="N200">
         <v>101.40616970000001</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O200" t="s">
+        <v>949</v>
+      </c>
+      <c r="P200" s="4">
+        <v>651834</v>
+      </c>
+      <c r="Q200" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R200" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>14</v>
       </c>
@@ -11477,8 +14822,20 @@
       <c r="N201">
         <v>99.90401</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O201" t="s">
+        <v>950</v>
+      </c>
+      <c r="P201" s="4">
+        <v>1116142</v>
+      </c>
+      <c r="Q201" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R201" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>14</v>
       </c>
@@ -11521,8 +14878,20 @@
       <c r="N202">
         <v>99.629170000000002</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O202" t="s">
+        <v>951</v>
+      </c>
+      <c r="P202" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q202" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R202" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>14</v>
       </c>
@@ -11565,8 +14934,20 @@
       <c r="N203" s="1">
         <v>99.165592000000004</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O203" t="s">
+        <v>952</v>
+      </c>
+      <c r="P203" s="4">
+        <v>229408</v>
+      </c>
+      <c r="Q203" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R203" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>14</v>
       </c>
@@ -11609,8 +14990,20 @@
       <c r="N204">
         <v>97.812486000000007</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O204" t="s">
+        <v>953</v>
+      </c>
+      <c r="P204" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q204" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R204" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>14</v>
       </c>
@@ -11653,8 +15046,20 @@
       <c r="N205">
         <v>98.711819000000006</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O205" t="s">
+        <v>954</v>
+      </c>
+      <c r="P205" s="4">
+        <v>178524</v>
+      </c>
+      <c r="Q205" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R205" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>14</v>
       </c>
@@ -11697,8 +15102,20 @@
       <c r="N206">
         <v>98.711819000000006</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O206" t="s">
+        <v>955</v>
+      </c>
+      <c r="P206" s="4">
+        <v>338064</v>
+      </c>
+      <c r="Q206" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R206" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>14</v>
       </c>
@@ -11741,8 +15158,20 @@
       <c r="N207">
         <v>98.673415000000006</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O207" t="s">
+        <v>956</v>
+      </c>
+      <c r="P207" s="4">
+        <v>792179</v>
+      </c>
+      <c r="Q207" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R207" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>14</v>
       </c>
@@ -11785,8 +15214,20 @@
       <c r="N208">
         <v>98.626040900000007</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O208" t="s">
+        <v>957</v>
+      </c>
+      <c r="P208" s="4">
+        <v>2016906</v>
+      </c>
+      <c r="Q208" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R208" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>14</v>
       </c>
@@ -11829,8 +15270,20 @@
       <c r="N209">
         <v>98.695500999999993</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O209" t="s">
+        <v>958</v>
+      </c>
+      <c r="P209" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q209" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R209" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>14</v>
       </c>
@@ -11873,8 +15326,20 @@
       <c r="N210">
         <v>98.672223900000006</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O210" t="s">
+        <v>959</v>
+      </c>
+      <c r="P210" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q210" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R210" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>14</v>
       </c>
@@ -11917,8 +15382,20 @@
       <c r="N211">
         <v>98.667000000000002</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O211" t="s">
+        <v>960</v>
+      </c>
+      <c r="P211" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q211" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R211" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>14</v>
       </c>
@@ -11961,8 +15438,20 @@
       <c r="N212">
         <v>98.654787799999994</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O212" t="s">
+        <v>961</v>
+      </c>
+      <c r="P212" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q212" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R212" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>14</v>
       </c>
@@ -12005,8 +15494,20 @@
       <c r="N213">
         <v>98.689914000000002</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O213" t="s">
+        <v>962</v>
+      </c>
+      <c r="P213" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q213" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R213" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>14</v>
       </c>
@@ -12049,8 +15550,20 @@
       <c r="N214">
         <v>96.710869000000002</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O214" t="s">
+        <v>963</v>
+      </c>
+      <c r="P214" s="4">
+        <v>455555</v>
+      </c>
+      <c r="Q214" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R214" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>14</v>
       </c>
@@ -12093,8 +15606,20 @@
       <c r="N215">
         <v>97.955706800000002</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O215" t="s">
+        <v>964</v>
+      </c>
+      <c r="P215" s="4">
+        <v>193950</v>
+      </c>
+      <c r="Q215" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R215" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>14</v>
       </c>
@@ -12137,8 +15662,20 @@
       <c r="N216">
         <v>97.138561800000005</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O216" t="s">
+        <v>965</v>
+      </c>
+      <c r="P216" s="4">
+        <v>201720</v>
+      </c>
+      <c r="Q216" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R216" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -12181,8 +15718,20 @@
       <c r="N217">
         <v>96.721269000000007</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O217" t="s">
+        <v>966</v>
+      </c>
+      <c r="P217" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q217" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R217" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>14</v>
       </c>
@@ -12225,8 +15774,20 @@
       <c r="N218">
         <v>95.321732699999998</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O218" t="s">
+        <v>967</v>
+      </c>
+      <c r="P218" s="4">
+        <v>2016906</v>
+      </c>
+      <c r="Q218" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R218" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>14</v>
       </c>
@@ -12269,8 +15830,20 @@
       <c r="N219" s="1">
         <v>104.00298100000001</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O219" t="s">
+        <v>968</v>
+      </c>
+      <c r="P219" s="4">
+        <v>233406</v>
+      </c>
+      <c r="Q219" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R219" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>14</v>
       </c>
@@ -12313,8 +15886,20 @@
       <c r="N220">
         <v>107.63120600000001</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O220" t="s">
+        <v>969</v>
+      </c>
+      <c r="P220" s="4">
+        <v>187038</v>
+      </c>
+      <c r="Q220" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R220" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>14</v>
       </c>
@@ -12357,8 +15942,20 @@
       <c r="N221" s="1">
         <v>106.815133</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O221" t="s">
+        <v>970</v>
+      </c>
+      <c r="P221" s="4">
+        <v>232915</v>
+      </c>
+      <c r="Q221" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R221" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>14</v>
       </c>
@@ -12401,8 +15998,20 @@
       <c r="N222" s="1">
         <v>106.923833</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O222" t="s">
+        <v>971</v>
+      </c>
+      <c r="P222" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q222" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R222" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>14</v>
       </c>
@@ -12445,8 +16054,20 @@
       <c r="N223" s="1">
         <v>106.73066799999999</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O223" t="s">
+        <v>972</v>
+      </c>
+      <c r="P223" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q223" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R223" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>14</v>
       </c>
@@ -12489,8 +16110,20 @@
       <c r="N224" s="1">
         <v>109.341559</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O224" t="s">
+        <v>973</v>
+      </c>
+      <c r="P224" s="4">
+        <v>676096</v>
+      </c>
+      <c r="Q224" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R224" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>14</v>
       </c>
@@ -12533,8 +16166,20 @@
       <c r="N225" s="1">
         <v>104.057447</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O225" t="s">
+        <v>974</v>
+      </c>
+      <c r="P225" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q225" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R225" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>14</v>
       </c>
@@ -12577,8 +16222,20 @@
       <c r="N226" s="1">
         <v>107.021265</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O226" t="s">
+        <v>975</v>
+      </c>
+      <c r="P226" s="4">
+        <v>2496198</v>
+      </c>
+      <c r="Q226" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R226" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>14</v>
       </c>
@@ -12621,8 +16278,20 @@
       <c r="N227" s="1">
         <v>106.90712499999999</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O227" t="s">
+        <v>976</v>
+      </c>
+      <c r="P227" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q227" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R227" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -12665,8 +16334,20 @@
       <c r="N228" s="1">
         <v>119.403639</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O228" t="s">
+        <v>977</v>
+      </c>
+      <c r="P228" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q228" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R228" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -12709,8 +16390,20 @@
       <c r="N229" s="1">
         <v>122.61952599999999</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O229" t="s">
+        <v>978</v>
+      </c>
+      <c r="P229" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q229" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R229" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -12753,8 +16446,20 @@
       <c r="N230">
         <v>110361913</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O230" t="s">
+        <v>979</v>
+      </c>
+      <c r="P230" s="4">
+        <v>1105415</v>
+      </c>
+      <c r="Q230" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R230" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>14</v>
       </c>
@@ -12797,8 +16502,20 @@
       <c r="N231">
         <v>1103695145</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O231" t="s">
+        <v>980</v>
+      </c>
+      <c r="P231" s="4">
+        <v>413784</v>
+      </c>
+      <c r="Q231" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R231" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -12841,8 +16558,20 @@
       <c r="N232">
         <v>1082607</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O232" t="s">
+        <v>981</v>
+      </c>
+      <c r="P232" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q232" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R232" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>14</v>
       </c>
@@ -12885,8 +16614,20 @@
       <c r="N233">
         <v>107605909</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O233" t="s">
+        <v>982</v>
+      </c>
+      <c r="P233" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q233" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R233" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>14</v>
       </c>
@@ -12929,8 +16670,20 @@
       <c r="N234">
         <v>-739202098</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O234" t="s">
+        <v>983</v>
+      </c>
+      <c r="P234" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q234" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R234" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>14</v>
       </c>
@@ -12973,8 +16726,20 @@
       <c r="N235">
         <v>107634087</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O235" t="s">
+        <v>984</v>
+      </c>
+      <c r="P235" s="4">
+        <v>2555187</v>
+      </c>
+      <c r="Q235" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R235" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>14</v>
       </c>
@@ -13017,8 +16782,20 @@
       <c r="N236">
         <v>1069311496</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O236" t="s">
+        <v>985</v>
+      </c>
+      <c r="P236" s="4">
+        <v>361581</v>
+      </c>
+      <c r="Q236" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R236" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>14</v>
       </c>
@@ -13061,8 +16838,20 @@
       <c r="N237">
         <v>1079215538</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O237" t="s">
+        <v>986</v>
+      </c>
+      <c r="P237" s="4">
+        <v>2770531</v>
+      </c>
+      <c r="Q237" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R237" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>14</v>
       </c>
@@ -13105,8 +16894,20 @@
       <c r="N238">
         <v>1120110772</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O238" t="s">
+        <v>987</v>
+      </c>
+      <c r="P238" s="4">
+        <v>296792</v>
+      </c>
+      <c r="Q238" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R238" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -13149,8 +16950,20 @@
       <c r="N239">
         <v>-79814668</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O239" t="s">
+        <v>988</v>
+      </c>
+      <c r="P239" s="4">
+        <v>201992</v>
+      </c>
+      <c r="Q239" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R239" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>14</v>
       </c>
@@ -13193,8 +17006,20 @@
       <c r="N240">
         <v>11435443</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O240" t="s">
+        <v>989</v>
+      </c>
+      <c r="P240" s="4">
+        <v>1769233</v>
+      </c>
+      <c r="Q240" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R240" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>14</v>
       </c>
@@ -13237,8 +17062,20 @@
       <c r="N241">
         <v>1127334286</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O241" t="s">
+        <v>990</v>
+      </c>
+      <c r="P241" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q241" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R241" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>14</v>
       </c>
@@ -13281,8 +17118,20 @@
       <c r="N242">
         <v>1127158127</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O242" t="s">
+        <v>991</v>
+      </c>
+      <c r="P242" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q242" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R242" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>14</v>
       </c>
@@ -13325,8 +17174,20 @@
       <c r="N243">
         <v>1127138355</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O243" t="s">
+        <v>992</v>
+      </c>
+      <c r="P243" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q243" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R243" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>14</v>
       </c>
@@ -13369,8 +17230,20 @@
       <c r="N244">
         <v>-799557</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O244" t="s">
+        <v>993</v>
+      </c>
+      <c r="P244" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q244" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R244" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>14</v>
       </c>
@@ -13413,8 +17286,20 @@
       <c r="N245">
         <v>1236131673</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O245" t="s">
+        <v>994</v>
+      </c>
+      <c r="P245" s="4">
+        <v>443349</v>
+      </c>
+      <c r="Q245" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R245" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -13457,8 +17342,20 @@
       <c r="N246">
         <v>116105985</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O246" t="s">
+        <v>995</v>
+      </c>
+      <c r="P246" s="4">
+        <v>452812</v>
+      </c>
+      <c r="Q246" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R246" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>14</v>
       </c>
@@ -13501,8 +17398,20 @@
       <c r="N247">
         <v>-121349241</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O247" t="s">
+        <v>996</v>
+      </c>
+      <c r="P247" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q247" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R247" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>14</v>
       </c>
@@ -13545,8 +17454,20 @@
       <c r="N248">
         <v>113714021</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O248" t="s">
+        <v>997</v>
+      </c>
+      <c r="P248" s="4">
+        <v>2590289</v>
+      </c>
+      <c r="Q248" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R248" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>14</v>
       </c>
@@ -13589,8 +17510,20 @@
       <c r="N249">
         <v>106868238</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O249" t="s">
+        <v>998</v>
+      </c>
+      <c r="P249" s="4">
+        <v>219540</v>
+      </c>
+      <c r="Q249" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R249" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>14</v>
       </c>
@@ -13633,8 +17566,20 @@
       <c r="N250">
         <v>1126826568</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O250" t="s">
+        <v>999</v>
+      </c>
+      <c r="P250" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="Q250" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R250" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -13677,8 +17622,20 @@
       <c r="N251">
         <v>1126116906</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O251" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P251" s="4">
+        <v>874660</v>
+      </c>
+      <c r="Q251" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R251" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>14</v>
       </c>
@@ -13721,8 +17678,20 @@
       <c r="N252">
         <v>728491409</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O252" t="s">
+        <v>1001</v>
+      </c>
+      <c r="P252" s="4">
+        <v>403861</v>
+      </c>
+      <c r="Q252" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R252" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>14</v>
       </c>
@@ -13765,8 +17734,20 @@
       <c r="N253">
         <v>112719072</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O253" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P253" s="4">
+        <v>201992</v>
+      </c>
+      <c r="Q253" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R253" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>14</v>
       </c>
@@ -13809,8 +17790,20 @@
       <c r="N254">
         <v>112711765</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O254" t="s">
+        <v>1003</v>
+      </c>
+      <c r="P254" s="4">
+        <v>1982939</v>
+      </c>
+      <c r="Q254" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R254" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>14</v>
       </c>
@@ -13853,8 +17846,20 @@
       <c r="N255">
         <v>107146471</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O255" t="s">
+        <v>1004</v>
+      </c>
+      <c r="P255" s="4">
+        <v>3172831</v>
+      </c>
+      <c r="Q255" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R255" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>14</v>
       </c>
@@ -13897,8 +17902,20 @@
       <c r="N256">
         <v>1069463243</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O256" t="s">
+        <v>1005</v>
+      </c>
+      <c r="P256" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q256" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R256" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>14</v>
       </c>
@@ -13941,8 +17958,20 @@
       <c r="N257">
         <v>1068626468</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O257" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P257" s="4">
+        <v>5495373</v>
+      </c>
+      <c r="Q257" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R257" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>14</v>
       </c>
@@ -13985,8 +18014,20 @@
       <c r="N258">
         <v>1068204918</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O258" t="s">
+        <v>1007</v>
+      </c>
+      <c r="P258" s="4">
+        <v>1109489</v>
+      </c>
+      <c r="Q258" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R258" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>14</v>
       </c>
@@ -14029,8 +18070,20 @@
       <c r="N259">
         <v>10828306</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O259" t="s">
+        <v>1008</v>
+      </c>
+      <c r="P259" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q259" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R259" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>14</v>
       </c>
@@ -14073,8 +18126,20 @@
       <c r="N260">
         <v>1067930421</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O260" t="s">
+        <v>1009</v>
+      </c>
+      <c r="P260" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q260" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R260" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>14</v>
       </c>
@@ -14117,8 +18182,20 @@
       <c r="N261">
         <v>1068431333</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O261" t="s">
+        <v>1010</v>
+      </c>
+      <c r="P261" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q261" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R261" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>14</v>
       </c>
@@ -14161,8 +18238,20 @@
       <c r="N262">
         <v>1068230563</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O262" t="s">
+        <v>1011</v>
+      </c>
+      <c r="P262" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q262" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R262" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>14</v>
       </c>
@@ -14205,8 +18294,20 @@
       <c r="N263">
         <v>1068252874</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O263" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P263" s="4">
+        <v>1927869</v>
+      </c>
+      <c r="Q263" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R263" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>14</v>
       </c>
@@ -14249,8 +18350,20 @@
       <c r="N264">
         <v>106958788</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O264" t="s">
+        <v>1013</v>
+      </c>
+      <c r="P264" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q264" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R264" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>14</v>
       </c>
@@ -14293,8 +18406,20 @@
       <c r="N265">
         <v>106862439</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O265" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P265" s="4">
+        <v>3310145</v>
+      </c>
+      <c r="Q265" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R265" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>14</v>
       </c>
@@ -14337,8 +18462,20 @@
       <c r="N266">
         <v>1068325395</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O266" t="s">
+        <v>1015</v>
+      </c>
+      <c r="P266" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q266" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R266" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>14</v>
       </c>
@@ -14381,8 +18518,20 @@
       <c r="N267">
         <v>106915924</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O267" t="s">
+        <v>1016</v>
+      </c>
+      <c r="P267" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q267" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R267" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>14</v>
       </c>
@@ -14425,8 +18574,20 @@
       <c r="N268">
         <v>1067782591</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O268" t="s">
+        <v>1017</v>
+      </c>
+      <c r="P268" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q268" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R268" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>14</v>
       </c>
@@ -14469,8 +18630,20 @@
       <c r="N269">
         <v>106824565</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O269" t="s">
+        <v>1018</v>
+      </c>
+      <c r="P269" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q269" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R269" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>14</v>
       </c>
@@ -14513,8 +18686,20 @@
       <c r="N270">
         <v>106822451</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O270" t="s">
+        <v>1019</v>
+      </c>
+      <c r="P270" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q270" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R270" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>14</v>
       </c>
@@ -14557,8 +18742,20 @@
       <c r="N271">
         <v>1069029813</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O271" t="s">
+        <v>1020</v>
+      </c>
+      <c r="P271" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q271" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R271" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>14</v>
       </c>
@@ -14601,8 +18798,20 @@
       <c r="N272">
         <v>1067912764</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O272" t="s">
+        <v>1021</v>
+      </c>
+      <c r="P272" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q272" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R272" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>14</v>
       </c>
@@ -14645,8 +18854,20 @@
       <c r="N273">
         <v>1068944386</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O273" t="s">
+        <v>1022</v>
+      </c>
+      <c r="P273" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q273" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R273" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>14</v>
       </c>
@@ -14689,8 +18910,20 @@
       <c r="N274">
         <v>106789693</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O274" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P274" s="4">
+        <v>1876057</v>
+      </c>
+      <c r="Q274" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R274" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>14</v>
       </c>
@@ -14733,8 +18966,20 @@
       <c r="N275">
         <v>116849977</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O275" t="s">
+        <v>1024</v>
+      </c>
+      <c r="P275" s="4">
+        <v>730530</v>
+      </c>
+      <c r="Q275" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R275" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>14</v>
       </c>
@@ -14777,8 +19022,20 @@
       <c r="N276">
         <v>10679686</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O276" t="s">
+        <v>1025</v>
+      </c>
+      <c r="P276" s="4">
+        <v>2408480</v>
+      </c>
+      <c r="Q276" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R276" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>14</v>
       </c>
@@ -14821,8 +19078,20 @@
       <c r="N277">
         <v>1067085737</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O277" t="s">
+        <v>1026</v>
+      </c>
+      <c r="P277" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q277" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R277" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>14</v>
       </c>
@@ -14865,8 +19134,20 @@
       <c r="N278">
         <v>106645058</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O278" t="s">
+        <v>1027</v>
+      </c>
+      <c r="P278" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q278" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R278" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>14</v>
       </c>
@@ -14909,8 +19190,20 @@
       <c r="N279">
         <v>106747101</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O279" t="s">
+        <v>1028</v>
+      </c>
+      <c r="P279" s="4">
+        <v>1404786</v>
+      </c>
+      <c r="Q279" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R279" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>14</v>
       </c>
@@ -14953,8 +19246,20 @@
       <c r="N280">
         <v>1066383567</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O280" t="s">
+        <v>1029</v>
+      </c>
+      <c r="P280" s="4">
+        <v>3286420</v>
+      </c>
+      <c r="Q280" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R280" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>14</v>
       </c>
@@ -14997,8 +19302,20 @@
       <c r="N281">
         <v>1067969889</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O281" t="s">
+        <v>1030</v>
+      </c>
+      <c r="P281" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q281" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R281" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>14</v>
       </c>
@@ -15041,8 +19358,20 @@
       <c r="N282">
         <v>1067922054</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O282" t="s">
+        <v>1031</v>
+      </c>
+      <c r="P282" s="4">
+        <v>2615945</v>
+      </c>
+      <c r="Q282" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R282" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>14</v>
       </c>
@@ -15085,8 +19414,20 @@
       <c r="N283">
         <v>-116898319</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O283" t="s">
+        <v>1032</v>
+      </c>
+      <c r="P283" s="4">
+        <v>129032</v>
+      </c>
+      <c r="Q283" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R283" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>14</v>
       </c>
@@ -15129,8 +19470,20 @@
       <c r="N284">
         <v>12739058</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O284" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P284" s="4">
+        <v>202871</v>
+      </c>
+      <c r="Q284" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R284" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>14</v>
       </c>
@@ -15173,8 +19526,20 @@
       <c r="N285">
         <v>1194131701</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O285" t="s">
+        <v>1034</v>
+      </c>
+      <c r="P285" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q285" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R285" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>14</v>
       </c>
@@ -15217,8 +19582,20 @@
       <c r="N286">
         <v>1194754949</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O286" t="s">
+        <v>1035</v>
+      </c>
+      <c r="P286" s="4">
+        <v>1470262</v>
+      </c>
+      <c r="Q286" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R286" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>14</v>
       </c>
@@ -15261,8 +19638,20 @@
       <c r="N287">
         <v>1036192594</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O287" t="s">
+        <v>1036</v>
+      </c>
+      <c r="P287" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q287" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R287" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>14</v>
       </c>
@@ -15305,8 +19694,20 @@
       <c r="N288">
         <v>1040104146</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O288" t="s">
+        <v>1037</v>
+      </c>
+      <c r="P288" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q288" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R288" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>14</v>
       </c>
@@ -15349,8 +19750,20 @@
       <c r="N289">
         <v>1040126334</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O289" t="s">
+        <v>1038</v>
+      </c>
+      <c r="P289" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q289" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R289" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>14</v>
       </c>
@@ -15393,8 +19806,20 @@
       <c r="N290">
         <v>104045481</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O290" t="s">
+        <v>1039</v>
+      </c>
+      <c r="P290" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q290" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R290" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>14</v>
       </c>
@@ -15437,8 +19862,20 @@
       <c r="N291">
         <v>103967872</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O291" t="s">
+        <v>1040</v>
+      </c>
+      <c r="P291" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q291" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R291" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>14</v>
       </c>
@@ -15481,8 +19918,20 @@
       <c r="N292">
         <v>104086049</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O292" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P292" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q292" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R292" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>14</v>
       </c>
@@ -15525,8 +19974,20 @@
       <c r="N293">
         <v>104056371</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O293" t="s">
+        <v>1042</v>
+      </c>
+      <c r="P293" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q293" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R293" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>14</v>
       </c>
@@ -15569,8 +20030,20 @@
       <c r="N294">
         <v>1040819873</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O294" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P294" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q294" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R294" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>14</v>
       </c>
@@ -15613,8 +20086,20 @@
       <c r="N295">
         <v>104056371</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O295" t="s">
+        <v>1044</v>
+      </c>
+      <c r="P295" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q295" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R295" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>14</v>
       </c>
@@ -15657,8 +20142,20 @@
       <c r="N296">
         <v>104097889</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O296" t="s">
+        <v>1045</v>
+      </c>
+      <c r="P296" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q296" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R296" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>14</v>
       </c>
@@ -15701,8 +20198,20 @@
       <c r="N297">
         <v>1039545036</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O297" t="s">
+        <v>1046</v>
+      </c>
+      <c r="P297" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q297" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R297" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>14</v>
       </c>
@@ -15745,8 +20254,20 @@
       <c r="N298">
         <v>1040185509</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O298" t="s">
+        <v>1047</v>
+      </c>
+      <c r="P298" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q298" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R298" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>14</v>
       </c>
@@ -15789,8 +20310,20 @@
       <c r="N299">
         <v>116849977</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O299" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P299" s="4">
+        <v>1240792</v>
+      </c>
+      <c r="Q299" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R299" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>14</v>
       </c>
@@ -15833,8 +20366,20 @@
       <c r="N300">
         <v>1036077806</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O300" t="s">
+        <v>1049</v>
+      </c>
+      <c r="P300" s="4">
+        <v>633649</v>
+      </c>
+      <c r="Q300" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R300" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>14</v>
       </c>
@@ -15877,8 +20422,20 @@
       <c r="N301">
         <v>9867648</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O301" t="s">
+        <v>1050</v>
+      </c>
+      <c r="P301" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q301" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="R301" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>14</v>
       </c>
@@ -15920,6 +20477,18 @@
       </c>
       <c r="N302">
         <v>9867648</v>
+      </c>
+      <c r="O302" t="s">
+        <v>1051</v>
+      </c>
+      <c r="P302" s="4">
+        <v>2530492</v>
+      </c>
+      <c r="Q302" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="R302" s="5" t="s">
+        <v>1053</v>
       </c>
     </row>
   </sheetData>

--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D3D338-51DC-4E50-B76F-BF3F798B2E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F87046E-7C2E-4557-81E0-3267A5039B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="1057">
   <si>
     <t>Store ID</t>
   </si>
@@ -3208,18 +3208,20 @@
   </si>
   <si>
     <t>150,000-240,000</t>
+  </si>
+  <si>
+    <t>KABUPATEN BANYUMAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -3257,14 +3259,14 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
@@ -3573,10 +3575,23 @@
   <dimension ref="A1:R302"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="137.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -6284,10 +6299,10 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>53</v>
+        <v>1056</v>
       </c>
       <c r="H49" t="s">
         <v>20</v>
@@ -6305,10 +6320,10 @@
         <v>14</v>
       </c>
       <c r="M49">
-        <v>-6.6349951000000003</v>
+        <v>-7.4289557999999998</v>
       </c>
       <c r="N49">
-        <v>106.80831910000001</v>
+        <v>109.24180987</v>
       </c>
       <c r="O49" t="s">
         <v>798</v>
@@ -6361,10 +6376,10 @@
         <v>14</v>
       </c>
       <c r="M50">
-        <v>-6.6106999999999996</v>
+        <v>-7.5985708000000001</v>
       </c>
       <c r="N50">
-        <v>110.6722</v>
+        <v>110.8140958</v>
       </c>
       <c r="O50" t="s">
         <v>799</v>
@@ -8881,10 +8896,10 @@
         <v>14</v>
       </c>
       <c r="M95">
-        <v>-6.2264280000000003</v>
+        <v>-6.8170533300000002</v>
       </c>
       <c r="N95">
-        <v>106.606928</v>
+        <v>107.13036271999999</v>
       </c>
       <c r="O95" t="s">
         <v>844</v>

--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7FCB6A-EBC4-4F90-A494-ABF7ADCDF206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EC0471-EE06-4B6A-BCBB-77C52E49CEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12697,10 +12697,10 @@
         <v>14</v>
       </c>
       <c r="M163" s="3">
-        <v>3.9579439999999999</v>
+        <v>1.1101262999999999</v>
       </c>
       <c r="N163" s="3">
-        <v>108.18632599999999</v>
+        <v>103.96294709999999</v>
       </c>
       <c r="O163" t="s">
         <v>911</v>

--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EC0471-EE06-4B6A-BCBB-77C52E49CEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FBE5A8-8D3E-4AC7-8D2C-C4DE1CC0F378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4533" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="1053">
   <si>
     <t>Store ID</t>
   </si>
@@ -1917,12 +1917,6 @@
     <t>alan Bida Ayu Pintu 1, Mangsang, Kecamatan Sei Beduk, Kota Batam, Kepulauan Riau</t>
   </si>
   <si>
-    <t>PAMBIL MALL</t>
-  </si>
-  <si>
-    <t>Jalan Ahmad Yani, Muka Kuning, Kecamatan Sei Beduk, Kota Batam, Kepulauan Riau (Kode Pos 29433)</t>
-  </si>
-  <si>
     <t>PLAZA BTC</t>
   </si>
   <si>
@@ -3163,9 +3157,6 @@
   </si>
   <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=MALL%20BOTANIA%202%20Jalan%20Raja%20Alikelana%2C%20Kelurahan%20Belian%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029464%29%20-</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/?api=1&amp;query=PAMBIL%20MALL%20Jalan%20Ahmad%20Yani%2C%20Muka%20Kuning%2C%20Kecamatan%20Sei%20Beduk%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20%28Kode%20Pos%2029433%29%20-</t>
   </si>
   <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=PLAZA%20MUSTAFA%20Raja%20Alikelana%2C%20Kelurahan%20Belian%2C%20Kecamatan%20Batam%20Kota%2C%20Kota%20Batam%2C%20Kepulauan%20Riau%20-</t>
@@ -3216,7 +3207,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -3259,7 +3250,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
@@ -3565,7 +3556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R306"/>
+  <dimension ref="A1:R305"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
@@ -3631,16 +3622,16 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="P1" t="s">
+        <v>745</v>
+      </c>
+      <c r="Q1" t="s">
         <v>746</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>747</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>748</v>
-      </c>
-      <c r="R1" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -3687,16 +3678,16 @@
         <v>106.86823800000001</v>
       </c>
       <c r="O2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="P2" s="2">
         <v>443349</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -3743,16 +3734,16 @@
         <v>95.426084700000004</v>
       </c>
       <c r="O3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P3" s="2">
         <v>257315</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -3799,16 +3790,16 @@
         <v>115.139672</v>
       </c>
       <c r="O4" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="P4" s="2">
         <v>526029</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -3855,16 +3846,16 @@
         <v>140.41463045</v>
       </c>
       <c r="O5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="P5" s="2">
         <v>240609</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -3911,16 +3902,16 @@
         <v>115.1800717</v>
       </c>
       <c r="O6" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="P6" s="2">
         <v>526029</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -3967,16 +3958,16 @@
         <v>115.16683556170941</v>
       </c>
       <c r="O7" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="P7" s="2">
         <v>526029</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -4023,16 +4014,16 @@
         <v>112.6326371</v>
       </c>
       <c r="O8" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="P8" s="2">
         <v>874660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -4079,16 +4070,16 @@
         <v>112.6225687</v>
       </c>
       <c r="O9" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="P9" s="2">
         <v>874660</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -4135,16 +4126,16 @@
         <v>112.644931</v>
       </c>
       <c r="O10" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="P10" s="2">
         <v>874660</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -4191,16 +4182,16 @@
         <v>111.5222126</v>
       </c>
       <c r="O11" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="P11" s="2">
         <v>201992</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -4247,16 +4238,16 @@
         <v>110.3630869</v>
       </c>
       <c r="O12" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="P12" s="2">
         <v>413784</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -4303,16 +4294,16 @@
         <v>110.36608</v>
       </c>
       <c r="O13" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="P13" s="2">
         <v>413784</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -4359,16 +4350,16 @@
         <v>110.39062</v>
       </c>
       <c r="O14" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="P14" s="2">
         <v>413784</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -4376,7 +4367,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -4385,7 +4376,7 @@
         <v>543</v>
       </c>
       <c r="E15" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F15" t="s">
         <v>579</v>
@@ -4415,16 +4406,16 @@
         <v>98.626940000000005</v>
       </c>
       <c r="O15" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="P15" s="2">
         <v>1116142</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -4471,16 +4462,16 @@
         <v>112.6974711</v>
       </c>
       <c r="O16" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="P16" s="2">
         <v>1197301</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -4527,16 +4518,16 @@
         <v>107.27278</v>
       </c>
       <c r="O17" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="P17" s="2">
         <v>1197301</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -4583,16 +4574,16 @@
         <v>95.992199999999997</v>
       </c>
       <c r="O18" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="P18" s="2">
         <v>633649</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -4639,16 +4630,16 @@
         <v>110.8511230875</v>
       </c>
       <c r="O19" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="P19" s="2">
         <v>586166</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -4695,16 +4686,16 @@
         <v>105.88436</v>
       </c>
       <c r="O20" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="P20" s="2">
         <v>908228</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -4751,16 +4742,16 @@
         <v>99.851590000000002</v>
       </c>
       <c r="O21" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="P21" s="2">
         <v>506673</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -4807,16 +4798,16 @@
         <v>107.57766580000001</v>
       </c>
       <c r="O22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="P22" s="2">
         <v>2555187</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -4863,16 +4854,16 @@
         <v>107.599767</v>
       </c>
       <c r="O23" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="P23" s="2">
         <v>2555187</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -4880,7 +4871,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -4889,7 +4880,7 @@
         <v>543</v>
       </c>
       <c r="E24" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F24" t="s">
         <v>561</v>
@@ -4919,16 +4910,16 @@
         <v>103.6271038</v>
       </c>
       <c r="O24" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="P24" s="2">
         <v>232915</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -4936,7 +4927,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -4945,7 +4936,7 @@
         <v>543</v>
       </c>
       <c r="E25" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F25" t="s">
         <v>579</v>
@@ -4975,16 +4966,16 @@
         <v>99.256428099999994</v>
       </c>
       <c r="O25" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="P25" s="2">
         <v>2530492</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -5031,16 +5022,16 @@
         <v>112.7325051</v>
       </c>
       <c r="O26" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="P26" s="2">
         <v>3000075</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -5087,16 +5078,16 @@
         <v>112.65759699166669</v>
       </c>
       <c r="O27" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="P27" s="2">
         <v>3000075</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -5143,16 +5134,16 @@
         <v>112.738051</v>
       </c>
       <c r="O28" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P28" s="2">
         <v>3000075</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -5199,16 +5190,16 @@
         <v>112.7392222</v>
       </c>
       <c r="O29" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="P29" s="2">
         <v>3000075</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -5255,16 +5246,16 @@
         <v>112.7174334</v>
       </c>
       <c r="O30" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P30" s="2">
         <v>3000075</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -5311,16 +5302,16 @@
         <v>112.6870227</v>
       </c>
       <c r="O31" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="P31" s="2">
         <v>3000075</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -5367,16 +5358,16 @@
         <v>112.7466218</v>
       </c>
       <c r="O32" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="P32" s="2">
         <v>3000075</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -5423,16 +5414,16 @@
         <v>112.74463470000001</v>
       </c>
       <c r="O33" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="P33" s="2">
         <v>3000075</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -5479,16 +5470,16 @@
         <v>112.73487249999999</v>
       </c>
       <c r="O34" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="P34" s="2">
         <v>3000075</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -5535,16 +5526,16 @@
         <v>110.38950269999999</v>
       </c>
       <c r="O35" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="P35" s="2">
         <v>1693034</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -5591,16 +5582,16 @@
         <v>112.6326371</v>
       </c>
       <c r="O36" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="P36" s="2">
         <v>874660</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -5647,16 +5638,16 @@
         <v>110.41083</v>
       </c>
       <c r="O37" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="P37" s="2">
         <v>1243381</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -5703,16 +5694,16 @@
         <v>110.4435859</v>
       </c>
       <c r="O38" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="P38" s="2">
         <v>1693034</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -5759,16 +5750,16 @@
         <v>107.7592616</v>
       </c>
       <c r="O39" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="P39" s="2">
         <v>3723181</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -5815,16 +5806,16 @@
         <v>109.19860799999999</v>
       </c>
       <c r="O40" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="P40" s="2">
         <v>291806</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -5871,16 +5862,16 @@
         <v>110.40374199999999</v>
       </c>
       <c r="O41" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="P41" s="2">
         <v>908228</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -5927,16 +5918,16 @@
         <v>110.434046</v>
       </c>
       <c r="O42" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="P42" s="2">
         <v>1693034</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -5983,16 +5974,16 @@
         <v>105.25949</v>
       </c>
       <c r="O43" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="P43" s="2">
         <v>1096935</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -6039,16 +6030,16 @@
         <v>131.33061025000001</v>
       </c>
       <c r="O44" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="P44" s="2">
         <v>283366</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -6095,16 +6086,16 @@
         <v>107.6075793</v>
       </c>
       <c r="O45" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="P45" s="2">
         <v>2555187</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -6151,16 +6142,16 @@
         <v>109.67203000000001</v>
       </c>
       <c r="O46" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="P46" s="2">
         <v>317534</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -6207,16 +6198,16 @@
         <v>108.56307769999999</v>
       </c>
       <c r="O47" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="P47" s="2">
         <v>348911</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -6263,16 +6254,16 @@
         <v>108.5591812</v>
       </c>
       <c r="O48" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="P48" s="2">
         <v>348911</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -6295,7 +6286,7 @@
         <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="H49" t="s">
         <v>20</v>
@@ -6319,16 +6310,16 @@
         <v>109.2423038</v>
       </c>
       <c r="O49" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="P49" s="2">
         <v>413784</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -6375,16 +6366,16 @@
         <v>109.79171100000001</v>
       </c>
       <c r="O50" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="P50" s="2">
         <v>586166</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -6431,16 +6422,16 @@
         <v>106.79707190000001</v>
       </c>
       <c r="O51" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="P51" s="2">
         <v>1122771</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -6487,16 +6478,16 @@
         <v>106.80342804</v>
       </c>
       <c r="O52" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="P52" s="2">
         <v>1122771</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -6543,16 +6534,16 @@
         <v>107.444568</v>
       </c>
       <c r="O53" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="P53" s="2">
         <v>1029561</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
@@ -6599,16 +6590,16 @@
         <v>106.79143498000001</v>
       </c>
       <c r="O54" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="P54" s="2">
         <v>1122771</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -6655,16 +6646,16 @@
         <v>107.148844</v>
       </c>
       <c r="O55" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="P55" s="2">
         <v>3172831</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -6711,16 +6702,16 @@
         <v>110.7926994</v>
       </c>
       <c r="O56" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="P56" s="2">
         <v>586166</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -6767,16 +6758,16 @@
         <v>105.88436</v>
       </c>
       <c r="O57" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="P57" s="2">
         <v>586166</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -6823,16 +6814,16 @@
         <v>107.46249090000001</v>
       </c>
       <c r="O58" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="P58" s="2">
         <v>2519882</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -6879,16 +6870,16 @@
         <v>107.286807</v>
       </c>
       <c r="O59" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="P59" s="2">
         <v>2519882</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -6935,16 +6926,16 @@
         <v>106.9152256</v>
       </c>
       <c r="O60" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="P60" s="2">
         <v>2496198</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -6991,16 +6982,16 @@
         <v>106.73447299999999</v>
       </c>
       <c r="O61" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="P61" s="2">
         <v>1404786</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
@@ -7047,16 +7038,16 @@
         <v>106.8194326</v>
       </c>
       <c r="O62" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="P62" s="2">
         <v>2408480</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
@@ -7103,16 +7094,16 @@
         <v>107.33363799999999</v>
       </c>
       <c r="O63" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="P63" s="2">
         <v>2519882</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
@@ -7159,16 +7150,16 @@
         <v>107.2924549</v>
       </c>
       <c r="O64" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="P64" s="2">
         <v>2519882</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -7215,16 +7206,16 @@
         <v>107.2898017</v>
       </c>
       <c r="O65" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="P65" s="2">
         <v>2519882</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
@@ -7271,16 +7262,16 @@
         <v>106.6985375</v>
       </c>
       <c r="O66" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="P66" s="2">
         <v>1404786</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
@@ -7327,16 +7318,16 @@
         <v>106.107681</v>
       </c>
       <c r="O67" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="P67" s="2">
         <v>1392049</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
@@ -7383,16 +7374,16 @@
         <v>106.6668019</v>
       </c>
       <c r="O68" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="P68" s="2">
         <v>1404786</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
@@ -7439,16 +7430,16 @@
         <v>106.8032613725</v>
       </c>
       <c r="O69" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="P69" s="2">
         <v>2408480</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
@@ -7495,16 +7486,16 @@
         <v>107.04671879999999</v>
       </c>
       <c r="O70" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="P70" s="2">
         <v>3172831</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
@@ -7551,16 +7542,16 @@
         <v>106.783653</v>
       </c>
       <c r="O71" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="P71" s="2">
         <v>2408480</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
@@ -7607,16 +7598,16 @@
         <v>106.65441060000001</v>
       </c>
       <c r="O72" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="P72" s="2">
         <v>3286420</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
@@ -7663,16 +7654,16 @@
         <v>106.780438</v>
       </c>
       <c r="O73" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="P73" s="2">
         <v>2408480</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
@@ -7719,16 +7710,16 @@
         <v>106.878243</v>
       </c>
       <c r="O74" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="P74" s="2">
         <v>3310145</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
@@ -7775,16 +7766,16 @@
         <v>106.82941580000001</v>
       </c>
       <c r="O75" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="P75" s="2">
         <v>2408480</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
@@ -7831,16 +7822,16 @@
         <v>106.74366240000001</v>
       </c>
       <c r="O76" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="P76" s="2">
         <v>1404786</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
@@ -7887,16 +7878,16 @@
         <v>106.6904844</v>
       </c>
       <c r="O77" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="P77" s="2">
         <v>1404786</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
@@ -7943,16 +7934,16 @@
         <v>106.816502</v>
       </c>
       <c r="O78" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="P78" s="2">
         <v>2408480</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
@@ -7999,16 +7990,16 @@
         <v>106.79686</v>
       </c>
       <c r="O79" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="P79" s="2">
         <v>2408480</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
@@ -8055,16 +8046,16 @@
         <v>106.7987329</v>
       </c>
       <c r="O80" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="P80" s="2">
         <v>2408480</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
@@ -8111,16 +8102,16 @@
         <v>106.864919</v>
       </c>
       <c r="O81" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="P81" s="2">
         <v>3310145</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
@@ -8167,16 +8158,16 @@
         <v>107.0078793</v>
       </c>
       <c r="O82" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="P82" s="2">
         <v>2496198</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
@@ -8223,16 +8214,16 @@
         <v>106.7501445</v>
       </c>
       <c r="O83" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="P83" s="2">
         <v>2408480</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
@@ -8279,16 +8270,16 @@
         <v>106.7025622</v>
       </c>
       <c r="O84" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="P84" s="2">
         <v>3286420</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
@@ -8335,16 +8326,16 @@
         <v>106.69190999999999</v>
       </c>
       <c r="O85" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="P85" s="2">
         <v>3286420</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
@@ -8391,16 +8382,16 @@
         <v>106.98876</v>
       </c>
       <c r="O86" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="P86" s="2">
         <v>2496198</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
@@ -8447,16 +8438,16 @@
         <v>107.69665070000001</v>
       </c>
       <c r="O87" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="P87" s="2">
         <v>2555187</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
@@ -8503,16 +8494,16 @@
         <v>106.91381699999999</v>
       </c>
       <c r="O88" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="P88" s="2">
         <v>3310145</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
@@ -8559,16 +8550,16 @@
         <v>106.805572</v>
       </c>
       <c r="O89" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="P89" s="2">
         <v>2408480</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
@@ -8615,16 +8606,16 @@
         <v>106.816502</v>
       </c>
       <c r="O90" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="P90" s="2">
         <v>2408480</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
@@ -8671,16 +8662,16 @@
         <v>106.9909492</v>
       </c>
       <c r="O91" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="P91" s="2">
         <v>2496198</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
@@ -8727,16 +8718,16 @@
         <v>106.80855425423729</v>
       </c>
       <c r="O92" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="P92" s="2">
         <v>2408480</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
@@ -8783,16 +8774,16 @@
         <v>106.7229396</v>
       </c>
       <c r="O93" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="P93" s="2">
         <v>2408480</v>
       </c>
       <c r="Q93" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
@@ -8839,16 +8830,16 @@
         <v>106.8012609</v>
       </c>
       <c r="O94" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="P94" s="2">
         <v>1109489</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
@@ -8895,16 +8886,16 @@
         <v>107.1307897333333</v>
       </c>
       <c r="O95" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="P95" s="2">
         <v>2516417</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
@@ -8951,16 +8942,16 @@
         <v>106.7995999</v>
       </c>
       <c r="O96" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="P96" s="2">
         <v>1109489</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
@@ -9007,16 +8998,16 @@
         <v>106.810351</v>
       </c>
       <c r="O97" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="P97" s="2">
         <v>2408480</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.3">
@@ -9063,16 +9054,16 @@
         <v>106.82950099999999</v>
       </c>
       <c r="O98" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="P98" s="2">
         <v>2408480</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.3">
@@ -9119,16 +9110,16 @@
         <v>106.79682699999999</v>
       </c>
       <c r="O99" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="P99" s="2">
         <v>1109489</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
@@ -9175,16 +9166,16 @@
         <v>106.8322373</v>
       </c>
       <c r="O100" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="P100" s="2">
         <v>2408480</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
@@ -9231,16 +9222,16 @@
         <v>106.81459220000001</v>
       </c>
       <c r="O101" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="P101" s="2">
         <v>2408480</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
@@ -9287,16 +9278,16 @@
         <v>106.8355559</v>
       </c>
       <c r="O102" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="P102" s="2">
         <v>2408480</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
@@ -9343,16 +9334,16 @@
         <v>106.904841</v>
       </c>
       <c r="O103" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="P103" s="2">
         <v>3310145</v>
       </c>
       <c r="Q103" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.3">
@@ -9399,16 +9390,16 @@
         <v>106.9350951</v>
       </c>
       <c r="O104" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="P104" s="2">
         <v>3310145</v>
       </c>
       <c r="Q104" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R104" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
@@ -9455,16 +9446,16 @@
         <v>106.904841</v>
       </c>
       <c r="O105" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="P105" s="2">
         <v>3310145</v>
       </c>
       <c r="Q105" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.3">
@@ -9511,16 +9502,16 @@
         <v>106.8623509</v>
       </c>
       <c r="O106" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="P106" s="2">
         <v>3310145</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R106" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
@@ -9567,16 +9558,16 @@
         <v>106.7186554</v>
       </c>
       <c r="O107" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="P107" s="2">
         <v>1899515</v>
       </c>
       <c r="Q107" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R107" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.3">
@@ -9623,16 +9614,16 @@
         <v>106.8300413</v>
       </c>
       <c r="O108" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="P108" s="2">
         <v>2408480</v>
       </c>
       <c r="Q108" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R108" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.3">
@@ -9679,16 +9670,16 @@
         <v>106.778358</v>
       </c>
       <c r="O109" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="P109" s="2">
         <v>2408480</v>
       </c>
       <c r="Q109" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
@@ -9696,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
@@ -9705,13 +9696,13 @@
         <v>543</v>
       </c>
       <c r="E110" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F110" t="s">
         <v>592</v>
       </c>
       <c r="G110" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="H110" t="s">
         <v>20</v>
@@ -9735,16 +9726,16 @@
         <v>101.1184993</v>
       </c>
       <c r="O110" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="P110" s="2" t="e">
         <v>#N/A</v>
       </c>
       <c r="Q110" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R110" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
@@ -9791,16 +9782,16 @@
         <v>106.81844220000001</v>
       </c>
       <c r="O111" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="P111" s="2">
         <v>1109489</v>
       </c>
       <c r="Q111" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R111" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.3">
@@ -9847,16 +9838,16 @@
         <v>106.822447</v>
       </c>
       <c r="O112" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="P112" s="2">
         <v>1109489</v>
       </c>
       <c r="Q112" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R112" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.3">
@@ -9903,16 +9894,16 @@
         <v>106.79639589999999</v>
       </c>
       <c r="O113" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="P113" s="2">
         <v>2615945</v>
       </c>
       <c r="Q113" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R113" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.3">
@@ -9959,16 +9950,16 @@
         <v>106.64505800000001</v>
       </c>
       <c r="O114" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="P114" s="2">
         <v>1404786</v>
       </c>
       <c r="Q114" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R114" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.3">
@@ -10015,16 +10006,16 @@
         <v>106.64505800000001</v>
       </c>
       <c r="O115" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="P115" s="2">
         <v>1404786</v>
       </c>
       <c r="Q115" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R115" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.3">
@@ -10071,16 +10062,16 @@
         <v>106.8761729</v>
       </c>
       <c r="O116" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="P116" s="2">
         <v>1109489</v>
       </c>
       <c r="Q116" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R116" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.3">
@@ -10127,16 +10118,16 @@
         <v>106.71875970000001</v>
       </c>
       <c r="O117" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="P117" s="2">
         <v>2615945</v>
       </c>
       <c r="Q117" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R117" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.3">
@@ -10183,16 +10174,16 @@
         <v>106.7900491</v>
       </c>
       <c r="O118" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="P118" s="2">
         <v>2615945</v>
       </c>
       <c r="Q118" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R118" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
@@ -10239,16 +10230,16 @@
         <v>106.810389</v>
       </c>
       <c r="O119" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="P119" s="2">
         <v>1109489</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R119" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.3">
@@ -10295,16 +10286,16 @@
         <v>106.691524</v>
       </c>
       <c r="O120" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="P120" s="2">
         <v>1404786</v>
       </c>
       <c r="Q120" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R120" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.3">
@@ -10351,16 +10342,16 @@
         <v>106.526785</v>
       </c>
       <c r="O121" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="P121" s="2">
         <v>3286420</v>
       </c>
       <c r="Q121" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R121" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.3">
@@ -10407,16 +10398,16 @@
         <v>106.71206050000001</v>
       </c>
       <c r="O122" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="P122" s="2">
         <v>2615945</v>
       </c>
       <c r="Q122" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R122" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.3">
@@ -10463,16 +10454,16 @@
         <v>106.71206050000001</v>
       </c>
       <c r="O123" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="P123" s="2">
         <v>2615945</v>
       </c>
       <c r="Q123" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R123" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.3">
@@ -10519,16 +10510,16 @@
         <v>106.8120297</v>
       </c>
       <c r="O124" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="P124" s="2">
         <v>2615945</v>
       </c>
       <c r="Q124" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R124" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.3">
@@ -10575,16 +10566,16 @@
         <v>106.794287</v>
       </c>
       <c r="O125" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="P125" s="2">
         <v>2615945</v>
       </c>
       <c r="Q125" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R125" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.3">
@@ -10631,16 +10622,16 @@
         <v>106.794287</v>
       </c>
       <c r="O126" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="P126" s="2">
         <v>1109489</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R126" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.3">
@@ -10687,16 +10678,16 @@
         <v>106.82715</v>
       </c>
       <c r="O127" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="P127" s="2">
         <v>1109489</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R127" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.3">
@@ -10743,16 +10734,16 @@
         <v>106.8356417086956</v>
       </c>
       <c r="O128" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="P128" s="2">
         <v>1876057</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R128" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.3">
@@ -10799,16 +10790,16 @@
         <v>106.8678798190476</v>
       </c>
       <c r="O129" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P129" s="2">
         <v>1876057</v>
       </c>
       <c r="Q129" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R129" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
@@ -10855,16 +10846,16 @@
         <v>106.8235201</v>
       </c>
       <c r="O130" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="P130" s="2">
         <v>2615945</v>
       </c>
       <c r="Q130" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R130" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
@@ -10911,16 +10902,16 @@
         <v>105.9926839571429</v>
       </c>
       <c r="O131" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="P131" s="2">
         <v>730530</v>
       </c>
       <c r="Q131" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R131" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
@@ -10967,16 +10958,16 @@
         <v>106.9059815</v>
       </c>
       <c r="O132" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="P132" s="2">
         <v>1876057</v>
       </c>
       <c r="Q132" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R132" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.3">
@@ -11023,16 +11014,16 @@
         <v>106.735461</v>
       </c>
       <c r="O133" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="P133" s="2">
         <v>1876057</v>
       </c>
       <c r="Q133" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R133" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.3">
@@ -11079,16 +11070,16 @@
         <v>106.021874</v>
       </c>
       <c r="O134" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="P134" s="2">
         <v>464716</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R134" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.3">
@@ -11135,16 +11126,16 @@
         <v>106.021874</v>
       </c>
       <c r="O135" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="P135" s="2">
         <v>464716</v>
       </c>
       <c r="Q135" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R135" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.3">
@@ -11191,16 +11182,16 @@
         <v>106.0577756</v>
       </c>
       <c r="O136" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="P136" s="2">
         <v>464716</v>
       </c>
       <c r="Q136" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R136" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
@@ -11247,16 +11238,16 @@
         <v>106.805099</v>
       </c>
       <c r="O137" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="P137" s="2">
         <v>1096935</v>
       </c>
       <c r="Q137" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R137" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
@@ -11264,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -11273,13 +11264,13 @@
         <v>543</v>
       </c>
       <c r="E138" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F138" t="s">
         <v>569</v>
       </c>
       <c r="G138" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H138" t="s">
         <v>20</v>
@@ -11303,16 +11294,16 @@
         <v>105.258031</v>
       </c>
       <c r="O138" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="P138" s="2">
         <v>411280</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R138" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
@@ -11359,16 +11350,16 @@
         <v>106.860127375</v>
       </c>
       <c r="O139" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="P139" s="2">
         <v>3310145</v>
       </c>
       <c r="Q139" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R139" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
@@ -11415,16 +11406,16 @@
         <v>119.40956370000001</v>
       </c>
       <c r="O140" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="P140" s="2">
         <v>1470262</v>
       </c>
       <c r="Q140" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R140" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
@@ -11471,16 +11462,16 @@
         <v>136.83976419999999</v>
       </c>
       <c r="O141" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="P141" s="2">
         <v>313016</v>
       </c>
       <c r="Q141" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R141" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
@@ -11527,16 +11518,16 @@
         <v>122.5263968</v>
       </c>
       <c r="O142" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="P142" s="2">
         <v>347380</v>
       </c>
       <c r="Q142" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R142" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
@@ -11583,16 +11574,16 @@
         <v>114.88889</v>
       </c>
       <c r="O143" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="P143" s="2">
         <v>360966</v>
       </c>
       <c r="Q143" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R143" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
@@ -11639,16 +11630,16 @@
         <v>102.2623797</v>
       </c>
       <c r="O144" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="P144" s="2">
         <v>385511</v>
       </c>
       <c r="Q144" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R144" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
@@ -11695,16 +11686,16 @@
         <v>128.22067999999999</v>
       </c>
       <c r="O145" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="P145" s="2">
         <v>354052</v>
       </c>
       <c r="Q145" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R145" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
@@ -11751,16 +11742,16 @@
         <v>128.24610999999999</v>
       </c>
       <c r="O146" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="P146" s="2">
         <v>354052</v>
       </c>
       <c r="Q146" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R146" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
@@ -11768,7 +11759,7 @@
         <v>14</v>
       </c>
       <c r="B147" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -11777,7 +11768,7 @@
         <v>543</v>
       </c>
       <c r="E147" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F147" t="s">
         <v>545</v>
@@ -11807,16 +11798,16 @@
         <v>99.643330000000006</v>
       </c>
       <c r="O147" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="P147" s="2">
         <v>232915</v>
       </c>
       <c r="Q147" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R147" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
@@ -11863,16 +11854,16 @@
         <v>129.05312000000001</v>
       </c>
       <c r="O148" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="P148" s="2">
         <v>429797</v>
       </c>
       <c r="Q148" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R148" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
@@ -11880,7 +11871,7 @@
         <v>14</v>
       </c>
       <c r="B149" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
@@ -11889,7 +11880,7 @@
         <v>543</v>
       </c>
       <c r="E149" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F149" t="s">
         <v>545</v>
@@ -11919,16 +11910,16 @@
         <v>104.7367697</v>
       </c>
       <c r="O149" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="P149" s="2">
         <v>1240792</v>
       </c>
       <c r="Q149" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R149" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.3">
@@ -11936,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -11945,7 +11936,7 @@
         <v>543</v>
       </c>
       <c r="E150" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F150" t="s">
         <v>545</v>
@@ -11975,16 +11966,16 @@
         <v>104.75221999999999</v>
       </c>
       <c r="O150" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="P150" s="2">
         <v>1761461</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R150" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.3">
@@ -12031,16 +12022,16 @@
         <v>104.76467510000001</v>
       </c>
       <c r="O151" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="P151" s="2">
         <v>1761461</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R151" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
@@ -12087,16 +12078,16 @@
         <v>140.68573069999999</v>
       </c>
       <c r="O152" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="P152" s="2">
         <v>403861</v>
       </c>
       <c r="Q152" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R152" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
@@ -12143,16 +12134,16 @@
         <v>140.71141</v>
       </c>
       <c r="O153" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="P153" s="2">
         <v>403861</v>
       </c>
       <c r="Q153" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R153" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
@@ -12160,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -12169,13 +12160,13 @@
         <v>543</v>
       </c>
       <c r="E154" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F154" t="s">
         <v>549</v>
       </c>
       <c r="G154" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H154" t="s">
         <v>20</v>
@@ -12199,16 +12190,16 @@
         <v>106.12224426</v>
       </c>
       <c r="O154" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="P154" s="2" t="e">
         <v>#N/A</v>
       </c>
       <c r="Q154" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R154" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
@@ -12216,7 +12207,7 @@
         <v>14</v>
       </c>
       <c r="B155" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
@@ -12225,7 +12216,7 @@
         <v>543</v>
       </c>
       <c r="E155" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F155" t="s">
         <v>549</v>
@@ -12255,16 +12246,16 @@
         <v>106.111982</v>
       </c>
       <c r="O155" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="P155" s="2">
         <v>232915</v>
       </c>
       <c r="Q155" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R155" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
@@ -12311,16 +12302,16 @@
         <v>106.11972</v>
       </c>
       <c r="O156" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="P156" s="2">
         <v>232915</v>
       </c>
       <c r="Q156" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R156" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
@@ -12328,7 +12319,7 @@
         <v>14</v>
       </c>
       <c r="B157" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
@@ -12337,7 +12328,7 @@
         <v>543</v>
       </c>
       <c r="E157" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F157" t="s">
         <v>549</v>
@@ -12367,16 +12358,16 @@
         <v>106.11346039999999</v>
       </c>
       <c r="O157" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="P157" s="2">
         <v>633649</v>
       </c>
       <c r="Q157" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R157" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
@@ -12384,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="B158" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C158" t="s">
         <v>14</v>
@@ -12393,7 +12384,7 @@
         <v>543</v>
       </c>
       <c r="E158" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F158" t="s">
         <v>549</v>
@@ -12423,16 +12414,16 @@
         <v>106.11346039999999</v>
       </c>
       <c r="O158" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="P158" s="2">
         <v>232915</v>
       </c>
       <c r="Q158" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R158" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
@@ -12479,16 +12470,16 @@
         <v>116.19811900000001</v>
       </c>
       <c r="O159" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="P159" s="2">
         <v>298996</v>
       </c>
       <c r="Q159" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R159" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
@@ -12496,7 +12487,7 @@
         <v>14</v>
       </c>
       <c r="B160" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
@@ -12505,7 +12496,7 @@
         <v>543</v>
       </c>
       <c r="E160" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F160" t="s">
         <v>602</v>
@@ -12535,16 +12526,16 @@
         <v>103.98111</v>
       </c>
       <c r="O160" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="P160" s="2">
         <v>1240792</v>
       </c>
       <c r="Q160" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R160" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
@@ -12591,16 +12582,16 @@
         <v>140.67375849999999</v>
       </c>
       <c r="O161" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="P161" s="2">
         <v>403861</v>
       </c>
       <c r="Q161" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R161" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
@@ -12647,16 +12638,16 @@
         <v>103.61540100000001</v>
       </c>
       <c r="O162" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="P162" s="2">
         <v>633649</v>
       </c>
       <c r="Q162" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R162" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
@@ -12664,7 +12655,7 @@
         <v>14</v>
       </c>
       <c r="B163" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C163" t="s">
         <v>14</v>
@@ -12673,7 +12664,7 @@
         <v>543</v>
       </c>
       <c r="E163" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F163" t="s">
         <v>602</v>
@@ -12703,16 +12694,16 @@
         <v>103.96294709999999</v>
       </c>
       <c r="O163" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="P163" s="2">
         <v>1240792</v>
       </c>
       <c r="Q163" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R163" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
@@ -12759,16 +12750,16 @@
         <v>116.8552771</v>
       </c>
       <c r="O164" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="P164" s="2">
         <v>733397</v>
       </c>
       <c r="Q164" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R164" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
@@ -12815,16 +12806,16 @@
         <v>116.87338389999999</v>
       </c>
       <c r="O165" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="P165" s="2">
         <v>733397</v>
       </c>
       <c r="Q165" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R165" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
@@ -12871,16 +12862,16 @@
         <v>116.87886207931039</v>
       </c>
       <c r="O166" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="P166" s="2">
         <v>733397</v>
       </c>
       <c r="Q166" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R166" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
@@ -12927,16 +12918,16 @@
         <v>121.041577</v>
       </c>
       <c r="O167" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="P167" s="2">
         <v>733397</v>
       </c>
       <c r="Q167" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R167" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
@@ -12983,16 +12974,16 @@
         <v>116.8409571</v>
       </c>
       <c r="O168" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="P168" s="2">
         <v>733397</v>
       </c>
       <c r="Q168" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R168" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
@@ -13039,16 +13030,16 @@
         <v>116.849977</v>
       </c>
       <c r="O169" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="P169" s="2">
         <v>3172831</v>
       </c>
       <c r="Q169" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R169" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
@@ -13095,16 +13086,16 @@
         <v>106.816604</v>
       </c>
       <c r="O170" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="P170" s="2">
         <v>1109489</v>
       </c>
       <c r="Q170" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R170" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
@@ -13151,16 +13142,16 @@
         <v>106.80373849999999</v>
       </c>
       <c r="O171" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="P171" s="2">
         <v>1109489</v>
       </c>
       <c r="Q171" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R171" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.3">
@@ -13207,16 +13198,16 @@
         <v>106.80374500000001</v>
       </c>
       <c r="O172" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="P172" s="2">
         <v>1109489</v>
       </c>
       <c r="Q172" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R172" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.3">
@@ -13224,7 +13215,7 @@
         <v>14</v>
       </c>
       <c r="B173" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C173" t="s">
         <v>14</v>
@@ -13233,13 +13224,13 @@
         <v>543</v>
       </c>
       <c r="E173" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F173" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G173" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H173" t="s">
         <v>20</v>
@@ -13263,16 +13254,16 @@
         <v>100.36126489999999</v>
       </c>
       <c r="O173" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="P173" s="2">
         <v>928539</v>
       </c>
       <c r="Q173" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R173" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.3">
@@ -13319,16 +13310,16 @@
         <v>131.3081554</v>
       </c>
       <c r="O174" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="P174" s="2">
         <v>283366</v>
       </c>
       <c r="Q174" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R174" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.3">
@@ -13375,16 +13366,16 @@
         <v>117.166201</v>
       </c>
       <c r="O175" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="P175" s="2">
         <v>856361</v>
       </c>
       <c r="Q175" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R175" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.3">
@@ -13392,7 +13383,7 @@
         <v>14</v>
       </c>
       <c r="B176" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C176" t="s">
         <v>14</v>
@@ -13401,10 +13392,10 @@
         <v>543</v>
       </c>
       <c r="E176" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F176" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G176" t="s">
         <v>576</v>
@@ -13431,16 +13422,16 @@
         <v>100.3688628</v>
       </c>
       <c r="O176" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="P176" s="2">
         <v>257315</v>
       </c>
       <c r="Q176" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R176" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.3">
@@ -13448,7 +13439,7 @@
         <v>14</v>
       </c>
       <c r="B177" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C177" t="s">
         <v>14</v>
@@ -13457,10 +13448,10 @@
         <v>543</v>
       </c>
       <c r="E177" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F177" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G177" t="s">
         <v>546</v>
@@ -13487,16 +13478,16 @@
         <v>100.445199</v>
       </c>
       <c r="O177" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P177" s="2">
         <v>1761461</v>
       </c>
       <c r="Q177" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R177" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.3">
@@ -13543,16 +13534,16 @@
         <v>117.46337629999999</v>
       </c>
       <c r="O178" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="P178" s="2">
         <v>187446</v>
       </c>
       <c r="Q178" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R178" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
@@ -13599,16 +13590,16 @@
         <v>101.36961700000001</v>
       </c>
       <c r="O179" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="P179" s="2">
         <v>1116142</v>
       </c>
       <c r="Q179" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R179" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.3">
@@ -13616,7 +13607,7 @@
         <v>14</v>
       </c>
       <c r="B180" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C180" t="s">
         <v>14</v>
@@ -13625,13 +13616,13 @@
         <v>543</v>
       </c>
       <c r="E180" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F180" t="s">
         <v>592</v>
       </c>
       <c r="G180" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H180" t="s">
         <v>20</v>
@@ -13655,16 +13646,16 @@
         <v>101.42177649999999</v>
       </c>
       <c r="O180" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="P180" s="2">
         <v>205288</v>
       </c>
       <c r="Q180" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R180" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
@@ -13672,7 +13663,7 @@
         <v>14</v>
       </c>
       <c r="B181" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C181" t="s">
         <v>14</v>
@@ -13681,7 +13672,7 @@
         <v>543</v>
       </c>
       <c r="E181" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F181" t="s">
         <v>592</v>
@@ -13711,16 +13702,16 @@
         <v>101.4353785</v>
       </c>
       <c r="O181" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="P181" s="2">
         <v>1116142</v>
       </c>
       <c r="Q181" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R181" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.3">
@@ -13767,16 +13758,16 @@
         <v>101.43194</v>
       </c>
       <c r="O182" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="P182" s="2">
         <v>1116142</v>
       </c>
       <c r="Q182" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R182" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.3">
@@ -13823,16 +13814,16 @@
         <v>115.9207</v>
       </c>
       <c r="O183" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="P183" s="2">
         <v>233406</v>
       </c>
       <c r="Q183" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R183" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.3">
@@ -13840,7 +13831,7 @@
         <v>14</v>
       </c>
       <c r="B184" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C184" t="s">
         <v>14</v>
@@ -13849,13 +13840,13 @@
         <v>543</v>
       </c>
       <c r="E184" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F184" t="s">
         <v>602</v>
       </c>
       <c r="G184" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="H184" t="s">
         <v>20</v>
@@ -13879,16 +13870,16 @@
         <v>119.49603</v>
       </c>
       <c r="O184" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="P184" s="2">
         <v>135489</v>
       </c>
       <c r="Q184" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R184" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.3">
@@ -13896,7 +13887,7 @@
         <v>14</v>
       </c>
       <c r="B185" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C185" t="s">
         <v>14</v>
@@ -13905,7 +13896,7 @@
         <v>543</v>
       </c>
       <c r="E185" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F185" t="s">
         <v>602</v>
@@ -13935,16 +13926,16 @@
         <v>110.426658</v>
       </c>
       <c r="O185" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="P185" s="2">
         <v>1240792</v>
       </c>
       <c r="Q185" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R185" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.3">
@@ -13991,16 +13982,16 @@
         <v>101.4550909</v>
       </c>
       <c r="O186" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="P186" s="2">
         <v>1116142</v>
       </c>
       <c r="Q186" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R186" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.3">
@@ -14047,16 +14038,16 @@
         <v>103.94777141874999</v>
       </c>
       <c r="O187" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="P187" s="2">
         <v>1240792</v>
       </c>
       <c r="Q187" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R187" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.3">
@@ -14064,7 +14055,7 @@
         <v>14</v>
       </c>
       <c r="B188" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C188" t="s">
         <v>14</v>
@@ -14073,13 +14064,13 @@
         <v>543</v>
       </c>
       <c r="E188" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F188" t="s">
         <v>602</v>
       </c>
       <c r="G188" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H188" t="s">
         <v>20</v>
@@ -14103,16 +14094,16 @@
         <v>103.9695346</v>
       </c>
       <c r="O188" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="P188" s="2">
         <v>928539</v>
       </c>
       <c r="Q188" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R188" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.3">
@@ -14159,16 +14150,16 @@
         <v>103.988912</v>
       </c>
       <c r="O189" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="P189" s="2">
         <v>1240792</v>
       </c>
       <c r="Q189" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R189" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.3">
@@ -14215,16 +14206,16 @@
         <v>104.05806</v>
       </c>
       <c r="O190" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="P190" s="2">
         <v>1240792</v>
       </c>
       <c r="Q190" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R190" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
@@ -14232,7 +14223,7 @@
         <v>14</v>
       </c>
       <c r="B191" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C191" t="s">
         <v>14</v>
@@ -14241,7 +14232,7 @@
         <v>543</v>
       </c>
       <c r="E191" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F191" t="s">
         <v>602</v>
@@ -14271,16 +14262,16 @@
         <v>103.988912</v>
       </c>
       <c r="O191" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="P191" s="2">
         <v>1240792</v>
       </c>
       <c r="Q191" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R191" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.3">
@@ -14288,7 +14279,7 @@
         <v>14</v>
       </c>
       <c r="B192" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C192" t="s">
         <v>14</v>
@@ -14297,7 +14288,7 @@
         <v>543</v>
       </c>
       <c r="E192" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F192" t="s">
         <v>602</v>
@@ -14327,16 +14318,16 @@
         <v>101.454866</v>
       </c>
       <c r="O192" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="P192" s="2">
         <v>1240792</v>
       </c>
       <c r="Q192" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R192" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.3">
@@ -14344,7 +14335,7 @@
         <v>14</v>
       </c>
       <c r="B193" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C193" t="s">
         <v>14</v>
@@ -14353,7 +14344,7 @@
         <v>543</v>
       </c>
       <c r="E193" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F193" t="s">
         <v>602</v>
@@ -14383,16 +14374,16 @@
         <v>104.01383</v>
       </c>
       <c r="O193" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="P193" s="2">
         <v>1240792</v>
       </c>
       <c r="Q193" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R193" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.3">
@@ -14400,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="B194" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C194" t="s">
         <v>14</v>
@@ -14409,7 +14400,7 @@
         <v>543</v>
       </c>
       <c r="E194" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F194" t="s">
         <v>602</v>
@@ -14439,16 +14430,16 @@
         <v>104.08190980000001</v>
       </c>
       <c r="O194" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P194" s="2">
         <v>1240792</v>
       </c>
       <c r="Q194" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R194" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.3">
@@ -14495,16 +14486,16 @@
         <v>104.0112395659575</v>
       </c>
       <c r="O195" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="P195" s="2">
         <v>1240792</v>
       </c>
       <c r="Q195" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R195" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.3">
@@ -14512,7 +14503,7 @@
         <v>14</v>
       </c>
       <c r="B196" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C196" t="s">
         <v>14</v>
@@ -14521,7 +14512,7 @@
         <v>543</v>
       </c>
       <c r="E196" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F196" t="s">
         <v>602</v>
@@ -14551,16 +14542,16 @@
         <v>103.988912</v>
       </c>
       <c r="O196" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P196" s="2">
         <v>1240792</v>
       </c>
       <c r="Q196" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R196" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.3">
@@ -14607,16 +14598,16 @@
         <v>124.8386173</v>
       </c>
       <c r="O197" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="P197" s="2">
         <v>478194</v>
       </c>
       <c r="Q197" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R197" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.3">
@@ -14663,16 +14654,16 @@
         <v>124.89865210000001</v>
       </c>
       <c r="O198" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="P198" s="2">
         <v>478194</v>
       </c>
       <c r="Q198" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R198" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.3">
@@ -14680,7 +14671,7 @@
         <v>14</v>
       </c>
       <c r="B199" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C199" t="s">
         <v>14</v>
@@ -14689,13 +14680,13 @@
         <v>543</v>
       </c>
       <c r="E199" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F199" t="s">
         <v>592</v>
       </c>
       <c r="G199" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="H199" t="s">
         <v>20</v>
@@ -14719,16 +14710,16 @@
         <v>100.4766108545455</v>
       </c>
       <c r="O199" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="P199" s="2">
         <v>186957</v>
       </c>
       <c r="Q199" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R199" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
@@ -14736,7 +14727,7 @@
         <v>14</v>
       </c>
       <c r="B200" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C200" t="s">
         <v>14</v>
@@ -14745,13 +14736,13 @@
         <v>543</v>
       </c>
       <c r="E200" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F200" t="s">
         <v>592</v>
       </c>
       <c r="G200" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="H200" t="s">
         <v>20</v>
@@ -14775,16 +14766,16 @@
         <v>101.383</v>
       </c>
       <c r="O200" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="P200" s="2">
         <v>651834</v>
       </c>
       <c r="Q200" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R200" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.3">
@@ -14831,16 +14822,16 @@
         <v>101.448266</v>
       </c>
       <c r="O201" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="P201" s="2">
         <v>1116142</v>
       </c>
       <c r="Q201" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R201" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.3">
@@ -14848,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="B202" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C202" t="s">
         <v>14</v>
@@ -14857,7 +14848,7 @@
         <v>543</v>
       </c>
       <c r="E202" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F202" t="s">
         <v>579</v>
@@ -14887,16 +14878,16 @@
         <v>98.385000000000005</v>
       </c>
       <c r="O202" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="P202" s="2">
         <v>1240792</v>
       </c>
       <c r="Q202" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R202" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.3">
@@ -14904,7 +14895,7 @@
         <v>14</v>
       </c>
       <c r="B203" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C203" t="s">
         <v>14</v>
@@ -14913,13 +14904,13 @@
         <v>543</v>
       </c>
       <c r="E203" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F203" t="s">
         <v>579</v>
       </c>
       <c r="G203" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H203" t="s">
         <v>20</v>
@@ -14943,16 +14934,16 @@
         <v>99.159263899999999</v>
       </c>
       <c r="O203" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="P203" s="2">
         <v>229408</v>
       </c>
       <c r="Q203" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R203" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
@@ -14999,16 +14990,16 @@
         <v>106.976947</v>
       </c>
       <c r="O204" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="P204" s="2">
         <v>2496198</v>
       </c>
       <c r="Q204" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R204" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.3">
@@ -15016,7 +15007,7 @@
         <v>14</v>
       </c>
       <c r="B205" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C205" t="s">
         <v>14</v>
@@ -15025,13 +15016,13 @@
         <v>543</v>
       </c>
       <c r="E205" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F205" t="s">
         <v>579</v>
       </c>
       <c r="G205" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H205" t="s">
         <v>20</v>
@@ -15055,16 +15046,16 @@
         <v>98.676479999999998</v>
       </c>
       <c r="O205" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="P205" s="2">
         <v>178524</v>
       </c>
       <c r="Q205" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R205" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.3">
@@ -15072,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="B206" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C206" t="s">
         <v>14</v>
@@ -15081,13 +15072,13 @@
         <v>543</v>
       </c>
       <c r="E206" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F206" t="s">
         <v>579</v>
       </c>
       <c r="G206" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H206" t="s">
         <v>20</v>
@@ -15111,16 +15102,16 @@
         <v>98.648010200000002</v>
       </c>
       <c r="O206" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="P206" s="2">
         <v>338064</v>
       </c>
       <c r="Q206" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R206" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
@@ -15128,7 +15119,7 @@
         <v>14</v>
       </c>
       <c r="B207" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C207" t="s">
         <v>14</v>
@@ -15137,13 +15128,13 @@
         <v>543</v>
       </c>
       <c r="E207" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F207" t="s">
         <v>579</v>
       </c>
       <c r="G207" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H207" t="s">
         <v>20</v>
@@ -15167,16 +15158,16 @@
         <v>98.669719999999998</v>
       </c>
       <c r="O207" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="P207" s="2">
         <v>792179</v>
       </c>
       <c r="Q207" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R207" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.3">
@@ -15184,7 +15175,7 @@
         <v>14</v>
       </c>
       <c r="B208" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C208" t="s">
         <v>14</v>
@@ -15193,13 +15184,13 @@
         <v>543</v>
       </c>
       <c r="E208" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F208" t="s">
         <v>579</v>
       </c>
       <c r="G208" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H208" t="s">
         <v>20</v>
@@ -15223,16 +15214,16 @@
         <v>98.626040900000007</v>
       </c>
       <c r="O208" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="P208" s="2">
         <v>2016906</v>
       </c>
       <c r="Q208" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R208" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
@@ -15240,7 +15231,7 @@
         <v>14</v>
       </c>
       <c r="B209" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C209" t="s">
         <v>14</v>
@@ -15249,7 +15240,7 @@
         <v>543</v>
       </c>
       <c r="E209" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F209" t="s">
         <v>579</v>
@@ -15279,16 +15270,16 @@
         <v>98.695500999999993</v>
       </c>
       <c r="O209" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="P209" s="2">
         <v>2530492</v>
       </c>
       <c r="Q209" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R209" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.3">
@@ -15335,16 +15326,16 @@
         <v>98.672223900000006</v>
       </c>
       <c r="O210" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="P210" s="2">
         <v>2530492</v>
       </c>
       <c r="Q210" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R210" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.3">
@@ -15391,16 +15382,16 @@
         <v>98.667586299999996</v>
       </c>
       <c r="O211" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="P211" s="2">
         <v>2530492</v>
       </c>
       <c r="Q211" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R211" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.3">
@@ -15447,16 +15438,16 @@
         <v>98.693543000000005</v>
       </c>
       <c r="O212" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="P212" s="2">
         <v>2530492</v>
       </c>
       <c r="Q212" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R212" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.3">
@@ -15503,16 +15494,16 @@
         <v>98.689914000000002</v>
       </c>
       <c r="O213" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="P213" s="2">
         <v>2530492</v>
       </c>
       <c r="Q213" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R213" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.3">
@@ -15520,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="B214" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C214" t="s">
         <v>14</v>
@@ -15529,13 +15520,13 @@
         <v>543</v>
       </c>
       <c r="E214" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F214" t="s">
         <v>575</v>
       </c>
       <c r="G214" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H214" t="s">
         <v>20</v>
@@ -15559,16 +15550,16 @@
         <v>98.6571</v>
       </c>
       <c r="O214" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="P214" s="2">
         <v>455555</v>
       </c>
       <c r="Q214" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R214" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.3">
@@ -15576,7 +15567,7 @@
         <v>14</v>
       </c>
       <c r="B215" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C215" t="s">
         <v>14</v>
@@ -15585,13 +15576,13 @@
         <v>543</v>
       </c>
       <c r="E215" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F215" t="s">
         <v>575</v>
       </c>
       <c r="G215" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="H215" t="s">
         <v>20</v>
@@ -15615,16 +15606,16 @@
         <v>97.955706800000002</v>
       </c>
       <c r="O215" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="P215" s="2">
         <v>193950</v>
       </c>
       <c r="Q215" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R215" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.3">
@@ -15632,7 +15623,7 @@
         <v>14</v>
       </c>
       <c r="B216" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C216" t="s">
         <v>14</v>
@@ -15641,13 +15632,13 @@
         <v>543</v>
       </c>
       <c r="E216" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F216" t="s">
         <v>575</v>
       </c>
       <c r="G216" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="H216" t="s">
         <v>20</v>
@@ -15671,16 +15662,16 @@
         <v>97.140679000000006</v>
       </c>
       <c r="O216" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="P216" s="2">
         <v>201720</v>
       </c>
       <c r="Q216" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R216" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.3">
@@ -15688,7 +15679,7 @@
         <v>14</v>
       </c>
       <c r="B217" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C217" t="s">
         <v>14</v>
@@ -15697,7 +15688,7 @@
         <v>543</v>
       </c>
       <c r="E217" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F217" t="s">
         <v>575</v>
@@ -15727,16 +15718,16 @@
         <v>96.721269000000007</v>
       </c>
       <c r="O217" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="P217" s="2">
         <v>2530492</v>
       </c>
       <c r="Q217" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R217" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.3">
@@ -15744,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="B218" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C218" t="s">
         <v>14</v>
@@ -15753,13 +15744,13 @@
         <v>543</v>
       </c>
       <c r="E218" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F218" t="s">
         <v>575</v>
       </c>
       <c r="G218" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H218" t="s">
         <v>20</v>
@@ -15783,16 +15774,16 @@
         <v>95.321732699999998</v>
       </c>
       <c r="O218" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="P218" s="2">
         <v>2016906</v>
       </c>
       <c r="Q218" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R218" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.3">
@@ -15800,7 +15791,7 @@
         <v>14</v>
       </c>
       <c r="B219" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C219" t="s">
         <v>14</v>
@@ -15809,7 +15800,7 @@
         <v>543</v>
       </c>
       <c r="E219" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F219" t="s">
         <v>602</v>
@@ -15839,16 +15830,16 @@
         <v>104.0112395659575</v>
       </c>
       <c r="O219" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="P219" s="2">
         <v>233406</v>
       </c>
       <c r="Q219" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R219" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.3">
@@ -15895,16 +15886,16 @@
         <v>106.8334381</v>
       </c>
       <c r="O220" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="P220" s="2">
         <v>187038</v>
       </c>
       <c r="Q220" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R220" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.3">
@@ -15951,16 +15942,16 @@
         <v>106.9258129</v>
       </c>
       <c r="O221" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="P221" s="2">
         <v>232915</v>
       </c>
       <c r="Q221" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R221" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.3">
@@ -16007,16 +15998,16 @@
         <v>106.938772</v>
       </c>
       <c r="O222" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="P222" s="2">
         <v>2496198</v>
       </c>
       <c r="Q222" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R222" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.3">
@@ -16063,16 +16054,16 @@
         <v>106.73284931273879</v>
       </c>
       <c r="O223" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="P223" s="2">
         <v>2615945</v>
       </c>
       <c r="Q223" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R223" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.3">
@@ -16119,16 +16110,16 @@
         <v>109.3411574</v>
       </c>
       <c r="O224" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="P224" s="2">
         <v>676096</v>
       </c>
       <c r="Q224" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R224" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.3">
@@ -16175,16 +16166,16 @@
         <v>104.11216899999999</v>
       </c>
       <c r="O225" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="P225" s="2">
         <v>1240792</v>
       </c>
       <c r="Q225" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R225" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.3">
@@ -16231,16 +16222,16 @@
         <v>107.02167</v>
       </c>
       <c r="O226" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="P226" s="2">
         <v>2496198</v>
       </c>
       <c r="Q226" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R226" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.3">
@@ -16287,16 +16278,16 @@
         <v>106.906481</v>
       </c>
       <c r="O227" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="P227" s="2">
         <v>1876057</v>
       </c>
       <c r="Q227" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R227" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.3">
@@ -16343,16 +16334,16 @@
         <v>119.403638</v>
       </c>
       <c r="O228" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="P228" s="2">
         <v>1470262</v>
       </c>
       <c r="Q228" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R228" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.3">
@@ -16399,16 +16390,16 @@
         <v>122.620175</v>
       </c>
       <c r="O229" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="P229" s="2" t="e">
         <v>#N/A</v>
       </c>
       <c r="Q229" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R229" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.3">
@@ -16455,16 +16446,16 @@
         <v>110.361913</v>
       </c>
       <c r="O230" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="P230" s="2">
         <v>1105415</v>
       </c>
       <c r="Q230" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R230" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.3">
@@ -16511,16 +16502,16 @@
         <v>110.3707273</v>
       </c>
       <c r="O231" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="P231" s="2">
         <v>413784</v>
       </c>
       <c r="Q231" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R231" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.3">
@@ -16567,16 +16558,16 @@
         <v>110.36417</v>
       </c>
       <c r="O232" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="P232" s="2">
         <v>2555187</v>
       </c>
       <c r="Q232" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R232" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.3">
@@ -16623,16 +16614,16 @@
         <v>107.6059089</v>
       </c>
       <c r="O233" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="P233" s="2">
         <v>2555187</v>
       </c>
       <c r="Q233" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R233" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.3">
@@ -16679,16 +16670,16 @@
         <v>110.5049942</v>
       </c>
       <c r="O234" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="P234" s="2">
         <v>2555187</v>
       </c>
       <c r="Q234" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R234" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.3">
@@ -16735,16 +16726,16 @@
         <v>107.63409299999999</v>
       </c>
       <c r="O235" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="P235" s="2">
         <v>2555187</v>
       </c>
       <c r="Q235" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R235" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
@@ -16791,16 +16782,16 @@
         <v>106.9545294</v>
       </c>
       <c r="O236" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="P236" s="2">
         <v>361581</v>
       </c>
       <c r="Q236" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R236" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.3">
@@ -16847,16 +16838,16 @@
         <v>111.484825</v>
       </c>
       <c r="O237" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="P237" s="2">
         <v>2770531</v>
       </c>
       <c r="Q237" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R237" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
@@ -16903,16 +16894,16 @@
         <v>112.016654</v>
       </c>
       <c r="O238" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="P238" s="2">
         <v>296792</v>
       </c>
       <c r="Q238" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R238" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.3">
@@ -16959,16 +16950,16 @@
         <v>111.520747</v>
       </c>
       <c r="O239" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="P239" s="2">
         <v>201992</v>
       </c>
       <c r="Q239" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R239" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.3">
@@ -17015,16 +17006,16 @@
         <v>114.37748999999999</v>
       </c>
       <c r="O240" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="P240" s="2">
         <v>1769233</v>
       </c>
       <c r="Q240" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R240" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.3">
@@ -17071,16 +17062,16 @@
         <v>112.7334286</v>
       </c>
       <c r="O241" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="P241" s="2">
         <v>3000075</v>
       </c>
       <c r="Q241" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R241" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.3">
@@ -17127,16 +17118,16 @@
         <v>112.7248373</v>
       </c>
       <c r="O242" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="P242" s="2">
         <v>3000075</v>
       </c>
       <c r="Q242" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R242" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.3">
@@ -17183,16 +17174,16 @@
         <v>112.7142917</v>
       </c>
       <c r="O243" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="P243" s="2">
         <v>1982939</v>
       </c>
       <c r="Q243" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R243" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.3">
@@ -17239,16 +17230,16 @@
         <v>112.73196299999999</v>
       </c>
       <c r="O244" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="P244" s="2">
         <v>3000075</v>
       </c>
       <c r="Q244" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R244" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.3">
@@ -17295,16 +17286,16 @@
         <v>123.6131673</v>
       </c>
       <c r="O245" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="P245" s="2">
         <v>443349</v>
       </c>
       <c r="Q245" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R245" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.3">
@@ -17351,16 +17342,16 @@
         <v>116.1257243</v>
       </c>
       <c r="O246" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="P246" s="2">
         <v>452812</v>
       </c>
       <c r="Q246" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R246" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.3">
@@ -17407,16 +17398,16 @@
         <v>112.7103484</v>
       </c>
       <c r="O247" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="P247" s="2">
         <v>1982939</v>
       </c>
       <c r="Q247" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R247" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.3">
@@ -17463,16 +17454,16 @@
         <v>113.69612815714289</v>
       </c>
       <c r="O248" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="P248" s="2">
         <v>2590289</v>
       </c>
       <c r="Q248" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R248" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.3">
@@ -17519,16 +17510,16 @@
         <v>112.5320945</v>
       </c>
       <c r="O249" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="P249" s="2">
         <v>219540</v>
       </c>
       <c r="Q249" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R249" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.3">
@@ -17575,16 +17566,16 @@
         <v>112.782014</v>
       </c>
       <c r="O250" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="P250" s="2">
         <v>3000075</v>
       </c>
       <c r="Q250" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R250" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.3">
@@ -17631,16 +17622,16 @@
         <v>112.6196578</v>
       </c>
       <c r="O251" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="P251" s="2">
         <v>874660</v>
       </c>
       <c r="Q251" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R251" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.3">
@@ -17687,16 +17678,16 @@
         <v>140.67375849999999</v>
       </c>
       <c r="O252" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="P252" s="2">
         <v>403861</v>
       </c>
       <c r="Q252" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R252" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.3">
@@ -17743,16 +17734,16 @@
         <v>111.5222126</v>
       </c>
       <c r="O253" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="P253" s="2">
         <v>201992</v>
       </c>
       <c r="Q253" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R253" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.3">
@@ -17799,16 +17790,16 @@
         <v>112.7096712</v>
       </c>
       <c r="O254" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="P254" s="2">
         <v>1982939</v>
       </c>
       <c r="Q254" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R254" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.3">
@@ -17855,16 +17846,16 @@
         <v>107.1434466</v>
       </c>
       <c r="O255" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="P255" s="2">
         <v>3172831</v>
       </c>
       <c r="Q255" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R255" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.3">
@@ -17911,16 +17902,16 @@
         <v>106.8320485</v>
       </c>
       <c r="O256" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="P256" s="2">
         <v>5495373</v>
       </c>
       <c r="Q256" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R256" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.3">
@@ -17967,16 +17958,16 @@
         <v>106.86264679999999</v>
       </c>
       <c r="O257" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="P257" s="2">
         <v>5495373</v>
       </c>
       <c r="Q257" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R257" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.3">
@@ -18023,16 +18014,16 @@
         <v>106.82375570000001</v>
       </c>
       <c r="O258" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="P258" s="2">
         <v>1109489</v>
       </c>
       <c r="Q258" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R258" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.3">
@@ -18079,16 +18070,16 @@
         <v>106.81271649999999</v>
       </c>
       <c r="O259" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="P259" s="2">
         <v>1927869</v>
       </c>
       <c r="Q259" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R259" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.3">
@@ -18135,16 +18126,16 @@
         <v>106.79304209999999</v>
       </c>
       <c r="O260" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="P260" s="2">
         <v>1927869</v>
       </c>
       <c r="Q260" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R260" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.3">
@@ -18191,16 +18182,16 @@
         <v>106.84094690000001</v>
       </c>
       <c r="O261" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="P261" s="2">
         <v>1927869</v>
       </c>
       <c r="Q261" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R261" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.3">
@@ -18247,16 +18238,16 @@
         <v>106.8230563</v>
       </c>
       <c r="O262" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="P262" s="2">
         <v>1927869</v>
       </c>
       <c r="Q262" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R262" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.3">
@@ -18303,16 +18294,16 @@
         <v>106.81243689999999</v>
       </c>
       <c r="O263" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="P263" s="2">
         <v>1927869</v>
       </c>
       <c r="Q263" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R263" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.3">
@@ -18359,16 +18350,16 @@
         <v>106.95247910000001</v>
       </c>
       <c r="O264" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="P264" s="2">
         <v>3310145</v>
       </c>
       <c r="Q264" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R264" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.3">
@@ -18415,16 +18406,16 @@
         <v>106.8620153</v>
       </c>
       <c r="O265" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="P265" s="2">
         <v>3310145</v>
       </c>
       <c r="Q265" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R265" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.3">
@@ -18471,16 +18462,16 @@
         <v>106.8341509166667</v>
       </c>
       <c r="O266" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="P266" s="2">
         <v>1876057</v>
       </c>
       <c r="Q266" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R266" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.3">
@@ -18527,16 +18518,16 @@
         <v>106.915924</v>
       </c>
       <c r="O267" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="P267" s="2">
         <v>1876057</v>
       </c>
       <c r="Q267" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R267" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.3">
@@ -18583,16 +18574,16 @@
         <v>106.78179958545461</v>
       </c>
       <c r="O268" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="P268" s="2">
         <v>1876057</v>
       </c>
       <c r="Q268" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R268" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.3">
@@ -18639,16 +18630,16 @@
         <v>106.8356417086956</v>
       </c>
       <c r="O269" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="P269" s="2">
         <v>1876057</v>
       </c>
       <c r="Q269" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R269" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.3">
@@ -18695,16 +18686,16 @@
         <v>106.8356417086956</v>
       </c>
       <c r="O270" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="P270" s="2">
         <v>1876057</v>
       </c>
       <c r="Q270" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R270" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.3">
@@ -18751,16 +18742,16 @@
         <v>106.9029</v>
       </c>
       <c r="O271" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="P271" s="2">
         <v>1876057</v>
       </c>
       <c r="Q271" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R271" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.3">
@@ -18807,16 +18798,16 @@
         <v>106.795376</v>
       </c>
       <c r="O272" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="P272" s="2">
         <v>1876057</v>
       </c>
       <c r="Q272" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R272" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.3">
@@ -18863,16 +18854,16 @@
         <v>106.89754436071431</v>
       </c>
       <c r="O273" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="P273" s="2">
         <v>1876057</v>
       </c>
       <c r="Q273" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R273" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.3">
@@ -18919,16 +18910,16 @@
         <v>106.7880296</v>
       </c>
       <c r="O274" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="P274" s="2">
         <v>1876057</v>
       </c>
       <c r="Q274" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R274" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.3">
@@ -18975,16 +18966,16 @@
         <v>106.1593124</v>
       </c>
       <c r="O275" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="P275" s="2">
         <v>730530</v>
       </c>
       <c r="Q275" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R275" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.3">
@@ -19031,16 +19022,16 @@
         <v>106.79687699999999</v>
       </c>
       <c r="O276" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="P276" s="2">
         <v>2408480</v>
       </c>
       <c r="Q276" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R276" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.3">
@@ -19087,16 +19078,16 @@
         <v>106.66464338</v>
       </c>
       <c r="O277" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="P277" s="2">
         <v>1404786</v>
       </c>
       <c r="Q277" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R277" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.3">
@@ -19143,16 +19134,16 @@
         <v>106.6944503</v>
       </c>
       <c r="O278" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="P278" s="2">
         <v>1404786</v>
       </c>
       <c r="Q278" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R278" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.3">
@@ -19199,16 +19190,16 @@
         <v>106.7085737</v>
       </c>
       <c r="O279" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="P279" s="2">
         <v>1404786</v>
       </c>
       <c r="Q279" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R279" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.3">
@@ -19255,16 +19246,16 @@
         <v>106.629623</v>
       </c>
       <c r="O280" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="P280" s="2">
         <v>3286420</v>
       </c>
       <c r="Q280" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R280" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.3">
@@ -19311,16 +19302,16 @@
         <v>106.79866</v>
       </c>
       <c r="O281" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="P281" s="2">
         <v>2615945</v>
       </c>
       <c r="Q281" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R281" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.3">
@@ -19367,16 +19358,16 @@
         <v>106.79215000000001</v>
       </c>
       <c r="O282" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="P282" s="2">
         <v>2615945</v>
       </c>
       <c r="Q282" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R282" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.3">
@@ -19423,16 +19414,16 @@
         <v>131.42986999999999</v>
       </c>
       <c r="O283" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="P283" s="2">
         <v>129032</v>
       </c>
       <c r="Q283" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R283" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.3">
@@ -19479,16 +19470,16 @@
         <v>106.846473</v>
       </c>
       <c r="O284" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="P284" s="2">
         <v>202871</v>
       </c>
       <c r="Q284" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R284" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.3">
@@ -19535,16 +19526,16 @@
         <v>119.413161</v>
       </c>
       <c r="O285" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="P285" s="2">
         <v>1470262</v>
       </c>
       <c r="Q285" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="R285" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.3">
@@ -19591,16 +19582,16 @@
         <v>119.4780336</v>
       </c>
       <c r="O286" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="P286" s="2">
         <v>1470262</v>
       </c>
       <c r="Q286" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R286" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.3">
@@ -19647,16 +19638,16 @@
         <v>103.581906</v>
       </c>
       <c r="O287" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="P287" s="2">
         <v>633649</v>
       </c>
       <c r="Q287" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R287" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.3">
@@ -19703,16 +19694,16 @@
         <v>106.59227300000001</v>
       </c>
       <c r="O288" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="P288" s="2">
         <v>1240792</v>
       </c>
       <c r="Q288" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R288" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.3">
@@ -19759,16 +19750,16 @@
         <v>104.0136742466667</v>
       </c>
       <c r="O289" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="P289" s="2">
         <v>1240792</v>
       </c>
       <c r="Q289" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R289" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.3">
@@ -19815,16 +19806,16 @@
         <v>104.078385</v>
       </c>
       <c r="O290" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="P290" s="2">
         <v>1240792</v>
       </c>
       <c r="Q290" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R290" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.3">
@@ -19871,16 +19862,16 @@
         <v>106.906538</v>
       </c>
       <c r="O291" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="P291" s="2">
         <v>1240792</v>
       </c>
       <c r="Q291" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R291" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.3">
@@ -19927,16 +19918,16 @@
         <v>104.086229</v>
       </c>
       <c r="O292" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="P292" s="2">
         <v>1240792</v>
       </c>
       <c r="Q292" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R292" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.3">
@@ -19944,7 +19935,7 @@
         <v>14</v>
       </c>
       <c r="B293" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C293" t="s">
         <v>14</v>
@@ -19953,7 +19944,7 @@
         <v>543</v>
       </c>
       <c r="E293" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F293" t="s">
         <v>602</v>
@@ -19977,22 +19968,22 @@
         <v>14</v>
       </c>
       <c r="M293" s="3">
-        <v>1.0518874</v>
+        <v>0.93102499999999999</v>
       </c>
       <c r="N293" s="3">
-        <v>103.96459249999999</v>
+        <v>104.50969000000001</v>
       </c>
       <c r="O293" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="P293" s="2">
         <v>1240792</v>
       </c>
       <c r="Q293" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R293" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.3">
@@ -20000,7 +19991,7 @@
         <v>14</v>
       </c>
       <c r="B294" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C294" t="s">
         <v>14</v>
@@ -20009,7 +20000,7 @@
         <v>543</v>
       </c>
       <c r="E294" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F294" t="s">
         <v>602</v>
@@ -20033,22 +20024,22 @@
         <v>14</v>
       </c>
       <c r="M294" s="3">
-        <v>0.93102499999999999</v>
+        <v>1.0518874</v>
       </c>
       <c r="N294" s="3">
-        <v>104.50969000000001</v>
+        <v>103.96459249999999</v>
       </c>
       <c r="O294" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="P294" s="2">
         <v>1240792</v>
       </c>
       <c r="Q294" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R294" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.3">
@@ -20089,22 +20080,22 @@
         <v>14</v>
       </c>
       <c r="M295" s="3">
-        <v>1.0518874</v>
+        <v>1.1573433</v>
       </c>
       <c r="N295" s="3">
-        <v>103.96459249999999</v>
+        <v>104.1031232</v>
       </c>
       <c r="O295" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="P295" s="2">
         <v>1240792</v>
       </c>
       <c r="Q295" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R295" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.3">
@@ -20145,22 +20136,22 @@
         <v>14</v>
       </c>
       <c r="M296" s="3">
-        <v>1.1573433</v>
+        <v>1.0666800000000001</v>
       </c>
       <c r="N296" s="3">
-        <v>104.1031232</v>
+        <v>103.988912</v>
       </c>
       <c r="O296" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="P296" s="2">
         <v>1240792</v>
       </c>
       <c r="Q296" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R296" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.3">
@@ -20168,7 +20159,7 @@
         <v>14</v>
       </c>
       <c r="B297" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C297" t="s">
         <v>14</v>
@@ -20177,7 +20168,7 @@
         <v>543</v>
       </c>
       <c r="E297" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F297" t="s">
         <v>602</v>
@@ -20201,22 +20192,22 @@
         <v>14</v>
       </c>
       <c r="M297" s="3">
-        <v>1.0666800000000001</v>
+        <v>1.0374855000000001</v>
       </c>
       <c r="N297" s="3">
-        <v>103.988912</v>
+        <v>104.00041280000001</v>
       </c>
       <c r="O297" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="P297" s="2">
         <v>1240792</v>
       </c>
       <c r="Q297" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R297" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.3">
@@ -20224,7 +20215,7 @@
         <v>14</v>
       </c>
       <c r="B298" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C298" t="s">
         <v>14</v>
@@ -20233,7 +20224,7 @@
         <v>543</v>
       </c>
       <c r="E298" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="F298" t="s">
         <v>602</v>
@@ -20257,22 +20248,22 @@
         <v>14</v>
       </c>
       <c r="M298" s="3">
-        <v>1.0374855000000001</v>
+        <v>1.0518874</v>
       </c>
       <c r="N298" s="3">
-        <v>104.00041280000001</v>
+        <v>103.96459249999999</v>
       </c>
       <c r="O298" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="P298" s="2">
         <v>1240792</v>
       </c>
       <c r="Q298" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R298" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.3">
@@ -20280,7 +20271,7 @@
         <v>14</v>
       </c>
       <c r="B299" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="C299" t="s">
         <v>14</v>
@@ -20289,13 +20280,13 @@
         <v>543</v>
       </c>
       <c r="E299" t="s">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="F299" t="s">
-        <v>602</v>
+        <v>561</v>
       </c>
       <c r="G299" t="s">
-        <v>603</v>
+        <v>562</v>
       </c>
       <c r="H299" t="s">
         <v>20</v>
@@ -20304,7 +20295,7 @@
         <v>21</v>
       </c>
       <c r="J299" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K299" t="s">
         <v>14</v>
@@ -20313,22 +20304,22 @@
         <v>14</v>
       </c>
       <c r="M299" s="3">
-        <v>1.0518874</v>
+        <v>-1.6170359999999999</v>
       </c>
       <c r="N299" s="3">
-        <v>103.96459249999999</v>
+        <v>103.576891</v>
       </c>
       <c r="O299" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="P299" s="2">
-        <v>1240792</v>
+        <v>633649</v>
       </c>
       <c r="Q299" s="3" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="R299" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.3">
@@ -20336,7 +20327,7 @@
         <v>14</v>
       </c>
       <c r="B300" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="C300" t="s">
         <v>14</v>
@@ -20345,13 +20336,13 @@
         <v>543</v>
       </c>
       <c r="E300" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="F300" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="G300" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="H300" t="s">
         <v>20</v>
@@ -20369,22 +20360,22 @@
         <v>14</v>
       </c>
       <c r="M300" s="3">
-        <v>-1.6170359999999999</v>
+        <v>2.9886417000000001</v>
       </c>
       <c r="N300" s="3">
-        <v>103.576891</v>
+        <v>99.611108599999994</v>
       </c>
       <c r="O300" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="P300" s="2">
-        <v>633649</v>
+        <v>2530492</v>
       </c>
       <c r="Q300" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="R300" s="3" t="s">
         <v>1051</v>
-      </c>
-      <c r="R300" s="3" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.3">
@@ -20392,7 +20383,7 @@
         <v>14</v>
       </c>
       <c r="B301" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="C301" t="s">
         <v>14</v>
@@ -20401,7 +20392,7 @@
         <v>543</v>
       </c>
       <c r="E301" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="F301" t="s">
         <v>579</v>
@@ -20425,79 +20416,27 @@
         <v>14</v>
       </c>
       <c r="M301" s="3">
-        <v>2.9886417000000001</v>
+        <v>3.5268989999999998</v>
       </c>
       <c r="N301" s="3">
-        <v>99.611108599999994</v>
+        <v>98.796487999999997</v>
       </c>
       <c r="O301" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="P301" s="2">
         <v>2530492</v>
       </c>
       <c r="Q301" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="R301" s="3" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>14</v>
-      </c>
-      <c r="B302" t="s">
-        <v>711</v>
-      </c>
-      <c r="C302" t="s">
-        <v>14</v>
-      </c>
-      <c r="D302" t="s">
-        <v>543</v>
-      </c>
-      <c r="E302" t="s">
-        <v>712</v>
-      </c>
-      <c r="F302" t="s">
-        <v>579</v>
-      </c>
-      <c r="G302" t="s">
-        <v>580</v>
-      </c>
-      <c r="H302" t="s">
-        <v>20</v>
-      </c>
-      <c r="I302" t="s">
-        <v>21</v>
-      </c>
-      <c r="J302" t="s">
-        <v>39</v>
-      </c>
-      <c r="K302" t="s">
-        <v>14</v>
-      </c>
-      <c r="L302" t="s">
-        <v>14</v>
-      </c>
-      <c r="M302" s="3">
-        <v>3.5268989999999998</v>
-      </c>
-      <c r="N302" s="3">
-        <v>98.796487999999997</v>
-      </c>
-      <c r="O302" t="s">
-        <v>1050</v>
-      </c>
-      <c r="P302" s="2">
-        <v>2530492</v>
-      </c>
-      <c r="Q302" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="R302" s="3" t="s">
-        <v>1052</v>
-      </c>
+      <c r="M302" s="3"/>
+      <c r="N302" s="3"/>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="M303" s="3"/>
@@ -20510,10 +20449,6 @@
     <row r="305" spans="13:14" x14ac:dyDescent="0.3">
       <c r="M305" s="3"/>
       <c r="N305" s="3"/>
-    </row>
-    <row r="306" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M306" s="3"/>
-      <c r="N306" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DCE28C-A16C-4FE4-8B6D-4A2C7AF216F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34E5A52-12C2-45BA-8512-D54B5E48D352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3594,7 +3594,7 @@
       <c r="I3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K3" t="s">
@@ -3650,7 +3650,7 @@
       <c r="I4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K4" t="s">
@@ -3706,7 +3706,7 @@
       <c r="I5" t="s">
         <v>21</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K5" t="s">
@@ -3762,7 +3762,7 @@
       <c r="I6" t="s">
         <v>21</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K6" t="s">
@@ -3818,7 +3818,7 @@
       <c r="I7" t="s">
         <v>21</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K7" t="s">
@@ -3874,7 +3874,7 @@
       <c r="I8" t="s">
         <v>21</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K8" t="s">
@@ -3930,7 +3930,7 @@
       <c r="I9" t="s">
         <v>21</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K9" t="s">
@@ -3986,7 +3986,7 @@
       <c r="I10" t="s">
         <v>21</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K10" t="s">
@@ -4042,7 +4042,7 @@
       <c r="I11" t="s">
         <v>21</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K11" t="s">
@@ -4098,7 +4098,7 @@
       <c r="I12" t="s">
         <v>21</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K12" t="s">
@@ -4154,7 +4154,7 @@
       <c r="I13" t="s">
         <v>21</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K13" t="s">
@@ -4210,7 +4210,7 @@
       <c r="I14" t="s">
         <v>21</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K14" t="s">
@@ -4266,7 +4266,7 @@
       <c r="I15" t="s">
         <v>21</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K15" t="s">
@@ -4322,7 +4322,7 @@
       <c r="I16" t="s">
         <v>21</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K16" t="s">
@@ -4378,7 +4378,7 @@
       <c r="I17" t="s">
         <v>21</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K17" t="s">
@@ -4434,7 +4434,7 @@
       <c r="I18" t="s">
         <v>21</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K18" t="s">
@@ -4490,7 +4490,7 @@
       <c r="I19" t="s">
         <v>21</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K19" t="s">
@@ -4546,7 +4546,7 @@
       <c r="I20" t="s">
         <v>21</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K20" t="s">
@@ -4602,7 +4602,7 @@
       <c r="I21" t="s">
         <v>21</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K21" t="s">
@@ -4658,7 +4658,7 @@
       <c r="I22" t="s">
         <v>21</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K22" t="s">
@@ -4714,7 +4714,7 @@
       <c r="I23" t="s">
         <v>21</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K23" t="s">
@@ -4770,7 +4770,7 @@
       <c r="I24" t="s">
         <v>21</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K24" t="s">
@@ -4826,7 +4826,7 @@
       <c r="I25" t="s">
         <v>21</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K25" t="s">
@@ -4882,7 +4882,7 @@
       <c r="I26" t="s">
         <v>21</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K26" t="s">
@@ -4938,7 +4938,7 @@
       <c r="I27" t="s">
         <v>21</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K27" t="s">
@@ -4994,7 +4994,7 @@
       <c r="I28" t="s">
         <v>21</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K28" t="s">
@@ -5050,7 +5050,7 @@
       <c r="I29" t="s">
         <v>21</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K29" t="s">
@@ -5106,7 +5106,7 @@
       <c r="I30" t="s">
         <v>21</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K30" t="s">
@@ -5162,7 +5162,7 @@
       <c r="I31" t="s">
         <v>21</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K31" t="s">
@@ -5218,7 +5218,7 @@
       <c r="I32" t="s">
         <v>21</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K32" t="s">
@@ -5274,7 +5274,7 @@
       <c r="I33" t="s">
         <v>21</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K33" t="s">
@@ -5330,7 +5330,7 @@
       <c r="I34" t="s">
         <v>21</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K34" t="s">
@@ -5386,7 +5386,7 @@
       <c r="I35" t="s">
         <v>21</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K35" t="s">
@@ -5442,7 +5442,7 @@
       <c r="I36" t="s">
         <v>21</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K36" t="s">
@@ -5498,7 +5498,7 @@
       <c r="I37" t="s">
         <v>21</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K37" t="s">
@@ -5554,7 +5554,7 @@
       <c r="I38" t="s">
         <v>21</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K38" t="s">
@@ -5610,7 +5610,7 @@
       <c r="I39" t="s">
         <v>21</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K39" t="s">
@@ -5666,7 +5666,7 @@
       <c r="I40" t="s">
         <v>21</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K40" t="s">
@@ -5722,7 +5722,7 @@
       <c r="I41" t="s">
         <v>21</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K41" t="s">
@@ -5778,7 +5778,7 @@
       <c r="I42" t="s">
         <v>21</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K42" t="s">
@@ -5834,7 +5834,7 @@
       <c r="I43" t="s">
         <v>21</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K43" t="s">
@@ -5890,7 +5890,7 @@
       <c r="I44" t="s">
         <v>21</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K44" t="s">
@@ -5946,7 +5946,7 @@
       <c r="I45" t="s">
         <v>21</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K45" t="s">
@@ -6002,7 +6002,7 @@
       <c r="I46" t="s">
         <v>21</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K46" t="s">
@@ -6058,7 +6058,7 @@
       <c r="I47" t="s">
         <v>21</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K47" t="s">
@@ -6114,8 +6114,8 @@
       <c r="I48" t="s">
         <v>21</v>
       </c>
-      <c r="J48" t="s">
-        <v>42</v>
+      <c r="J48" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="K48" t="s">
         <v>14</v>
@@ -6170,7 +6170,7 @@
       <c r="I49" t="s">
         <v>21</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K49" t="s">
@@ -6226,7 +6226,7 @@
       <c r="I50" t="s">
         <v>21</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K50" t="s">
@@ -6282,7 +6282,7 @@
       <c r="I51" t="s">
         <v>21</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K51" t="s">
@@ -6338,7 +6338,7 @@
       <c r="I52" t="s">
         <v>21</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K52" t="s">
@@ -6394,7 +6394,7 @@
       <c r="I53" t="s">
         <v>21</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K53" t="s">
@@ -6450,7 +6450,7 @@
       <c r="I54" t="s">
         <v>21</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K54" t="s">
@@ -6506,7 +6506,7 @@
       <c r="I55" t="s">
         <v>21</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K55" t="s">
@@ -6562,7 +6562,7 @@
       <c r="I56" t="s">
         <v>21</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K56" t="s">
@@ -6618,7 +6618,7 @@
       <c r="I57" t="s">
         <v>21</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K57" t="s">
@@ -6674,7 +6674,7 @@
       <c r="I58" t="s">
         <v>21</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K58" t="s">
@@ -6730,7 +6730,7 @@
       <c r="I59" t="s">
         <v>21</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K59" t="s">
@@ -6786,7 +6786,7 @@
       <c r="I60" t="s">
         <v>21</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K60" t="s">
@@ -6842,7 +6842,7 @@
       <c r="I61" t="s">
         <v>21</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K61" t="s">
@@ -6898,7 +6898,7 @@
       <c r="I62" t="s">
         <v>21</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K62" t="s">
@@ -6954,7 +6954,7 @@
       <c r="I63" t="s">
         <v>21</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K63" t="s">
@@ -7010,7 +7010,7 @@
       <c r="I64" t="s">
         <v>21</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K64" t="s">
@@ -7066,7 +7066,7 @@
       <c r="I65" t="s">
         <v>21</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K65" t="s">
@@ -7122,8 +7122,8 @@
       <c r="I66" t="s">
         <v>21</v>
       </c>
-      <c r="J66" t="s">
-        <v>14</v>
+      <c r="J66" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="K66" t="s">
         <v>14</v>
@@ -7178,7 +7178,7 @@
       <c r="I67" t="s">
         <v>21</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K67" t="s">
@@ -7234,7 +7234,7 @@
       <c r="I68" t="s">
         <v>21</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K68" t="s">
@@ -7290,7 +7290,7 @@
       <c r="I69" t="s">
         <v>21</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K69" t="s">
@@ -7346,7 +7346,7 @@
       <c r="I70" t="s">
         <v>21</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K70" t="s">
@@ -7402,7 +7402,7 @@
       <c r="I71" t="s">
         <v>21</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="3" t="s">
         <v>214</v>
       </c>
       <c r="K71" t="s">
@@ -7458,7 +7458,7 @@
       <c r="I72" t="s">
         <v>21</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K72" t="s">
@@ -7514,7 +7514,7 @@
       <c r="I73" t="s">
         <v>21</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K73" t="s">
@@ -7570,8 +7570,8 @@
       <c r="I74" t="s">
         <v>21</v>
       </c>
-      <c r="J74" t="s">
-        <v>14</v>
+      <c r="J74" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="K74" t="s">
         <v>14</v>
@@ -7626,7 +7626,7 @@
       <c r="I75" t="s">
         <v>21</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K75" t="s">
@@ -7682,7 +7682,7 @@
       <c r="I76" t="s">
         <v>21</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K76" t="s">
@@ -7738,7 +7738,7 @@
       <c r="I77" t="s">
         <v>21</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K77" t="s">
@@ -7794,7 +7794,7 @@
       <c r="I78" t="s">
         <v>21</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K78" t="s">
@@ -7850,7 +7850,7 @@
       <c r="I79" t="s">
         <v>21</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K79" t="s">
@@ -7906,7 +7906,7 @@
       <c r="I80" t="s">
         <v>21</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K80" t="s">
@@ -7962,7 +7962,7 @@
       <c r="I81" t="s">
         <v>21</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K81" t="s">
@@ -8018,7 +8018,7 @@
       <c r="I82" t="s">
         <v>21</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J82" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K82" t="s">
@@ -8074,7 +8074,7 @@
       <c r="I83" t="s">
         <v>21</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K83" t="s">
@@ -8130,7 +8130,7 @@
       <c r="I84" t="s">
         <v>21</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K84" t="s">
@@ -8186,7 +8186,7 @@
       <c r="I85" t="s">
         <v>21</v>
       </c>
-      <c r="J85" t="s">
+      <c r="J85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K85" t="s">
@@ -8242,7 +8242,7 @@
       <c r="I86" t="s">
         <v>21</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K86" t="s">
@@ -8298,7 +8298,7 @@
       <c r="I87" t="s">
         <v>21</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K87" t="s">
@@ -8354,7 +8354,7 @@
       <c r="I88" t="s">
         <v>21</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K88" t="s">
@@ -8410,7 +8410,7 @@
       <c r="I89" t="s">
         <v>21</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K89" t="s">
@@ -8466,7 +8466,7 @@
       <c r="I90" t="s">
         <v>21</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K90" t="s">
@@ -8522,7 +8522,7 @@
       <c r="I91" t="s">
         <v>21</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K91" t="s">
@@ -8578,7 +8578,7 @@
       <c r="I92" t="s">
         <v>21</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K92" t="s">
@@ -8634,7 +8634,7 @@
       <c r="I93" t="s">
         <v>21</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K93" t="s">
@@ -8690,7 +8690,7 @@
       <c r="I94" t="s">
         <v>21</v>
       </c>
-      <c r="J94" t="s">
+      <c r="J94" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K94" t="s">
@@ -8746,7 +8746,7 @@
       <c r="I95" t="s">
         <v>21</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J95" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K95" t="s">
@@ -8802,7 +8802,7 @@
       <c r="I96" t="s">
         <v>21</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J96" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K96" t="s">
@@ -8858,7 +8858,7 @@
       <c r="I97" t="s">
         <v>21</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J97" s="3" t="s">
         <v>214</v>
       </c>
       <c r="K97" t="s">
@@ -8914,7 +8914,7 @@
       <c r="I98" t="s">
         <v>21</v>
       </c>
-      <c r="J98" t="s">
+      <c r="J98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K98" t="s">
@@ -8970,7 +8970,7 @@
       <c r="I99" t="s">
         <v>21</v>
       </c>
-      <c r="J99" t="s">
+      <c r="J99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K99" t="s">
@@ -9026,7 +9026,7 @@
       <c r="I100" t="s">
         <v>21</v>
       </c>
-      <c r="J100" t="s">
+      <c r="J100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K100" t="s">
@@ -9082,7 +9082,7 @@
       <c r="I101" t="s">
         <v>21</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K101" t="s">
@@ -9138,7 +9138,7 @@
       <c r="I102" t="s">
         <v>21</v>
       </c>
-      <c r="J102" t="s">
+      <c r="J102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K102" t="s">
@@ -9194,7 +9194,7 @@
       <c r="I103" t="s">
         <v>21</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J103" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K103" t="s">
@@ -9250,7 +9250,7 @@
       <c r="I104" t="s">
         <v>21</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K104" t="s">
@@ -9306,7 +9306,7 @@
       <c r="I105" t="s">
         <v>21</v>
       </c>
-      <c r="J105" t="s">
+      <c r="J105" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K105" t="s">
@@ -9362,7 +9362,7 @@
       <c r="I106" t="s">
         <v>21</v>
       </c>
-      <c r="J106" t="s">
+      <c r="J106" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K106" t="s">
@@ -9418,7 +9418,7 @@
       <c r="I107" t="s">
         <v>21</v>
       </c>
-      <c r="J107" t="s">
+      <c r="J107" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K107" t="s">
@@ -9474,7 +9474,7 @@
       <c r="I108" t="s">
         <v>21</v>
       </c>
-      <c r="J108" t="s">
+      <c r="J108" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K108" t="s">
@@ -9530,7 +9530,7 @@
       <c r="I109" t="s">
         <v>21</v>
       </c>
-      <c r="J109" t="s">
+      <c r="J109" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K109" t="s">
@@ -9586,7 +9586,7 @@
       <c r="I110" t="s">
         <v>21</v>
       </c>
-      <c r="J110" t="s">
+      <c r="J110" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K110" t="s">
@@ -9642,8 +9642,8 @@
       <c r="I111" t="s">
         <v>21</v>
       </c>
-      <c r="J111" t="s">
-        <v>14</v>
+      <c r="J111" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="K111" t="s">
         <v>14</v>
@@ -9698,7 +9698,7 @@
       <c r="I112" t="s">
         <v>21</v>
       </c>
-      <c r="J112" t="s">
+      <c r="J112" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K112" t="s">
@@ -9754,7 +9754,7 @@
       <c r="I113" t="s">
         <v>21</v>
       </c>
-      <c r="J113" t="s">
+      <c r="J113" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K113" t="s">
@@ -9810,7 +9810,7 @@
       <c r="I114" t="s">
         <v>21</v>
       </c>
-      <c r="J114" t="s">
+      <c r="J114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K114" t="s">
@@ -9866,7 +9866,7 @@
       <c r="I115" t="s">
         <v>21</v>
       </c>
-      <c r="J115" t="s">
+      <c r="J115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K115" t="s">
@@ -9922,7 +9922,7 @@
       <c r="I116" t="s">
         <v>21</v>
       </c>
-      <c r="J116" t="s">
+      <c r="J116" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K116" t="s">
@@ -9978,7 +9978,7 @@
       <c r="I117" t="s">
         <v>21</v>
       </c>
-      <c r="J117" t="s">
+      <c r="J117" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K117" t="s">
@@ -10034,7 +10034,7 @@
       <c r="I118" t="s">
         <v>21</v>
       </c>
-      <c r="J118" t="s">
+      <c r="J118" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K118" t="s">
@@ -10090,7 +10090,7 @@
       <c r="I119" t="s">
         <v>21</v>
       </c>
-      <c r="J119" t="s">
+      <c r="J119" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K119" t="s">
@@ -10146,7 +10146,7 @@
       <c r="I120" t="s">
         <v>21</v>
       </c>
-      <c r="J120" t="s">
+      <c r="J120" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K120" t="s">
@@ -10202,7 +10202,7 @@
       <c r="I121" t="s">
         <v>21</v>
       </c>
-      <c r="J121" t="s">
+      <c r="J121" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K121" t="s">
@@ -10258,7 +10258,7 @@
       <c r="I122" t="s">
         <v>21</v>
       </c>
-      <c r="J122" t="s">
+      <c r="J122" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K122" t="s">
@@ -10314,7 +10314,7 @@
       <c r="I123" t="s">
         <v>21</v>
       </c>
-      <c r="J123" t="s">
+      <c r="J123" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K123" t="s">
@@ -10370,7 +10370,7 @@
       <c r="I124" t="s">
         <v>21</v>
       </c>
-      <c r="J124" t="s">
+      <c r="J124" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K124" t="s">
@@ -10426,7 +10426,7 @@
       <c r="I125" t="s">
         <v>21</v>
       </c>
-      <c r="J125" t="s">
+      <c r="J125" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K125" t="s">
@@ -10482,7 +10482,7 @@
       <c r="I126" t="s">
         <v>21</v>
       </c>
-      <c r="J126" t="s">
+      <c r="J126" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K126" t="s">
@@ -10538,7 +10538,7 @@
       <c r="I127" t="s">
         <v>21</v>
       </c>
-      <c r="J127" t="s">
+      <c r="J127" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K127" t="s">
@@ -10594,7 +10594,7 @@
       <c r="I128" t="s">
         <v>21</v>
       </c>
-      <c r="J128" t="s">
+      <c r="J128" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K128" t="s">
@@ -10650,7 +10650,7 @@
       <c r="I129" t="s">
         <v>21</v>
       </c>
-      <c r="J129" t="s">
+      <c r="J129" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K129" t="s">
@@ -10706,7 +10706,7 @@
       <c r="I130" t="s">
         <v>21</v>
       </c>
-      <c r="J130" t="s">
+      <c r="J130" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K130" t="s">
@@ -10762,7 +10762,7 @@
       <c r="I131" t="s">
         <v>21</v>
       </c>
-      <c r="J131" t="s">
+      <c r="J131" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K131" t="s">
@@ -10818,7 +10818,7 @@
       <c r="I132" t="s">
         <v>21</v>
       </c>
-      <c r="J132" t="s">
+      <c r="J132" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K132" t="s">
@@ -10874,7 +10874,7 @@
       <c r="I133" t="s">
         <v>21</v>
       </c>
-      <c r="J133" t="s">
+      <c r="J133" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K133" t="s">
@@ -10930,7 +10930,7 @@
       <c r="I134" t="s">
         <v>21</v>
       </c>
-      <c r="J134" t="s">
+      <c r="J134" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K134" t="s">
@@ -10986,7 +10986,7 @@
       <c r="I135" t="s">
         <v>21</v>
       </c>
-      <c r="J135" t="s">
+      <c r="J135" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K135" t="s">
@@ -11042,7 +11042,7 @@
       <c r="I136" t="s">
         <v>21</v>
       </c>
-      <c r="J136" t="s">
+      <c r="J136" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K136" t="s">
@@ -11098,7 +11098,7 @@
       <c r="I137" t="s">
         <v>21</v>
       </c>
-      <c r="J137" t="s">
+      <c r="J137" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K137" t="s">
@@ -11154,7 +11154,7 @@
       <c r="I138" t="s">
         <v>21</v>
       </c>
-      <c r="J138" t="s">
+      <c r="J138" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K138" t="s">
@@ -11210,7 +11210,7 @@
       <c r="I139" t="s">
         <v>21</v>
       </c>
-      <c r="J139" t="s">
+      <c r="J139" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K139" t="s">
@@ -11266,7 +11266,7 @@
       <c r="I140" t="s">
         <v>21</v>
       </c>
-      <c r="J140" t="s">
+      <c r="J140" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K140" t="s">
@@ -11322,7 +11322,7 @@
       <c r="I141" t="s">
         <v>21</v>
       </c>
-      <c r="J141" t="s">
+      <c r="J141" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K141" t="s">
@@ -11378,7 +11378,7 @@
       <c r="I142" t="s">
         <v>21</v>
       </c>
-      <c r="J142" t="s">
+      <c r="J142" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K142" t="s">
@@ -11434,7 +11434,7 @@
       <c r="I143" t="s">
         <v>21</v>
       </c>
-      <c r="J143" t="s">
+      <c r="J143" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K143" t="s">
@@ -11490,7 +11490,7 @@
       <c r="I144" t="s">
         <v>21</v>
       </c>
-      <c r="J144" t="s">
+      <c r="J144" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K144" t="s">
@@ -11546,7 +11546,7 @@
       <c r="I145" t="s">
         <v>21</v>
       </c>
-      <c r="J145" t="s">
+      <c r="J145" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K145" t="s">
@@ -11602,7 +11602,7 @@
       <c r="I146" t="s">
         <v>21</v>
       </c>
-      <c r="J146" t="s">
+      <c r="J146" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K146" t="s">
@@ -11658,7 +11658,7 @@
       <c r="I147" t="s">
         <v>21</v>
       </c>
-      <c r="J147" t="s">
+      <c r="J147" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K147" t="s">
@@ -11714,7 +11714,7 @@
       <c r="I148" t="s">
         <v>21</v>
       </c>
-      <c r="J148" t="s">
+      <c r="J148" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K148" t="s">
@@ -11770,7 +11770,7 @@
       <c r="I149" t="s">
         <v>21</v>
       </c>
-      <c r="J149" t="s">
+      <c r="J149" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K149" t="s">
@@ -11826,7 +11826,7 @@
       <c r="I150" t="s">
         <v>21</v>
       </c>
-      <c r="J150" t="s">
+      <c r="J150" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K150" t="s">
@@ -11882,7 +11882,7 @@
       <c r="I151" t="s">
         <v>21</v>
       </c>
-      <c r="J151" t="s">
+      <c r="J151" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K151" t="s">
@@ -11938,7 +11938,7 @@
       <c r="I152" t="s">
         <v>21</v>
       </c>
-      <c r="J152" t="s">
+      <c r="J152" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K152" t="s">
@@ -11994,7 +11994,7 @@
       <c r="I153" t="s">
         <v>21</v>
       </c>
-      <c r="J153" t="s">
+      <c r="J153" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K153" t="s">
@@ -12050,7 +12050,7 @@
       <c r="I154" t="s">
         <v>21</v>
       </c>
-      <c r="J154" t="s">
+      <c r="J154" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K154" t="s">
@@ -12106,7 +12106,7 @@
       <c r="I155" t="s">
         <v>21</v>
       </c>
-      <c r="J155" t="s">
+      <c r="J155" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K155" t="s">
@@ -12162,7 +12162,7 @@
       <c r="I156" t="s">
         <v>21</v>
       </c>
-      <c r="J156" t="s">
+      <c r="J156" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K156" t="s">
@@ -12218,7 +12218,7 @@
       <c r="I157" t="s">
         <v>21</v>
       </c>
-      <c r="J157" t="s">
+      <c r="J157" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K157" t="s">
@@ -12274,7 +12274,7 @@
       <c r="I158" t="s">
         <v>21</v>
       </c>
-      <c r="J158" t="s">
+      <c r="J158" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K158" t="s">
@@ -12330,7 +12330,7 @@
       <c r="I159" t="s">
         <v>21</v>
       </c>
-      <c r="J159" t="s">
+      <c r="J159" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K159" t="s">
@@ -12386,7 +12386,7 @@
       <c r="I160" t="s">
         <v>21</v>
       </c>
-      <c r="J160" t="s">
+      <c r="J160" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K160" t="s">
@@ -12442,7 +12442,7 @@
       <c r="I161" t="s">
         <v>21</v>
       </c>
-      <c r="J161" t="s">
+      <c r="J161" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K161" t="s">
@@ -12498,7 +12498,7 @@
       <c r="I162" t="s">
         <v>21</v>
       </c>
-      <c r="J162" t="s">
+      <c r="J162" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K162" t="s">
@@ -12554,7 +12554,7 @@
       <c r="I163" t="s">
         <v>21</v>
       </c>
-      <c r="J163" t="s">
+      <c r="J163" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K163" t="s">
@@ -12610,7 +12610,7 @@
       <c r="I164" t="s">
         <v>21</v>
       </c>
-      <c r="J164" t="s">
+      <c r="J164" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K164" t="s">
@@ -12666,7 +12666,7 @@
       <c r="I165" t="s">
         <v>21</v>
       </c>
-      <c r="J165" t="s">
+      <c r="J165" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K165" t="s">
@@ -12722,7 +12722,7 @@
       <c r="I166" t="s">
         <v>21</v>
       </c>
-      <c r="J166" t="s">
+      <c r="J166" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K166" t="s">
@@ -12778,7 +12778,7 @@
       <c r="I167" t="s">
         <v>21</v>
       </c>
-      <c r="J167" t="s">
+      <c r="J167" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K167" t="s">
@@ -12834,7 +12834,7 @@
       <c r="I168" t="s">
         <v>21</v>
       </c>
-      <c r="J168" t="s">
+      <c r="J168" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K168" t="s">
@@ -12890,7 +12890,7 @@
       <c r="I169" t="s">
         <v>21</v>
       </c>
-      <c r="J169" t="s">
+      <c r="J169" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K169" t="s">
@@ -12946,7 +12946,7 @@
       <c r="I170" t="s">
         <v>21</v>
       </c>
-      <c r="J170" t="s">
+      <c r="J170" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K170" t="s">
@@ -13002,7 +13002,7 @@
       <c r="I171" t="s">
         <v>21</v>
       </c>
-      <c r="J171" t="s">
+      <c r="J171" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K171" t="s">
@@ -13058,7 +13058,7 @@
       <c r="I172" t="s">
         <v>21</v>
       </c>
-      <c r="J172" t="s">
+      <c r="J172" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K172" t="s">
@@ -13114,7 +13114,7 @@
       <c r="I173" t="s">
         <v>21</v>
       </c>
-      <c r="J173" t="s">
+      <c r="J173" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K173" t="s">
@@ -13170,7 +13170,7 @@
       <c r="I174" t="s">
         <v>21</v>
       </c>
-      <c r="J174" t="s">
+      <c r="J174" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K174" t="s">
@@ -13226,7 +13226,7 @@
       <c r="I175" t="s">
         <v>21</v>
       </c>
-      <c r="J175" t="s">
+      <c r="J175" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K175" t="s">
@@ -13282,7 +13282,7 @@
       <c r="I176" t="s">
         <v>21</v>
       </c>
-      <c r="J176" t="s">
+      <c r="J176" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K176" t="s">
@@ -13338,7 +13338,7 @@
       <c r="I177" t="s">
         <v>21</v>
       </c>
-      <c r="J177" t="s">
+      <c r="J177" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K177" t="s">
@@ -13394,7 +13394,7 @@
       <c r="I178" t="s">
         <v>21</v>
       </c>
-      <c r="J178" t="s">
+      <c r="J178" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K178" t="s">
@@ -13450,7 +13450,7 @@
       <c r="I179" t="s">
         <v>21</v>
       </c>
-      <c r="J179" t="s">
+      <c r="J179" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K179" t="s">
@@ -13506,7 +13506,7 @@
       <c r="I180" t="s">
         <v>21</v>
       </c>
-      <c r="J180" t="s">
+      <c r="J180" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K180" t="s">
@@ -13562,7 +13562,7 @@
       <c r="I181" t="s">
         <v>21</v>
       </c>
-      <c r="J181" t="s">
+      <c r="J181" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K181" t="s">
@@ -13618,7 +13618,7 @@
       <c r="I182" t="s">
         <v>21</v>
       </c>
-      <c r="J182" t="s">
+      <c r="J182" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
@@ -13674,7 +13674,7 @@
       <c r="I183" t="s">
         <v>21</v>
       </c>
-      <c r="J183" t="s">
+      <c r="J183" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K183" t="s">
@@ -13730,7 +13730,7 @@
       <c r="I184" t="s">
         <v>21</v>
       </c>
-      <c r="J184" t="s">
+      <c r="J184" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K184" t="s">
@@ -13786,7 +13786,7 @@
       <c r="I185" t="s">
         <v>21</v>
       </c>
-      <c r="J185" t="s">
+      <c r="J185" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K185" t="s">
@@ -13842,7 +13842,7 @@
       <c r="I186" t="s">
         <v>21</v>
       </c>
-      <c r="J186" t="s">
+      <c r="J186" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K186" t="s">
@@ -13898,7 +13898,7 @@
       <c r="I187" t="s">
         <v>21</v>
       </c>
-      <c r="J187" t="s">
+      <c r="J187" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K187" t="s">
@@ -13954,7 +13954,7 @@
       <c r="I188" t="s">
         <v>21</v>
       </c>
-      <c r="J188" t="s">
+      <c r="J188" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K188" t="s">
@@ -14010,7 +14010,7 @@
       <c r="I189" t="s">
         <v>21</v>
       </c>
-      <c r="J189" t="s">
+      <c r="J189" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K189" t="s">
@@ -14066,7 +14066,7 @@
       <c r="I190" t="s">
         <v>21</v>
       </c>
-      <c r="J190" t="s">
+      <c r="J190" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K190" t="s">
@@ -14122,7 +14122,7 @@
       <c r="I191" t="s">
         <v>21</v>
       </c>
-      <c r="J191" t="s">
+      <c r="J191" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K191" t="s">
@@ -14178,7 +14178,7 @@
       <c r="I192" t="s">
         <v>21</v>
       </c>
-      <c r="J192" t="s">
+      <c r="J192" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K192" t="s">
@@ -14234,7 +14234,7 @@
       <c r="I193" t="s">
         <v>21</v>
       </c>
-      <c r="J193" t="s">
+      <c r="J193" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K193" t="s">
@@ -14290,7 +14290,7 @@
       <c r="I194" t="s">
         <v>21</v>
       </c>
-      <c r="J194" t="s">
+      <c r="J194" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K194" t="s">
@@ -14346,7 +14346,7 @@
       <c r="I195" t="s">
         <v>21</v>
       </c>
-      <c r="J195" t="s">
+      <c r="J195" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K195" t="s">
@@ -14402,7 +14402,7 @@
       <c r="I196" t="s">
         <v>21</v>
       </c>
-      <c r="J196" t="s">
+      <c r="J196" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K196" t="s">
@@ -14458,7 +14458,7 @@
       <c r="I197" t="s">
         <v>21</v>
       </c>
-      <c r="J197" t="s">
+      <c r="J197" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K197" t="s">
@@ -14514,7 +14514,7 @@
       <c r="I198" t="s">
         <v>21</v>
       </c>
-      <c r="J198" t="s">
+      <c r="J198" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K198" t="s">
@@ -14570,7 +14570,7 @@
       <c r="I199" t="s">
         <v>21</v>
       </c>
-      <c r="J199" t="s">
+      <c r="J199" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K199" t="s">
@@ -14626,7 +14626,7 @@
       <c r="I200" t="s">
         <v>21</v>
       </c>
-      <c r="J200" t="s">
+      <c r="J200" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K200" t="s">
@@ -14682,7 +14682,7 @@
       <c r="I201" t="s">
         <v>21</v>
       </c>
-      <c r="J201" t="s">
+      <c r="J201" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K201" t="s">
@@ -14738,7 +14738,7 @@
       <c r="I202" t="s">
         <v>21</v>
       </c>
-      <c r="J202" t="s">
+      <c r="J202" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K202" t="s">
@@ -14794,7 +14794,7 @@
       <c r="I203" t="s">
         <v>21</v>
       </c>
-      <c r="J203" t="s">
+      <c r="J203" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K203" t="s">
@@ -14850,7 +14850,7 @@
       <c r="I204" t="s">
         <v>21</v>
       </c>
-      <c r="J204" t="s">
+      <c r="J204" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K204" t="s">
@@ -14906,7 +14906,7 @@
       <c r="I205" t="s">
         <v>21</v>
       </c>
-      <c r="J205" t="s">
+      <c r="J205" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K205" t="s">
@@ -14962,7 +14962,7 @@
       <c r="I206" t="s">
         <v>21</v>
       </c>
-      <c r="J206" t="s">
+      <c r="J206" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K206" t="s">
@@ -15018,7 +15018,7 @@
       <c r="I207" t="s">
         <v>21</v>
       </c>
-      <c r="J207" t="s">
+      <c r="J207" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K207" t="s">
@@ -15074,7 +15074,7 @@
       <c r="I208" t="s">
         <v>21</v>
       </c>
-      <c r="J208" t="s">
+      <c r="J208" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K208" t="s">
@@ -15130,7 +15130,7 @@
       <c r="I209" t="s">
         <v>21</v>
       </c>
-      <c r="J209" t="s">
+      <c r="J209" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K209" t="s">
@@ -15186,7 +15186,7 @@
       <c r="I210" t="s">
         <v>21</v>
       </c>
-      <c r="J210" t="s">
+      <c r="J210" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K210" t="s">
@@ -15242,7 +15242,7 @@
       <c r="I211" t="s">
         <v>21</v>
       </c>
-      <c r="J211" t="s">
+      <c r="J211" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K211" t="s">
@@ -15298,7 +15298,7 @@
       <c r="I212" t="s">
         <v>21</v>
       </c>
-      <c r="J212" t="s">
+      <c r="J212" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K212" t="s">
@@ -15354,7 +15354,7 @@
       <c r="I213" t="s">
         <v>21</v>
       </c>
-      <c r="J213" t="s">
+      <c r="J213" s="3" t="s">
         <v>205</v>
       </c>
       <c r="K213" t="s">
@@ -15410,7 +15410,7 @@
       <c r="I214" t="s">
         <v>21</v>
       </c>
-      <c r="J214" t="s">
+      <c r="J214" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K214" t="s">
@@ -15466,7 +15466,7 @@
       <c r="I215" t="s">
         <v>21</v>
       </c>
-      <c r="J215" t="s">
+      <c r="J215" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K215" t="s">
@@ -15522,7 +15522,7 @@
       <c r="I216" t="s">
         <v>21</v>
       </c>
-      <c r="J216" t="s">
+      <c r="J216" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K216" t="s">
@@ -15578,7 +15578,7 @@
       <c r="I217" t="s">
         <v>21</v>
       </c>
-      <c r="J217" t="s">
+      <c r="J217" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K217" t="s">
@@ -15634,7 +15634,7 @@
       <c r="I218" t="s">
         <v>21</v>
       </c>
-      <c r="J218" t="s">
+      <c r="J218" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K218" t="s">
@@ -15690,7 +15690,7 @@
       <c r="I219" t="s">
         <v>21</v>
       </c>
-      <c r="J219" t="s">
+      <c r="J219" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K219" t="s">
@@ -15746,7 +15746,7 @@
       <c r="I220" t="s">
         <v>21</v>
       </c>
-      <c r="J220" t="s">
+      <c r="J220" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K220" t="s">
@@ -15802,7 +15802,7 @@
       <c r="I221" t="s">
         <v>21</v>
       </c>
-      <c r="J221" t="s">
+      <c r="J221" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K221" t="s">
@@ -15858,7 +15858,7 @@
       <c r="I222" t="s">
         <v>21</v>
       </c>
-      <c r="J222" t="s">
+      <c r="J222" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K222" t="s">
@@ -15914,7 +15914,7 @@
       <c r="I223" t="s">
         <v>21</v>
       </c>
-      <c r="J223" t="s">
+      <c r="J223" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K223" t="s">
@@ -15970,7 +15970,7 @@
       <c r="I224" t="s">
         <v>21</v>
       </c>
-      <c r="J224" t="s">
+      <c r="J224" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K224" t="s">
@@ -16026,7 +16026,7 @@
       <c r="I225" t="s">
         <v>21</v>
       </c>
-      <c r="J225" t="s">
+      <c r="J225" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K225" t="s">
@@ -16082,7 +16082,7 @@
       <c r="I226" t="s">
         <v>21</v>
       </c>
-      <c r="J226" t="s">
+      <c r="J226" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K226" t="s">
@@ -16138,7 +16138,7 @@
       <c r="I227" t="s">
         <v>21</v>
       </c>
-      <c r="J227" t="s">
+      <c r="J227" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K227" t="s">
@@ -16194,7 +16194,7 @@
       <c r="I228" t="s">
         <v>21</v>
       </c>
-      <c r="J228" t="s">
+      <c r="J228" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K228" t="s">
@@ -16250,7 +16250,7 @@
       <c r="I229" t="s">
         <v>21</v>
       </c>
-      <c r="J229" t="s">
+      <c r="J229" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K229" t="s">
@@ -16306,7 +16306,7 @@
       <c r="I230" t="s">
         <v>21</v>
       </c>
-      <c r="J230" t="s">
+      <c r="J230" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K230" t="s">
@@ -16362,7 +16362,7 @@
       <c r="I231" t="s">
         <v>21</v>
       </c>
-      <c r="J231" t="s">
+      <c r="J231" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K231" t="s">
@@ -16418,7 +16418,7 @@
       <c r="I232" t="s">
         <v>21</v>
       </c>
-      <c r="J232" t="s">
+      <c r="J232" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K232" t="s">
@@ -16474,7 +16474,7 @@
       <c r="I233" t="s">
         <v>21</v>
       </c>
-      <c r="J233" t="s">
+      <c r="J233" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K233" t="s">
@@ -16530,7 +16530,7 @@
       <c r="I234" t="s">
         <v>21</v>
       </c>
-      <c r="J234" t="s">
+      <c r="J234" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K234" t="s">
@@ -16586,7 +16586,7 @@
       <c r="I235" t="s">
         <v>21</v>
       </c>
-      <c r="J235" t="s">
+      <c r="J235" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K235" t="s">
@@ -16642,7 +16642,7 @@
       <c r="I236" t="s">
         <v>21</v>
       </c>
-      <c r="J236" t="s">
+      <c r="J236" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K236" t="s">
@@ -16698,7 +16698,7 @@
       <c r="I237" t="s">
         <v>21</v>
       </c>
-      <c r="J237" t="s">
+      <c r="J237" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K237" t="s">
@@ -16754,7 +16754,7 @@
       <c r="I238" t="s">
         <v>21</v>
       </c>
-      <c r="J238" t="s">
+      <c r="J238" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K238" t="s">
@@ -16810,7 +16810,7 @@
       <c r="I239" t="s">
         <v>21</v>
       </c>
-      <c r="J239" t="s">
+      <c r="J239" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K239" t="s">
@@ -16866,7 +16866,7 @@
       <c r="I240" t="s">
         <v>21</v>
       </c>
-      <c r="J240" t="s">
+      <c r="J240" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K240" t="s">
@@ -16922,7 +16922,7 @@
       <c r="I241" t="s">
         <v>21</v>
       </c>
-      <c r="J241" t="s">
+      <c r="J241" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K241" t="s">
@@ -16978,7 +16978,7 @@
       <c r="I242" t="s">
         <v>21</v>
       </c>
-      <c r="J242" t="s">
+      <c r="J242" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K242" t="s">
@@ -17034,7 +17034,7 @@
       <c r="I243" t="s">
         <v>21</v>
       </c>
-      <c r="J243" t="s">
+      <c r="J243" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K243" t="s">
@@ -17090,7 +17090,7 @@
       <c r="I244" t="s">
         <v>21</v>
       </c>
-      <c r="J244" t="s">
+      <c r="J244" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K244" t="s">
@@ -17146,7 +17146,7 @@
       <c r="I245" t="s">
         <v>21</v>
       </c>
-      <c r="J245" t="s">
+      <c r="J245" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K245" t="s">
@@ -17202,7 +17202,7 @@
       <c r="I246" t="s">
         <v>21</v>
       </c>
-      <c r="J246" t="s">
+      <c r="J246" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K246" t="s">
@@ -17258,7 +17258,7 @@
       <c r="I247" t="s">
         <v>21</v>
       </c>
-      <c r="J247" t="s">
+      <c r="J247" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K247" t="s">
@@ -17314,7 +17314,7 @@
       <c r="I248" t="s">
         <v>21</v>
       </c>
-      <c r="J248" t="s">
+      <c r="J248" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K248" t="s">
@@ -17370,7 +17370,7 @@
       <c r="I249" t="s">
         <v>21</v>
       </c>
-      <c r="J249" t="s">
+      <c r="J249" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K249" t="s">
@@ -17426,7 +17426,7 @@
       <c r="I250" t="s">
         <v>21</v>
       </c>
-      <c r="J250" t="s">
+      <c r="J250" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K250" t="s">
@@ -17482,7 +17482,7 @@
       <c r="I251" t="s">
         <v>21</v>
       </c>
-      <c r="J251" t="s">
+      <c r="J251" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K251" t="s">
@@ -17538,7 +17538,7 @@
       <c r="I252" t="s">
         <v>21</v>
       </c>
-      <c r="J252" t="s">
+      <c r="J252" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K252" t="s">
@@ -17594,7 +17594,7 @@
       <c r="I253" t="s">
         <v>21</v>
       </c>
-      <c r="J253" t="s">
+      <c r="J253" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K253" t="s">
@@ -17650,7 +17650,7 @@
       <c r="I254" t="s">
         <v>21</v>
       </c>
-      <c r="J254" t="s">
+      <c r="J254" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K254" t="s">
@@ -17706,7 +17706,7 @@
       <c r="I255" t="s">
         <v>21</v>
       </c>
-      <c r="J255" t="s">
+      <c r="J255" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K255" t="s">
@@ -17762,7 +17762,7 @@
       <c r="I256" t="s">
         <v>21</v>
       </c>
-      <c r="J256" t="s">
+      <c r="J256" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K256" t="s">
@@ -17818,7 +17818,7 @@
       <c r="I257" t="s">
         <v>21</v>
       </c>
-      <c r="J257" t="s">
+      <c r="J257" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K257" t="s">
@@ -17874,7 +17874,7 @@
       <c r="I258" t="s">
         <v>21</v>
       </c>
-      <c r="J258" t="s">
+      <c r="J258" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K258" t="s">
@@ -17930,7 +17930,7 @@
       <c r="I259" t="s">
         <v>21</v>
       </c>
-      <c r="J259" t="s">
+      <c r="J259" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K259" t="s">
@@ -17986,7 +17986,7 @@
       <c r="I260" t="s">
         <v>21</v>
       </c>
-      <c r="J260" t="s">
+      <c r="J260" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K260" t="s">
@@ -18042,7 +18042,7 @@
       <c r="I261" t="s">
         <v>21</v>
       </c>
-      <c r="J261" t="s">
+      <c r="J261" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K261" t="s">
@@ -18098,7 +18098,7 @@
       <c r="I262" t="s">
         <v>21</v>
       </c>
-      <c r="J262" t="s">
+      <c r="J262" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K262" t="s">
@@ -18154,7 +18154,7 @@
       <c r="I263" t="s">
         <v>21</v>
       </c>
-      <c r="J263" t="s">
+      <c r="J263" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K263" t="s">
@@ -18210,7 +18210,7 @@
       <c r="I264" t="s">
         <v>21</v>
       </c>
-      <c r="J264" t="s">
+      <c r="J264" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K264" t="s">
@@ -18266,7 +18266,7 @@
       <c r="I265" t="s">
         <v>21</v>
       </c>
-      <c r="J265" t="s">
+      <c r="J265" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K265" t="s">
@@ -18322,7 +18322,7 @@
       <c r="I266" t="s">
         <v>21</v>
       </c>
-      <c r="J266" t="s">
+      <c r="J266" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K266" t="s">
@@ -18378,7 +18378,7 @@
       <c r="I267" t="s">
         <v>21</v>
       </c>
-      <c r="J267" t="s">
+      <c r="J267" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K267" t="s">
@@ -18434,7 +18434,7 @@
       <c r="I268" t="s">
         <v>21</v>
       </c>
-      <c r="J268" t="s">
+      <c r="J268" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K268" t="s">
@@ -18490,7 +18490,7 @@
       <c r="I269" t="s">
         <v>21</v>
       </c>
-      <c r="J269" t="s">
+      <c r="J269" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K269" t="s">
@@ -18546,7 +18546,7 @@
       <c r="I270" t="s">
         <v>21</v>
       </c>
-      <c r="J270" t="s">
+      <c r="J270" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K270" t="s">
@@ -18602,7 +18602,7 @@
       <c r="I271" t="s">
         <v>21</v>
       </c>
-      <c r="J271" t="s">
+      <c r="J271" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K271" t="s">
@@ -18658,7 +18658,7 @@
       <c r="I272" t="s">
         <v>21</v>
       </c>
-      <c r="J272" t="s">
+      <c r="J272" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K272" t="s">
@@ -18714,7 +18714,7 @@
       <c r="I273" t="s">
         <v>21</v>
       </c>
-      <c r="J273" t="s">
+      <c r="J273" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K273" t="s">
@@ -18770,7 +18770,7 @@
       <c r="I274" t="s">
         <v>21</v>
       </c>
-      <c r="J274" t="s">
+      <c r="J274" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K274" t="s">
@@ -18826,7 +18826,7 @@
       <c r="I275" t="s">
         <v>21</v>
       </c>
-      <c r="J275" t="s">
+      <c r="J275" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K275" t="s">
@@ -18882,7 +18882,7 @@
       <c r="I276" t="s">
         <v>21</v>
       </c>
-      <c r="J276" t="s">
+      <c r="J276" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K276" t="s">
@@ -18938,7 +18938,7 @@
       <c r="I277" t="s">
         <v>21</v>
       </c>
-      <c r="J277" t="s">
+      <c r="J277" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K277" t="s">
@@ -18994,7 +18994,7 @@
       <c r="I278" t="s">
         <v>21</v>
       </c>
-      <c r="J278" t="s">
+      <c r="J278" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K278" t="s">
@@ -19050,7 +19050,7 @@
       <c r="I279" t="s">
         <v>21</v>
       </c>
-      <c r="J279" t="s">
+      <c r="J279" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K279" t="s">
@@ -19106,7 +19106,7 @@
       <c r="I280" t="s">
         <v>21</v>
       </c>
-      <c r="J280" t="s">
+      <c r="J280" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K280" t="s">
@@ -19162,7 +19162,7 @@
       <c r="I281" t="s">
         <v>21</v>
       </c>
-      <c r="J281" t="s">
+      <c r="J281" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K281" t="s">
@@ -19218,7 +19218,7 @@
       <c r="I282" t="s">
         <v>21</v>
       </c>
-      <c r="J282" t="s">
+      <c r="J282" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K282" t="s">
@@ -19274,7 +19274,7 @@
       <c r="I283" t="s">
         <v>21</v>
       </c>
-      <c r="J283" t="s">
+      <c r="J283" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K283" t="s">
@@ -19330,7 +19330,7 @@
       <c r="I284" t="s">
         <v>21</v>
       </c>
-      <c r="J284" t="s">
+      <c r="J284" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K284" t="s">
@@ -19386,7 +19386,7 @@
       <c r="I285" t="s">
         <v>21</v>
       </c>
-      <c r="J285" t="s">
+      <c r="J285" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K285" t="s">
@@ -19442,7 +19442,7 @@
       <c r="I286" t="s">
         <v>21</v>
       </c>
-      <c r="J286" t="s">
+      <c r="J286" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K286" t="s">
@@ -19498,7 +19498,7 @@
       <c r="I287" t="s">
         <v>21</v>
       </c>
-      <c r="J287" t="s">
+      <c r="J287" s="3" t="s">
         <v>39</v>
       </c>
       <c r="K287" t="s">

--- a/output/mall candidate_complete.xlsx
+++ b/output/mall candidate_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ADAM\1. New Retail\1. Expansion\1. Expansion\4. PPT\Xiaomi Store Locator\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34E5A52-12C2-45BA-8512-D54B5E48D352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65D5D760-EA3C-417C-B0FE-7B00A1298FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3548,10 +3548,10 @@
         <v>14</v>
       </c>
       <c r="M2" s="3">
-        <v>-6.2712899999999996</v>
+        <v>-10.1706</v>
       </c>
       <c r="N2" s="3">
-        <v>106.86823800000001</v>
+        <v>123.6148</v>
       </c>
       <c r="O2" t="s">
         <v>717</v>
@@ -3604,10 +3604,10 @@
         <v>14</v>
       </c>
       <c r="M3" s="3">
-        <v>5.5563954000000004</v>
+        <v>5.5502000000000002</v>
       </c>
       <c r="N3" s="3">
-        <v>95.426084700000004</v>
+        <v>95.319199999999995</v>
       </c>
       <c r="O3" t="s">
         <v>718</v>
@@ -3660,10 +3660,10 @@
         <v>14</v>
       </c>
       <c r="M4" s="3">
-        <v>-8.6344469999999998</v>
+        <v>-8.7943999999999996</v>
       </c>
       <c r="N4" s="3">
-        <v>115.139672</v>
+        <v>115.1712</v>
       </c>
       <c r="O4" t="s">
         <v>719</v>
@@ -3716,10 +3716,10 @@
         <v>14</v>
       </c>
       <c r="M5" s="3">
-        <v>-8.5212352333333321</v>
+        <v>-8.4911999999999992</v>
       </c>
       <c r="N5" s="3">
-        <v>140.41463045</v>
+        <v>140.4042</v>
       </c>
       <c r="O5" t="s">
         <v>720</v>
@@ -3772,10 +3772,10 @@
         <v>14</v>
       </c>
       <c r="M6" s="3">
-        <v>-8.7055822000000003</v>
+        <v>-8.7231000000000005</v>
       </c>
       <c r="N6" s="3">
-        <v>115.1800717</v>
+        <v>115.1681</v>
       </c>
       <c r="O6" t="s">
         <v>721</v>
@@ -3828,10 +3828,10 @@
         <v>14</v>
       </c>
       <c r="M7" s="3">
-        <v>-8.7143896598860398</v>
+        <v>-8.7187999999999999</v>
       </c>
       <c r="N7" s="3">
-        <v>115.16683556170941</v>
+        <v>115.1691</v>
       </c>
       <c r="O7" t="s">
         <v>722</v>
@@ -3884,10 +3884,10 @@
         <v>14</v>
       </c>
       <c r="M8" s="3">
-        <v>-7.9840054</v>
+        <v>-7.9786000000000001</v>
       </c>
       <c r="N8" s="3">
-        <v>112.6326371</v>
+        <v>112.6288</v>
       </c>
       <c r="O8" t="s">
         <v>723</v>
@@ -3940,10 +3940,10 @@
         <v>14</v>
       </c>
       <c r="M9" s="3">
-        <v>-7.9427060000000003</v>
+        <v>-7.9574999999999996</v>
       </c>
       <c r="N9" s="3">
-        <v>112.6225687</v>
+        <v>112.61579999999999</v>
       </c>
       <c r="O9" t="s">
         <v>724</v>
@@ -3996,10 +3996,10 @@
         <v>14</v>
       </c>
       <c r="M10" s="3">
-        <v>-7.9399709999999999</v>
+        <v>-7.9481999999999999</v>
       </c>
       <c r="N10" s="3">
-        <v>112.644931</v>
+        <v>112.6534</v>
       </c>
       <c r="O10" t="s">
         <v>725</v>
@@ -4052,10 +4052,10 @@
         <v>14</v>
       </c>
       <c r="M11" s="3">
-        <v>-7.6235261999999997</v>
+        <v>-7.6298000000000004</v>
       </c>
       <c r="N11" s="3">
-        <v>111.5222126</v>
+        <v>111.5239</v>
       </c>
       <c r="O11" t="s">
         <v>726</v>
@@ -4108,10 +4108,10 @@
         <v>14</v>
       </c>
       <c r="M12" s="3">
-        <v>-7.7969711999999998</v>
+        <v>-7.7942</v>
       </c>
       <c r="N12" s="3">
-        <v>110.3630869</v>
+        <v>110.36620000000001</v>
       </c>
       <c r="O12" t="s">
         <v>727</v>
@@ -4164,10 +4164,10 @@
         <v>14</v>
       </c>
       <c r="M13" s="3">
-        <v>-7.7933057000000003</v>
+        <v>-7.7925000000000004</v>
       </c>
       <c r="N13" s="3">
-        <v>110.36608</v>
+        <v>110.36579999999999</v>
       </c>
       <c r="O13" t="s">
         <v>728</v>
@@ -4220,10 +4220,10 @@
         <v>14</v>
       </c>
       <c r="M14" s="3">
-        <v>-7.7844410000000002</v>
+        <v>-7.7891000000000004</v>
       </c>
       <c r="N14" s="3">
-        <v>110.39062</v>
+        <v>110.3921</v>
       </c>
       <c r="O14" t="s">
         <v>729</v>
@@ -4276,10 +4276,10 @@
         <v>14</v>
       </c>
       <c r="M15" s="3">
-        <v>3.5805600000000002</v>
+        <v>3.5594000000000001</v>
       </c>
       <c r="N15" s="3">
-        <v>98.626940000000005</v>
+        <v>98.618200000000002</v>
       </c>
       <c r="O15" t="s">
         <v>730</v>
@@ -4332,10 +4332,10 @@
         <v>14</v>
       </c>
       <c r="M16" s="3">
-        <v>-7.2725584999999997</v>
+        <v>-6.9328000000000003</v>
       </c>
       <c r="N16" s="3">
-        <v>112.6974711</v>
+        <v>107.7719</v>
       </c>
       <c r="O16" t="s">
         <v>731</v>
@@ -4388,10 +4388,10 @@
         <v>14</v>
       </c>
       <c r="M17" s="3">
-        <v>-6.2805600000000004</v>
+        <v>-6.8414999999999999</v>
       </c>
       <c r="N17" s="3">
-        <v>107.27278</v>
+        <v>107.9174</v>
       </c>
       <c r="O17" t="s">
         <v>732</v>
@@ -4444,10 +4444,10 @@
         <v>14</v>
       </c>
       <c r="M18" s="3">
-        <v>5.3444000000000003</v>
+        <v>-1.6171</v>
       </c>
       <c r="N18" s="3">
-        <v>95.992199999999997</v>
+        <v>103.6062</v>
       </c>
       <c r="O18" t="s">
         <v>733</v>
@@ -4500,10 +4500,10 @@
         <v>14</v>
       </c>
       <c r="M19" s="3">
-        <v>-7.5838574999999997</v>
+        <v>-7.5612000000000004</v>
       </c>
       <c r="N19" s="3">
-        <v>110.8511230875</v>
+        <v>110.81740000000001</v>
       </c>
       <c r="O19" t="s">
         <v>734</v>
@@ -4556,10 +4556,10 @@
         <v>14</v>
       </c>
       <c r="M20" s="3">
-        <v>-6.4204699999999999</v>
+        <v>-7.5651999999999999</v>
       </c>
       <c r="N20" s="3">
-        <v>105.88436</v>
+        <v>110.8222</v>
       </c>
       <c r="O20" t="s">
         <v>735</v>
@@ -4612,10 +4612,10 @@
         <v>14</v>
       </c>
       <c r="M21" s="3">
-        <v>2.0821749999999999</v>
+        <v>2.1052</v>
       </c>
       <c r="N21" s="3">
-        <v>99.851590000000002</v>
+        <v>99.825199999999995</v>
       </c>
       <c r="O21" t="s">
         <v>736</v>
@@ -4668,10 +4668,10 @@
         <v>14</v>
       </c>
       <c r="M22" s="3">
-        <v>-6.9435975000000001</v>
+        <v>-6.9535</v>
       </c>
       <c r="N22" s="3">
-        <v>107.57766580000001</v>
+        <v>107.5752</v>
       </c>
       <c r="O22" t="s">
         <v>737</v>
@@ -4724,10 +4724,10 @@
         <v>14</v>
       </c>
       <c r="M23" s="3">
-        <v>-6.8898099999999998</v>
+        <v>-6.9458000000000002</v>
       </c>
       <c r="N23" s="3">
-        <v>107.599767</v>
+        <v>107.6542</v>
       </c>
       <c r="O23" t="s">
         <v>738</v>
@@ -4780,10 +4780,10 @@
         <v>14</v>
       </c>
       <c r="M24" s="3">
-        <v>-1.6155337000000001</v>
+        <v>-1.6114999999999999</v>
       </c>
       <c r="N24" s="3">
-        <v>103.6271038</v>
+        <v>103.5932</v>
       </c>
       <c r="O24" t="s">
         <v>739</v>
@@ -4836,10 +4836,10 @@
         <v>14</v>
       </c>
       <c r="M25" s="3">
-        <v>1.391005</v>
+        <v>1.3752</v>
       </c>
       <c r="N25" s="3">
-        <v>99.256428099999994</v>
+        <v>99.265199999999993</v>
       </c>
       <c r="O25" t="s">
         <v>740</v>
@@ -4892,10 +4892,10 @@
         <v>14</v>
       </c>
       <c r="M26" s="3">
-        <v>-7.3202699999999998</v>
+        <v>-7.3620999999999999</v>
       </c>
       <c r="N26" s="3">
-        <v>112.7325051</v>
+        <v>112.7312</v>
       </c>
       <c r="O26" t="s">
         <v>741</v>
@@ -4948,10 +4948,10 @@
         <v>14</v>
       </c>
       <c r="M27" s="3">
-        <v>-7.299936475</v>
+        <v>-7.2884000000000002</v>
       </c>
       <c r="N27" s="3">
-        <v>112.65759699166669</v>
+        <v>112.67489999999999</v>
       </c>
       <c r="O27" t="s">
         <v>742</v>
@@ -5004,10 +5004,10 @@
         <v>14</v>
       </c>
       <c r="M28" s="3">
-        <v>-7.3022239999999998</v>
+        <v>-7.3030999999999997</v>
       </c>
       <c r="N28" s="3">
-        <v>112.738051</v>
+        <v>112.7302</v>
       </c>
       <c r="O28" t="s">
         <v>743</v>
@@ -5060,10 +5060,10 @@
         <v>14</v>
       </c>
       <c r="M29" s="3">
-        <v>-7.3020554000000004</v>
+        <v>-7.2934000000000001</v>
       </c>
       <c r="N29" s="3">
-        <v>112.7392222</v>
+        <v>112.7495</v>
       </c>
       <c r="O29" t="s">
         <v>744</v>
@@ -5116,10 +5116,10 @@
         <v>14</v>
       </c>
       <c r="M30" s="3">
-        <v>-7.2934757000000001</v>
+        <v>-6.2652000000000001</v>
       </c>
       <c r="N30" s="3">
-        <v>112.7174334</v>
+        <v>106.98520000000001</v>
       </c>
       <c r="O30" t="s">
         <v>745</v>
@@ -5172,10 +5172,10 @@
         <v>14</v>
       </c>
       <c r="M31" s="3">
-        <v>-7.2588964999999996</v>
+        <v>-7.2591999999999999</v>
       </c>
       <c r="N31" s="3">
-        <v>112.6870227</v>
+        <v>112.6315</v>
       </c>
       <c r="O31" t="s">
         <v>746</v>
@@ -5228,10 +5228,10 @@
         <v>14</v>
       </c>
       <c r="M32" s="3">
-        <v>-7.2411164000000001</v>
+        <v>-7.2347999999999999</v>
       </c>
       <c r="N32" s="3">
-        <v>112.7466218</v>
+        <v>112.7482</v>
       </c>
       <c r="O32" t="s">
         <v>747</v>
@@ -5284,10 +5284,10 @@
         <v>14</v>
       </c>
       <c r="M33" s="3">
-        <v>-7.2424701999999996</v>
+        <v>-7.2335000000000003</v>
       </c>
       <c r="N33" s="3">
-        <v>112.74463470000001</v>
+        <v>112.7461</v>
       </c>
       <c r="O33" t="s">
         <v>748</v>
@@ -5340,10 +5340,10 @@
         <v>14</v>
       </c>
       <c r="M34" s="3">
-        <v>-7.2342161999999997</v>
+        <v>-7.2371999999999996</v>
       </c>
       <c r="N34" s="3">
-        <v>112.73487249999999</v>
+        <v>112.7423</v>
       </c>
       <c r="O34" t="s">
         <v>749</v>
@@ -5396,10 +5396,10 @@
         <v>14</v>
       </c>
       <c r="M35" s="3">
-        <v>-7.0131204</v>
+        <v>-6.9855999999999998</v>
       </c>
       <c r="N35" s="3">
-        <v>110.38950269999999</v>
+        <v>110.4012</v>
       </c>
       <c r="O35" t="s">
         <v>750</v>
@@ -5452,10 +5452,10 @@
         <v>14</v>
       </c>
       <c r="M36" s="3">
-        <v>-7.9840054</v>
+        <v>-7.9821</v>
       </c>
       <c r="N36" s="3">
-        <v>112.6326371</v>
+        <v>112.62909999999999</v>
       </c>
       <c r="O36" t="s">
         <v>751</v>
@@ -5508,10 +5508,10 @@
         <v>14</v>
       </c>
       <c r="M37" s="3">
-        <v>-7.1541699999999997</v>
+        <v>-7.2653999999999996</v>
       </c>
       <c r="N37" s="3">
-        <v>110.41083</v>
+        <v>112.6052</v>
       </c>
       <c r="O37" t="s">
         <v>752</v>
@@ -5564,10 +5564,10 @@
         <v>14</v>
       </c>
       <c r="M38" s="3">
-        <v>-7.0606774000000003</v>
+        <v>-6.9892000000000003</v>
       </c>
       <c r="N38" s="3">
-        <v>110.4435859</v>
+        <v>110.42310000000001</v>
       </c>
       <c r="O38" t="s">
         <v>753</v>
@@ -5620,10 +5620,10 @@
         <v>14</v>
       </c>
       <c r="M39" s="3">
-        <v>-7.0478981999999997</v>
+        <v>-7.0351999999999997</v>
       </c>
       <c r="N39" s="3">
-        <v>107.7592616</v>
+        <v>107.90519999999999</v>
       </c>
       <c r="O39" t="s">
         <v>754</v>
@@ -5676,10 +5676,10 @@
         <v>14</v>
       </c>
       <c r="M40" s="3">
-        <v>-7.0300240000000001</v>
+        <v>-6.8692000000000002</v>
       </c>
       <c r="N40" s="3">
-        <v>109.19860799999999</v>
+        <v>109.1384</v>
       </c>
       <c r="O40" t="s">
         <v>755</v>
@@ -5732,10 +5732,10 @@
         <v>14</v>
       </c>
       <c r="M41" s="3">
-        <v>-7.0238500000000004</v>
+        <v>-6.1651999999999996</v>
       </c>
       <c r="N41" s="3">
-        <v>110.40374199999999</v>
+        <v>106.79519999999999</v>
       </c>
       <c r="O41" t="s">
         <v>756</v>
@@ -5788,10 +5788,10 @@
         <v>14</v>
       </c>
       <c r="M42" s="3">
-        <v>-5.3819699999999999</v>
+        <v>-5.3853999999999997</v>
       </c>
       <c r="N42" s="3">
-        <v>105.25949</v>
+        <v>105.2531</v>
       </c>
       <c r="O42" t="s">
         <v>757</v>
@@ -5844,10 +5844,10 @@
         <v>14</v>
       </c>
       <c r="M43" s="3">
-        <v>-0.95869579999999999</v>
+        <v>-0.8952</v>
       </c>
       <c r="N43" s="3">
-        <v>131.33061025000001</v>
+        <v>131.2552</v>
       </c>
       <c r="O43" t="s">
         <v>758</v>
@@ -5900,10 +5900,10 @@
         <v>14</v>
       </c>
       <c r="M44" s="3">
-        <v>-6.9246089</v>
+        <v>-6.9181999999999997</v>
       </c>
       <c r="N44" s="3">
-        <v>107.6075793</v>
+        <v>107.6082</v>
       </c>
       <c r="O44" t="s">
         <v>759</v>
@@ -5956,10 +5956,10 @@
         <v>14</v>
       </c>
       <c r="M45" s="3">
-        <v>-6.904801</v>
+        <v>-6.8912000000000004</v>
       </c>
       <c r="N45" s="3">
-        <v>109.67203000000001</v>
+        <v>109.6712</v>
       </c>
       <c r="O45" t="s">
         <v>760</v>
@@ -6012,10 +6012,10 @@
         <v>14</v>
       </c>
       <c r="M46" s="3">
-        <v>-6.7145447999999996</v>
+        <v>-6.8251999999999997</v>
       </c>
       <c r="N46" s="3">
-        <v>108.56307769999999</v>
+        <v>108.2252</v>
       </c>
       <c r="O46" t="s">
         <v>761</v>
@@ -6068,10 +6068,10 @@
         <v>14</v>
       </c>
       <c r="M47" s="3">
-        <v>-6.7084087999999999</v>
+        <v>-6.7081999999999997</v>
       </c>
       <c r="N47" s="3">
-        <v>108.5591812</v>
+        <v>108.5532</v>
       </c>
       <c r="O47" t="s">
         <v>762</v>
@@ -6124,10 +6124,10 @@
         <v>14</v>
       </c>
       <c r="M48" s="3">
-        <v>-7.4339054999999998</v>
+        <v>-7.4215</v>
       </c>
       <c r="N48" s="3">
-        <v>109.2423038</v>
+        <v>109.2435</v>
       </c>
       <c r="O48" t="s">
         <v>763</v>
@@ -6180,10 +6180,10 @@
         <v>14</v>
       </c>
       <c r="M49" s="3">
-        <v>-7.3537470000000003</v>
+        <v>-7.6012000000000004</v>
       </c>
       <c r="N49" s="3">
-        <v>109.79171100000001</v>
+        <v>110.8124</v>
       </c>
       <c r="O49" t="s">
         <v>764</v>
@@ -6236,10 +6236,10 @@
         <v>14</v>
       </c>
       <c r="M50" s="3">
-        <v>-6.5930163000000004</v>
+        <v>-6.5982000000000003</v>
       </c>
       <c r="N50" s="3">
-        <v>106.79707190000001</v>
+        <v>106.7971</v>
       </c>
       <c r="O50" t="s">
         <v>765</v>
@@ -6292,10 +6292,10 @@
         <v>14</v>
       </c>
       <c r="M51" s="3">
-        <v>-6.5893423000000002</v>
+        <v>-6.6025</v>
       </c>
       <c r="N51" s="3">
-        <v>106.80342804</v>
+        <v>106.8052</v>
       </c>
       <c r="O51" t="s">
         <v>766</v>
@@ -6348,10 +6348,10 @@
         <v>14</v>
       </c>
       <c r="M52" s="3">
-        <v>-6.5895159999999997</v>
+        <v>-6.9252000000000002</v>
       </c>
       <c r="N52" s="3">
-        <v>107.444568</v>
+        <v>106.9282</v>
       </c>
       <c r="O52" t="s">
         <v>767</v>
@@ -6404,10 +6404,10 @@
         <v>14</v>
       </c>
       <c r="M53" s="3">
-        <v>-6.5659210066666667</v>
+        <v>-6.5590999999999999</v>
       </c>
       <c r="N53" s="3">
-        <v>106.79143498000001</v>
+        <v>106.8124</v>
       </c>
       <c r="O53" t="s">
         <v>768</v>
@@ -6460,10 +6460,10 @@
         <v>14</v>
       </c>
       <c r="M54" s="3">
-        <v>-6.2937830000000003</v>
+        <v>-6.3213999999999997</v>
       </c>
       <c r="N54" s="3">
-        <v>107.148844</v>
+        <v>107.1512</v>
       </c>
       <c r="O54" t="s">
         <v>769</v>
@@ -6516,10 +6516,10 @@
         <v>14</v>
       </c>
       <c r="M55" s="3">
-        <v>-7.5615585999999997</v>
+        <v>-7.5500999999999996</v>
       </c>
       <c r="N55" s="3">
-        <v>110.7926994</v>
+        <v>110.79510000000001</v>
       </c>
       <c r="O55" t="s">
         <v>770</v>
@@ -6572,10 +6572,10 @@
         <v>14</v>
       </c>
       <c r="M56" s="3">
-        <v>-6.4204699999999999</v>
+        <v>-7.5713999999999997</v>
       </c>
       <c r="N56" s="3">
-        <v>105.88436</v>
+        <v>110.82510000000001</v>
       </c>
       <c r="O56" t="s">
         <v>771</v>
@@ -6628,10 +6628,10 @@
         <v>14</v>
       </c>
       <c r="M57" s="3">
-        <v>-6.4085939999999999</v>
+        <v>-6.4012000000000002</v>
       </c>
       <c r="N57" s="3">
-        <v>107.46249090000001</v>
+        <v>107.45820000000001</v>
       </c>
       <c r="O57" t="s">
         <v>772</v>
@@ -6684,10 +6684,10 @@
         <v>14</v>
       </c>
       <c r="M58" s="3">
-        <v>-6.3281901999999999</v>
+        <v>-6.3052000000000001</v>
       </c>
       <c r="N58" s="3">
-        <v>107.286807</v>
+        <v>107.3052</v>
       </c>
       <c r="O58" t="s">
         <v>773</v>
@@ -6740,10 +6740,10 @@
         <v>14</v>
       </c>
       <c r="M59" s="3">
-        <v>-6.3765112000000004</v>
+        <v>-6.3752000000000004</v>
       </c>
       <c r="N59" s="3">
-        <v>106.9152256</v>
+        <v>106.91840000000001</v>
       </c>
       <c r="O59" t="s">
         <v>774</v>
@@ -6796,10 +6796,10 @@
         <v>14</v>
       </c>
       <c r="M60" s="3">
-        <v>-6.3399704999999997</v>
+        <v>-6.3452000000000002</v>
       </c>
       <c r="N60" s="3">
-        <v>106.73447299999999</v>
+        <v>106.7291</v>
       </c>
       <c r="O60" t="s">
         <v>775</v>
@@ -6852,10 +6852,10 @@
         <v>14</v>
       </c>
       <c r="M61" s="3">
-        <v>-6.3442115000000001</v>
+        <v>-6.3082000000000003</v>
       </c>
       <c r="N61" s="3">
-        <v>106.8194326</v>
+        <v>106.79519999999999</v>
       </c>
       <c r="O61" t="s">
         <v>776</v>
@@ -6908,10 +6908,10 @@
         <v>14</v>
       </c>
       <c r="M62" s="3">
-        <v>-6.3250183</v>
+        <v>-6.3552</v>
       </c>
       <c r="N62" s="3">
-        <v>107.2924549</v>
+        <v>107.2552</v>
       </c>
       <c r="O62" t="s">
         <v>777</v>
@@ -6964,10 +6964,10 @@
         <v>14</v>
       </c>
       <c r="M63" s="3">
-        <v>-6.3172356000000001</v>
+        <v>-6.3125</v>
       </c>
       <c r="N63" s="3">
-        <v>107.2898017</v>
+        <v>107.30119999999999</v>
       </c>
       <c r="O63" t="s">
         <v>778</v>
@@ -7020,10 +7020,10 @@
         <v>14</v>
       </c>
       <c r="M64" s="3">
-        <v>-6.2853279000000004</v>
+        <v>-6.2812000000000001</v>
       </c>
       <c r="N64" s="3">
-        <v>106.6985375</v>
+        <v>106.7152</v>
       </c>
       <c r="O64" t="s">
         <v>779</v>
@@ -7076,10 +7076,10 @@
         <v>14</v>
       </c>
       <c r="M65" s="3">
-        <v>-6.3043287000000001</v>
+        <v>-6.3112000000000004</v>
       </c>
       <c r="N65" s="3">
-        <v>106.107681</v>
+        <v>106.1082</v>
       </c>
       <c r="O65" t="s">
         <v>780</v>
@@ -7132,10 +7132,10 @@
         <v>14</v>
       </c>
       <c r="M66" s="3">
-        <v>-6.2935185999999996</v>
+        <v>-6.2915000000000001</v>
       </c>
       <c r="N66" s="3">
-        <v>106.6668019</v>
+        <v>106.6631</v>
       </c>
       <c r="O66" t="s">
         <v>781</v>
@@ -7188,10 +7188,10 @@
         <v>14</v>
       </c>
       <c r="M67" s="3">
-        <v>-6.248756975</v>
+        <v>-6.2445000000000004</v>
       </c>
       <c r="N67" s="3">
-        <v>106.8032613725</v>
+        <v>106.8015</v>
       </c>
       <c r="O67" t="s">
         <v>782</v>
@@ -7244,10 +7244,10 @@
         <v>14</v>
       </c>
       <c r="M68" s="3">
-        <v>-6.2919314999999996</v>
+        <v>-6.2625000000000002</v>
       </c>
       <c r="N68" s="3">
-        <v>107.04671879999999</v>
+        <v>107.05119999999999</v>
       </c>
       <c r="O68" t="s">
         <v>783</v>
@@ -7300,10 +7300,10 @@
         <v>14</v>
       </c>
       <c r="M69" s="3">
-        <v>-6.29209</v>
+        <v>-6.2891000000000004</v>
       </c>
       <c r="N69" s="3">
-        <v>106.783653</v>
+        <v>106.7984</v>
       </c>
       <c r="O69" t="s">
         <v>784</v>
@@ -7356,10 +7356,10 @@
         <v>14</v>
       </c>
       <c r="M70" s="3">
-        <v>-6.2856234000000004</v>
+        <v>-6.3011999999999997</v>
       </c>
       <c r="N70" s="3">
-        <v>106.65441060000001</v>
+        <v>106.64319999999999</v>
       </c>
       <c r="O70" t="s">
         <v>785</v>
@@ -7412,10 +7412,10 @@
         <v>14</v>
       </c>
       <c r="M71" s="3">
-        <v>-6.2837708000000001</v>
+        <v>-6.2653999999999996</v>
       </c>
       <c r="N71" s="3">
-        <v>106.780438</v>
+        <v>106.7842</v>
       </c>
       <c r="O71" t="s">
         <v>786</v>
@@ -7468,10 +7468,10 @@
         <v>14</v>
       </c>
       <c r="M72" s="3">
-        <v>-6.2822740000000001</v>
+        <v>-6.2812000000000001</v>
       </c>
       <c r="N72" s="3">
-        <v>106.878243</v>
+        <v>106.8852</v>
       </c>
       <c r="O72" t="s">
         <v>787</v>
@@ -7524,10 +7524,10 @@
         <v>14</v>
       </c>
       <c r="M73" s="3">
-        <v>-6.2798220999999996</v>
+        <v>-6.2790999999999997</v>
       </c>
       <c r="N73" s="3">
-        <v>106.82941580000001</v>
+        <v>106.84310000000001</v>
       </c>
       <c r="O73" t="s">
         <v>788</v>
@@ -7580,10 +7580,10 @@
         <v>14</v>
       </c>
       <c r="M74" s="3">
-        <v>-6.2691790000000003</v>
+        <v>-6.2812000000000001</v>
       </c>
       <c r="N74" s="3">
-        <v>106.74366240000001</v>
+        <v>106.72539999999999</v>
       </c>
       <c r="O74" t="s">
         <v>789</v>
@@ -7636,10 +7636,10 @@
         <v>14</v>
       </c>
       <c r="M75" s="3">
-        <v>-6.3127779000000004</v>
+        <v>-6.2792000000000003</v>
       </c>
       <c r="N75" s="3">
-        <v>106.6904844</v>
+        <v>106.7221</v>
       </c>
       <c r="O75" t="s">
         <v>790</v>
@@ -7692,10 +7692,10 @@
         <v>14</v>
       </c>
       <c r="M76" s="3">
-        <v>-6.2743381999999999</v>
+        <v>-6.2550999999999997</v>
       </c>
       <c r="N76" s="3">
-        <v>106.816502</v>
+        <v>106.8532</v>
       </c>
       <c r="O76" t="s">
         <v>791</v>
@@ -7748,10 +7748,10 @@
         <v>14</v>
       </c>
       <c r="M77" s="3">
-        <v>-6.2766788</v>
+        <v>-6.2901999999999996</v>
       </c>
       <c r="N77" s="3">
-        <v>106.79686</v>
+        <v>106.8142</v>
       </c>
       <c r="O77" t="s">
         <v>792</v>
@@ -7804,10 +7804,10 @@
         <v>14</v>
       </c>
       <c r="M78" s="3">
-        <v>-6.2642445999999996</v>
+        <v>-6.2591999999999999</v>
       </c>
       <c r="N78" s="3">
-        <v>106.7987329</v>
+        <v>106.79819999999999</v>
       </c>
       <c r="O78" t="s">
         <v>793</v>
@@ -7860,10 +7860,10 @@
         <v>14</v>
       </c>
       <c r="M79" s="3">
-        <v>-6.2623759000000003</v>
+        <v>-6.2651000000000003</v>
       </c>
       <c r="N79" s="3">
-        <v>106.864919</v>
+        <v>106.8682</v>
       </c>
       <c r="O79" t="s">
         <v>794</v>
@@ -7916,10 +7916,10 @@
         <v>14</v>
       </c>
       <c r="M80" s="3">
-        <v>-6.2560561999999997</v>
+        <v>-6.2451999999999996</v>
       </c>
       <c r="N80" s="3">
-        <v>107.0078793</v>
+        <v>106.9952</v>
       </c>
       <c r="O80" t="s">
         <v>795</v>
@@ -7972,10 +7972,10 @@
         <v>14</v>
       </c>
       <c r="M81" s="3">
-        <v>-6.1539855000000001</v>
+        <v>-6.2911999999999999</v>
       </c>
       <c r="N81" s="3">
-        <v>106.7501445</v>
+        <v>106.7791</v>
       </c>
       <c r="O81" t="s">
         <v>796</v>
@@ -8028,10 +8028,10 @@
         <v>14</v>
       </c>
       <c r="M82" s="3">
-        <v>-6.0469726000000001</v>
+        <v>-6.2252000000000001</v>
       </c>
       <c r="N82" s="3">
-        <v>106.7025622</v>
+        <v>106.8152</v>
       </c>
       <c r="O82" t="s">
         <v>797</v>
@@ -8084,10 +8084,10 @@
         <v>14</v>
       </c>
       <c r="M83" s="3">
-        <v>-6.0918419999999998</v>
+        <v>-6.1151999999999997</v>
       </c>
       <c r="N83" s="3">
-        <v>106.69190999999999</v>
+        <v>106.6952</v>
       </c>
       <c r="O83" t="s">
         <v>798</v>
@@ -8140,10 +8140,10 @@
         <v>14</v>
       </c>
       <c r="M84" s="3">
-        <v>-6.2408700000000001</v>
+        <v>-6.2591000000000001</v>
       </c>
       <c r="N84" s="3">
-        <v>106.98876</v>
+        <v>106.9892</v>
       </c>
       <c r="O84" t="s">
         <v>799</v>
@@ -8196,10 +8196,10 @@
         <v>14</v>
       </c>
       <c r="M85" s="3">
-        <v>-6.9156817000000004</v>
+        <v>-6.9151999999999996</v>
       </c>
       <c r="N85" s="3">
-        <v>107.69665070000001</v>
+        <v>107.6892</v>
       </c>
       <c r="O85" t="s">
         <v>800</v>
@@ -8252,10 +8252,10 @@
         <v>14</v>
       </c>
       <c r="M86" s="3">
-        <v>-6.2482208000000004</v>
+        <v>-6.2312000000000003</v>
       </c>
       <c r="N86" s="3">
-        <v>106.91381699999999</v>
+        <v>106.8852</v>
       </c>
       <c r="O86" t="s">
         <v>801</v>
@@ -8308,10 +8308,10 @@
         <v>14</v>
       </c>
       <c r="M87" s="3">
-        <v>-6.2726870000000003</v>
+        <v>-6.2351000000000001</v>
       </c>
       <c r="N87" s="3">
-        <v>106.805572</v>
+        <v>106.7791</v>
       </c>
       <c r="O87" t="s">
         <v>802</v>
@@ -8364,10 +8364,10 @@
         <v>14</v>
       </c>
       <c r="M88" s="3">
-        <v>-6.2743381999999999</v>
+        <v>-6.2435</v>
       </c>
       <c r="N88" s="3">
-        <v>106.816502</v>
+        <v>106.7991</v>
       </c>
       <c r="O88" t="s">
         <v>803</v>
@@ -8420,10 +8420,10 @@
         <v>14</v>
       </c>
       <c r="M89" s="3">
-        <v>-6.2485213000000002</v>
+        <v>-6.2582000000000004</v>
       </c>
       <c r="N89" s="3">
-        <v>106.9909492</v>
+        <v>106.98820000000001</v>
       </c>
       <c r="O89" t="s">
         <v>804</v>
@@ -8476,10 +8476,10 @@
         <v>14</v>
       </c>
       <c r="M90" s="3">
-        <v>-6.2287058677966103</v>
+        <v>-6.2290999999999999</v>
       </c>
       <c r="N90" s="3">
-        <v>106.80855425423729</v>
+        <v>106.8062</v>
       </c>
       <c r="O90" t="s">
         <v>805</v>
@@ -8532,10 +8532,10 @@
         <v>14</v>
       </c>
       <c r="M91" s="3">
-        <v>-6.2781754999999997</v>
+        <v>-6.2815000000000003</v>
       </c>
       <c r="N91" s="3">
-        <v>106.7229396</v>
+        <v>106.7152</v>
       </c>
       <c r="O91" t="s">
         <v>806</v>
@@ -8588,10 +8588,10 @@
         <v>14</v>
       </c>
       <c r="M92" s="3">
-        <v>-6.2266611000000003</v>
+        <v>-6.2251000000000003</v>
       </c>
       <c r="N92" s="3">
-        <v>106.8012609</v>
+        <v>106.8015</v>
       </c>
       <c r="O92" t="s">
         <v>807</v>
@@ -8644,10 +8644,10 @@
         <v>14</v>
       </c>
       <c r="M93" s="3">
-        <v>-6.8171480999999998</v>
+        <v>-6.8215000000000003</v>
       </c>
       <c r="N93" s="3">
-        <v>107.1307897333333</v>
+        <v>107.1425</v>
       </c>
       <c r="O93" t="s">
         <v>808</v>
@@ -8700,10 +8700,10 @@
         <v>14</v>
       </c>
       <c r="M94" s="3">
-        <v>-6.2255839999999996</v>
+        <v>-6.2262000000000004</v>
       </c>
       <c r="N94" s="3">
-        <v>106.7995999</v>
+        <v>106.7991</v>
       </c>
       <c r="O94" t="s">
         <v>809</v>
@@ -8756,10 +8756,10 @@
         <v>14</v>
       </c>
       <c r="M95" s="3">
-        <v>-6.2249220000000003</v>
+        <v>-6.2241</v>
       </c>
       <c r="N95" s="3">
-        <v>106.810351</v>
+        <v>106.8082</v>
       </c>
       <c r="O95" t="s">
         <v>810</v>
@@ -8812,10 +8812,10 @@
         <v>14</v>
       </c>
       <c r="M96" s="3">
-        <v>-6.2245280000000003</v>
+        <v>-6.2214999999999998</v>
       </c>
       <c r="N96" s="3">
-        <v>106.82950099999999</v>
+        <v>106.8282</v>
       </c>
       <c r="O96" t="s">
         <v>811</v>
@@ -8868,10 +8868,10 @@
         <v>14</v>
       </c>
       <c r="M97" s="3">
-        <v>-6.2282196000000001</v>
+        <v>-6.2251000000000003</v>
       </c>
       <c r="N97" s="3">
-        <v>106.79682699999999</v>
+        <v>106.7962</v>
       </c>
       <c r="O97" t="s">
         <v>812</v>
@@ -8924,10 +8924,10 @@
         <v>14</v>
       </c>
       <c r="M98" s="3">
-        <v>-6.2216088999999997</v>
+        <v>-6.2211999999999996</v>
       </c>
       <c r="N98" s="3">
-        <v>106.8322373</v>
+        <v>106.8321</v>
       </c>
       <c r="O98" t="s">
         <v>813</v>
@@ -8980,10 +8980,10 @@
         <v>14</v>
       </c>
       <c r="M99" s="3">
-        <v>-6.2197988999999998</v>
+        <v>-6.2214999999999998</v>
       </c>
       <c r="N99" s="3">
-        <v>106.81459220000001</v>
+        <v>106.81619999999999</v>
       </c>
       <c r="O99" t="s">
         <v>814</v>
@@ -9036,10 +9036,10 @@
         <v>14</v>
       </c>
       <c r="M100" s="3">
-        <v>-6.2177939000000002</v>
+        <v>-6.2225000000000001</v>
       </c>
       <c r="N100" s="3">
-        <v>106.8355559</v>
+        <v>106.83410000000001</v>
       </c>
       <c r="O100" t="s">
         <v>815</v>
@@ -9092,10 +9092,10 @@
         <v>14</v>
       </c>
       <c r="M101" s="3">
-        <v>-6.2173619999999996</v>
+        <v>-7.2884000000000002</v>
       </c>
       <c r="N101" s="3">
-        <v>106.904841</v>
+        <v>112.67489999999999</v>
       </c>
       <c r="O101" t="s">
         <v>816</v>
@@ -9148,10 +9148,10 @@
         <v>14</v>
       </c>
       <c r="M102" s="3">
-        <v>-6.2399820000000004</v>
+        <v>-6.2392000000000003</v>
       </c>
       <c r="N102" s="3">
-        <v>106.9350951</v>
+        <v>106.92910000000001</v>
       </c>
       <c r="O102" t="s">
         <v>817</v>
@@ -9204,10 +9204,10 @@
         <v>14</v>
       </c>
       <c r="M103" s="3">
-        <v>-6.2142061999999996</v>
+        <v>-6.2214999999999998</v>
       </c>
       <c r="N103" s="3">
-        <v>106.8623509</v>
+        <v>106.86920000000001</v>
       </c>
       <c r="O103" t="s">
         <v>818</v>
@@ -9260,10 +9260,10 @@
         <v>14</v>
       </c>
       <c r="M104" s="3">
-        <v>-6.2283914999999999</v>
+        <v>-6.2281000000000004</v>
       </c>
       <c r="N104" s="3">
-        <v>106.7186554</v>
+        <v>106.7182</v>
       </c>
       <c r="O104" t="s">
         <v>819</v>
@@ -9316,10 +9316,10 @@
         <v>14</v>
       </c>
       <c r="M105" s="3">
-        <v>-6.2152224</v>
+        <v>-6.2211999999999996</v>
       </c>
       <c r="N105" s="3">
-        <v>106.8300413</v>
+        <v>106.8291</v>
       </c>
       <c r="O105" t="s">
         <v>820</v>
@@ -9372,10 +9372,10 @@
         <v>14</v>
       </c>
       <c r="M106" s="3">
-        <v>-6.2497239999999996</v>
+        <v>-6.2152000000000003</v>
       </c>
       <c r="N106" s="3">
-        <v>106.778358</v>
+        <v>106.7821</v>
       </c>
       <c r="O106" t="s">
         <v>821</v>
@@ -9428,10 +9428,10 @@
         <v>14</v>
       </c>
       <c r="M107" s="3">
-        <v>1.2752368000000001</v>
+        <v>1.2552000000000001</v>
       </c>
       <c r="N107" s="3">
-        <v>101.1184993</v>
+        <v>101.9252</v>
       </c>
       <c r="O107" t="s">
         <v>822</v>
@@ -9484,10 +9484,10 @@
         <v>14</v>
       </c>
       <c r="M108" s="3">
-        <v>-6.2089457000000001</v>
+        <v>-6.2081999999999997</v>
       </c>
       <c r="N108" s="3">
-        <v>106.81844220000001</v>
+        <v>106.8182</v>
       </c>
       <c r="O108" t="s">
         <v>823</v>
@@ -9540,10 +9540,10 @@
         <v>14</v>
       </c>
       <c r="M109" s="3">
-        <v>-6.1938029999999999</v>
+        <v>-6.1931000000000003</v>
       </c>
       <c r="N109" s="3">
-        <v>106.822447</v>
+        <v>106.82250000000001</v>
       </c>
       <c r="O109" t="s">
         <v>824</v>
@@ -9596,10 +9596,10 @@
         <v>14</v>
       </c>
       <c r="M110" s="3">
-        <v>-6.1890860999999999</v>
+        <v>-6.1935000000000002</v>
       </c>
       <c r="N110" s="3">
-        <v>106.79639589999999</v>
+        <v>106.7991</v>
       </c>
       <c r="O110" t="s">
         <v>825</v>
@@ -9652,10 +9652,10 @@
         <v>14</v>
       </c>
       <c r="M111" s="3">
-        <v>-6.1825840000000003</v>
+        <v>-6.2351999999999999</v>
       </c>
       <c r="N111" s="3">
-        <v>106.64505800000001</v>
+        <v>106.6782</v>
       </c>
       <c r="O111" t="s">
         <v>826</v>
@@ -9708,10 +9708,10 @@
         <v>14</v>
       </c>
       <c r="M112" s="3">
-        <v>-6.1825840000000003</v>
+        <v>-6.2901999999999996</v>
       </c>
       <c r="N112" s="3">
-        <v>106.64505800000001</v>
+        <v>106.6652</v>
       </c>
       <c r="O112" t="s">
         <v>827</v>
@@ -9764,10 +9764,10 @@
         <v>14</v>
       </c>
       <c r="M113" s="3">
-        <v>-6.1648465999999997</v>
+        <v>-6.1752000000000002</v>
       </c>
       <c r="N113" s="3">
-        <v>106.8761729</v>
+        <v>106.86920000000001</v>
       </c>
       <c r="O113" t="s">
         <v>828</v>
@@ -9820,10 +9820,10 @@
         <v>14</v>
       </c>
       <c r="M114" s="3">
-        <v>-6.1333248999999999</v>
+        <v>-6.1425000000000001</v>
       </c>
       <c r="N114" s="3">
-        <v>106.71875970000001</v>
+        <v>106.7321</v>
       </c>
       <c r="O114" t="s">
         <v>829</v>
@@ -9876,10 +9876,10 @@
         <v>14</v>
       </c>
       <c r="M115" s="3">
-        <v>-6.1749251999999997</v>
+        <v>-6.1782000000000004</v>
       </c>
       <c r="N115" s="3">
-        <v>106.7900491</v>
+        <v>106.7925</v>
       </c>
       <c r="O115" t="s">
         <v>830</v>
@@ -9932,10 +9932,10 @@
         <v>14</v>
       </c>
       <c r="M116" s="3">
-        <v>-6.1757479999999996</v>
+        <v>-6.1651999999999996</v>
       </c>
       <c r="N116" s="3">
-        <v>106.810389</v>
+        <v>106.8052</v>
       </c>
       <c r="O116" t="s">
         <v>831</v>
@@ -9988,10 +9988,10 @@
         <v>14</v>
       </c>
       <c r="M117" s="3">
-        <v>-6.2209539999999999</v>
+        <v>-6.2415000000000003</v>
       </c>
       <c r="N117" s="3">
-        <v>106.691524</v>
+        <v>106.6542</v>
       </c>
       <c r="O117" t="s">
         <v>832</v>
@@ -10044,10 +10044,10 @@
         <v>14</v>
       </c>
       <c r="M118" s="3">
-        <v>-6.2082280000000001</v>
+        <v>-6.2552000000000003</v>
       </c>
       <c r="N118" s="3">
-        <v>106.526785</v>
+        <v>106.51519999999999</v>
       </c>
       <c r="O118" t="s">
         <v>833</v>
@@ -10100,10 +10100,10 @@
         <v>14</v>
       </c>
       <c r="M119" s="3">
-        <v>-6.1573314999999997</v>
+        <v>-6.1551999999999998</v>
       </c>
       <c r="N119" s="3">
-        <v>106.71206050000001</v>
+        <v>106.7052</v>
       </c>
       <c r="O119" t="s">
         <v>834</v>
@@ -10156,10 +10156,10 @@
         <v>14</v>
       </c>
       <c r="M120" s="3">
-        <v>-6.1573314999999997</v>
+        <v>-6.1492000000000004</v>
       </c>
       <c r="N120" s="3">
-        <v>106.71206050000001</v>
+        <v>106.7281</v>
       </c>
       <c r="O120" t="s">
         <v>835</v>
@@ -10212,10 +10212,10 @@
         <v>14</v>
       </c>
       <c r="M121" s="3">
-        <v>-6.1513958999999998</v>
+        <v>-6.1551999999999998</v>
       </c>
       <c r="N121" s="3">
-        <v>106.8120297</v>
+        <v>106.8152</v>
       </c>
       <c r="O121" t="s">
         <v>836</v>
@@ -10268,10 +10268,10 @@
         <v>14</v>
       </c>
       <c r="M122" s="3">
-        <v>-6.1983569999999997</v>
+        <v>-6.1435000000000004</v>
       </c>
       <c r="N122" s="3">
-        <v>106.794287</v>
+        <v>106.8152</v>
       </c>
       <c r="O122" t="s">
         <v>837</v>
@@ -10324,10 +10324,10 @@
         <v>14</v>
       </c>
       <c r="M123" s="3">
-        <v>-6.1983569999999997</v>
+        <v>-6.1352000000000002</v>
       </c>
       <c r="N123" s="3">
-        <v>106.794287</v>
+        <v>106.8291</v>
       </c>
       <c r="O123" t="s">
         <v>838</v>
@@ -10380,10 +10380,10 @@
         <v>14</v>
       </c>
       <c r="M124" s="3">
-        <v>-6.1378000000000004</v>
+        <v>-6.1382000000000003</v>
       </c>
       <c r="N124" s="3">
-        <v>106.82715</v>
+        <v>106.8291</v>
       </c>
       <c r="O124" t="s">
         <v>839</v>
@@ -10436,10 +10436,10 @@
         <v>14</v>
       </c>
       <c r="M125" s="3">
-        <v>-6.128449008695652</v>
+        <v>-6.1252000000000004</v>
       </c>
       <c r="N125" s="3">
-        <v>106.8356417086956</v>
+        <v>106.8352</v>
       </c>
       <c r="O125" t="s">
         <v>840</v>
@@ -10492,10 +10492,10 @@
         <v>14</v>
       </c>
       <c r="M126" s="3">
-        <v>-6.1416686571428576</v>
+        <v>-6.1382000000000003</v>
       </c>
       <c r="N126" s="3">
-        <v>106.8678798190476</v>
+        <v>106.86920000000001</v>
       </c>
       <c r="O126" t="s">
         <v>841</v>
@@ -10548,10 +10548,10 @@
         <v>14</v>
       </c>
       <c r="M127" s="3">
-        <v>-6.1465389000000004</v>
+        <v>-6.1482000000000001</v>
       </c>
       <c r="N127" s="3">
-        <v>106.8235201</v>
+        <v>106.8252</v>
       </c>
       <c r="O127" t="s">
         <v>842</v>
@@ -10604,10 +10604,10 @@
         <v>14</v>
       </c>
       <c r="M128" s="3">
-        <v>-6.0564186142857146</v>
+        <v>-6.1151999999999997</v>
       </c>
       <c r="N128" s="3">
-        <v>105.9926839571429</v>
+        <v>106.15519999999999</v>
       </c>
       <c r="O128" t="s">
         <v>843</v>
@@ -10660,10 +10660,10 @@
         <v>14</v>
       </c>
       <c r="M129" s="3">
-        <v>-6.1594366000000003</v>
+        <v>-6.1151999999999997</v>
       </c>
       <c r="N129" s="3">
-        <v>106.9059815</v>
+        <v>106.7921</v>
       </c>
       <c r="O129" t="s">
         <v>844</v>
@@ -10716,10 +10716,10 @@
         <v>14</v>
       </c>
       <c r="M130" s="3">
-        <v>-6.1153500000000003</v>
+        <v>-6.1112000000000002</v>
       </c>
       <c r="N130" s="3">
-        <v>106.735461</v>
+        <v>106.74120000000001</v>
       </c>
       <c r="O130" t="s">
         <v>845</v>
@@ -10772,10 +10772,10 @@
         <v>14</v>
       </c>
       <c r="M131" s="3">
-        <v>-6.0067050000000002</v>
+        <v>-6.0182000000000002</v>
       </c>
       <c r="N131" s="3">
-        <v>106.021874</v>
+        <v>106.01519999999999</v>
       </c>
       <c r="O131" t="s">
         <v>846</v>
@@ -10828,10 +10828,10 @@
         <v>14</v>
       </c>
       <c r="M132" s="3">
-        <v>-5.9912764000000003</v>
+        <v>-6.0152000000000001</v>
       </c>
       <c r="N132" s="3">
-        <v>106.0577756</v>
+        <v>106.02119999999999</v>
       </c>
       <c r="O132" t="s">
         <v>847</v>
@@ -10884,10 +10884,10 @@
         <v>14</v>
       </c>
       <c r="M133" s="3">
-        <v>-6.5862999999999996</v>
+        <v>-5.4352</v>
       </c>
       <c r="N133" s="3">
-        <v>106.805099</v>
+        <v>105.2582</v>
       </c>
       <c r="O133" t="s">
         <v>848</v>
@@ -10940,10 +10940,10 @@
         <v>14</v>
       </c>
       <c r="M134" s="3">
-        <v>-5.4200980000000003</v>
+        <v>-5.4252000000000002</v>
       </c>
       <c r="N134" s="3">
-        <v>105.258031</v>
+        <v>105.26519999999999</v>
       </c>
       <c r="O134" t="s">
         <v>849</v>
@@ -10996,10 +10996,10 @@
         <v>14</v>
       </c>
       <c r="M135" s="3">
-        <v>-6.314754475</v>
+        <v>-6.3125</v>
       </c>
       <c r="N135" s="3">
-        <v>106.860127375</v>
+        <v>106.8652</v>
       </c>
       <c r="O135" t="s">
         <v>850</v>
@@ -11052,10 +11052,10 @@
         <v>14</v>
       </c>
       <c r="M136" s="3">
-        <v>-5.1329349999999998</v>
+        <v>-5.1325000000000003</v>
       </c>
       <c r="N136" s="3">
-        <v>119.40956370000001</v>
+        <v>119.41249999999999</v>
       </c>
       <c r="O136" t="s">
         <v>851</v>
@@ -11108,10 +11108,10 @@
         <v>14</v>
       </c>
       <c r="M137" s="3">
-        <v>-4.5633892999999999</v>
+        <v>-4.5452000000000004</v>
       </c>
       <c r="N137" s="3">
-        <v>136.83976419999999</v>
+        <v>136.8852</v>
       </c>
       <c r="O137" t="s">
         <v>852</v>
@@ -11164,10 +11164,10 @@
         <v>14</v>
       </c>
       <c r="M138" s="3">
-        <v>-3.9691386999999998</v>
+        <v>-3.9851999999999999</v>
       </c>
       <c r="N138" s="3">
-        <v>122.5263968</v>
+        <v>122.51519999999999</v>
       </c>
       <c r="O138" t="s">
         <v>853</v>
@@ -11220,10 +11220,10 @@
         <v>14</v>
       </c>
       <c r="M139" s="3">
-        <v>-3.72139</v>
+        <v>-3.8052000000000001</v>
       </c>
       <c r="N139" s="3">
-        <v>114.88889</v>
+        <v>114.76519999999999</v>
       </c>
       <c r="O139" t="s">
         <v>854</v>
@@ -11276,10 +11276,10 @@
         <v>14</v>
       </c>
       <c r="M140" s="3">
-        <v>-3.6547200000000002</v>
+        <v>-3.6751999999999998</v>
       </c>
       <c r="N140" s="3">
-        <v>128.24610999999999</v>
+        <v>128.18520000000001</v>
       </c>
       <c r="O140" t="s">
         <v>855</v>
@@ -11332,10 +11332,10 @@
         <v>14</v>
       </c>
       <c r="M141" s="3">
-        <v>2.98306</v>
+        <v>-3.4352</v>
       </c>
       <c r="N141" s="3">
-        <v>99.643330000000006</v>
+        <v>104.23520000000001</v>
       </c>
       <c r="O141" t="s">
         <v>856</v>
@@ -11388,10 +11388,10 @@
         <v>14</v>
       </c>
       <c r="M142" s="3">
-        <v>-3.2561460000000002</v>
+        <v>-3.2852000000000001</v>
       </c>
       <c r="N142" s="3">
-        <v>129.05312000000001</v>
+        <v>128.95519999999999</v>
       </c>
       <c r="O142" t="s">
         <v>857</v>
@@ -11444,10 +11444,10 @@
         <v>14</v>
       </c>
       <c r="M143" s="3">
-        <v>-2.9676178000000002</v>
+        <v>-2.9851999999999999</v>
       </c>
       <c r="N143" s="3">
-        <v>104.7367697</v>
+        <v>104.7552</v>
       </c>
       <c r="O143" t="s">
         <v>858</v>
@@ -11500,10 +11500,10 @@
         <v>14</v>
       </c>
       <c r="M144" s="3">
-        <v>-2.9838331999999999</v>
+        <v>-2.9912000000000001</v>
       </c>
       <c r="N144" s="3">
-        <v>104.76467510000001</v>
+        <v>104.7612</v>
       </c>
       <c r="O144" t="s">
         <v>859</v>
@@ -11556,10 +11556,10 @@
         <v>14</v>
       </c>
       <c r="M145" s="3">
-        <v>-2.6214301999999998</v>
+        <v>-2.9251999999999998</v>
       </c>
       <c r="N145" s="3">
-        <v>140.68573069999999</v>
+        <v>140.70519999999999</v>
       </c>
       <c r="O145" t="s">
         <v>860</v>
@@ -11612,10 +11612,10 @@
         <v>14</v>
       </c>
       <c r="M146" s="3">
-        <v>-2.5344350000000002</v>
+        <v>-2.5352000000000001</v>
       </c>
       <c r="N146" s="3">
-        <v>140.71141</v>
+        <v>140.7182</v>
       </c>
       <c r="O146" t="s">
         <v>861</v>
@@ -11668,10 +11668,10 @@
         <v>14</v>
       </c>
       <c r="M147" s="3">
-        <v>-2.1588735699999999</v>
+        <v>-2.1352000000000002</v>
       </c>
       <c r="N147" s="3">
-        <v>106.12224426</v>
+        <v>106.1182</v>
       </c>
       <c r="O147" t="s">
         <v>862</v>
@@ -11724,10 +11724,10 @@
         <v>14</v>
       </c>
       <c r="M148" s="3">
-        <v>-2.1456040000000001</v>
+        <v>-2.1252</v>
       </c>
       <c r="N148" s="3">
-        <v>106.111982</v>
+        <v>106.1052</v>
       </c>
       <c r="O148" t="s">
         <v>863</v>
@@ -11780,10 +11780,10 @@
         <v>14</v>
       </c>
       <c r="M149" s="3">
-        <v>-2.1441699999999999</v>
+        <v>-2.1252</v>
       </c>
       <c r="N149" s="3">
-        <v>106.11972</v>
+        <v>106.1122</v>
       </c>
       <c r="O149" t="s">
         <v>864</v>
@@ -11836,10 +11836,10 @@
         <v>14</v>
       </c>
       <c r="M150" s="3">
-        <v>-2.1206733</v>
+        <v>-2.1452</v>
       </c>
       <c r="N150" s="3">
-        <v>106.11346039999999</v>
+        <v>106.1182</v>
       </c>
       <c r="O150" t="s">
         <v>865</v>
@@ -11892,10 +11892,10 @@
         <v>14</v>
       </c>
       <c r="M151" s="3">
-        <v>-1.912757</v>
+        <v>-1.9052</v>
       </c>
       <c r="N151" s="3">
-        <v>116.19811900000001</v>
+        <v>116.18519999999999</v>
       </c>
       <c r="O151" t="s">
         <v>866</v>
@@ -11948,10 +11948,10 @@
         <v>14</v>
       </c>
       <c r="M152" s="3">
-        <v>1.0263899999999999</v>
+        <v>1.0451999999999999</v>
       </c>
       <c r="N152" s="3">
-        <v>103.98111</v>
+        <v>103.9652</v>
       </c>
       <c r="O152" t="s">
         <v>867</v>
@@ -12004,10 +12004,10 @@
         <v>14</v>
       </c>
       <c r="M153" s="3">
-        <v>-2.608026133333333</v>
+        <v>-2.5851999999999999</v>
       </c>
       <c r="N153" s="3">
-        <v>140.67375849999999</v>
+        <v>140.70519999999999</v>
       </c>
       <c r="O153" t="s">
         <v>868</v>
@@ -12060,10 +12060,10 @@
         <v>14</v>
       </c>
       <c r="M154" s="3">
-        <v>-1.5889009999999999</v>
+        <v>-1.5751999999999999</v>
       </c>
       <c r="N154" s="3">
-        <v>103.61540100000001</v>
+        <v>103.6152</v>
       </c>
       <c r="O154" t="s">
         <v>869</v>
@@ -12116,10 +12116,10 @@
         <v>14</v>
       </c>
       <c r="M155" s="3">
-        <v>1.1101262999999999</v>
+        <v>-1.8552</v>
       </c>
       <c r="N155" s="3">
-        <v>103.96294709999999</v>
+        <v>109.65519999999999</v>
       </c>
       <c r="O155" t="s">
         <v>870</v>
@@ -12172,10 +12172,10 @@
         <v>14</v>
       </c>
       <c r="M156" s="3">
-        <v>-1.2701958</v>
+        <v>-1.2452000000000001</v>
       </c>
       <c r="N156" s="3">
-        <v>116.8552771</v>
+        <v>116.8552</v>
       </c>
       <c r="O156" t="s">
         <v>871</v>
@@ -12228,10 +12228,10 @@
         <v>14</v>
       </c>
       <c r="M157" s="3">
-        <v>-1.2741807999999999</v>
+        <v>-1.2682</v>
       </c>
       <c r="N157" s="3">
-        <v>116.87338389999999</v>
+        <v>116.8252</v>
       </c>
       <c r="O157" t="s">
         <v>872</v>
@@ -12284,10 +12284,10 @@
         <v>14</v>
       </c>
       <c r="M158" s="3">
-        <v>-1.2469279551724139</v>
+        <v>-1.2582</v>
       </c>
       <c r="N158" s="3">
-        <v>116.87886207931039</v>
+        <v>116.8582</v>
       </c>
       <c r="O158" t="s">
         <v>873</v>
@@ -12340,10 +12340,10 @@
         <v>14</v>
       </c>
       <c r="M159" s="3">
-        <v>-8.6895059999999997</v>
+        <v>-1.2452000000000001</v>
       </c>
       <c r="N159" s="3">
-        <v>121.041577</v>
+        <v>116.8352</v>
       </c>
       <c r="O159" t="s">
         <v>874</v>
@@ -12396,10 +12396,10 @@
         <v>14</v>
       </c>
       <c r="M160" s="3">
-        <v>-1.2273569</v>
+        <v>-1.2452000000000001</v>
       </c>
       <c r="N160" s="3">
-        <v>116.8409571</v>
+        <v>116.8282</v>
       </c>
       <c r="O160" t="s">
         <v>875</v>
@@ -12452,10 +12452,10 @@
         <v>14</v>
       </c>
       <c r="M161" s="3">
-        <v>-1.220844</v>
+        <v>-6.2652000000000001</v>
       </c>
       <c r="N161" s="3">
-        <v>116.849977</v>
+        <v>107.1052</v>
       </c>
       <c r="O161" t="s">
         <v>876</v>
@@ -12508,10 +12508,10 @@
         <v>14</v>
       </c>
       <c r="M162" s="3">
-        <v>-6.1946669999999999</v>
+        <v>-6.1981999999999999</v>
       </c>
       <c r="N162" s="3">
-        <v>106.816604</v>
+        <v>106.8182</v>
       </c>
       <c r="O162" t="s">
         <v>877</v>
@@ -12564,10 +12564,10 @@
         <v>14</v>
       </c>
       <c r="M163" s="3">
-        <v>-6.2254942</v>
+        <v>-6.2234999999999996</v>
       </c>
       <c r="N163" s="3">
-        <v>106.80373849999999</v>
+        <v>106.80419999999999</v>
       </c>
       <c r="O163" t="s">
         <v>878</v>
@@ -12620,10 +12620,10 @@
         <v>14</v>
       </c>
       <c r="M164" s="3">
-        <v>-6.212796</v>
+        <v>-6.2161999999999997</v>
       </c>
       <c r="N164" s="3">
-        <v>106.80374500000001</v>
+        <v>106.8032</v>
       </c>
       <c r="O164" t="s">
         <v>879</v>
@@ -12676,10 +12676,10 @@
         <v>14</v>
       </c>
       <c r="M165" s="3">
-        <v>-0.92326799999999998</v>
+        <v>-6.2351999999999999</v>
       </c>
       <c r="N165" s="3">
-        <v>100.36126489999999</v>
+        <v>106.8352</v>
       </c>
       <c r="O165" t="s">
         <v>880</v>
@@ -12732,10 +12732,10 @@
         <v>14</v>
       </c>
       <c r="M166" s="3">
-        <v>-0.87409360000000003</v>
+        <v>-0.87519999999999998</v>
       </c>
       <c r="N166" s="3">
-        <v>131.3081554</v>
+        <v>131.2552</v>
       </c>
       <c r="O166" t="s">
         <v>881</v>
@@ -12788,10 +12788,10 @@
         <v>14</v>
       </c>
       <c r="M167" s="3">
-        <v>-0.49953799999999998</v>
+        <v>-0.48520000000000002</v>
       </c>
       <c r="N167" s="3">
-        <v>117.166201</v>
+        <v>117.1452</v>
       </c>
       <c r="O167" t="s">
         <v>882</v>
@@ -12844,10 +12844,10 @@
         <v>14</v>
       </c>
       <c r="M168" s="3">
-        <v>-0.3051973</v>
+        <v>-0.30520000000000003</v>
       </c>
       <c r="N168" s="3">
-        <v>100.3688628</v>
+        <v>100.37520000000001</v>
       </c>
       <c r="O168" t="s">
         <v>883</v>
@@ -12900,10 +12900,10 @@
         <v>14</v>
       </c>
       <c r="M169" s="3">
-        <v>-0.89556800000000003</v>
+        <v>-0.91520000000000001</v>
       </c>
       <c r="N169" s="3">
-        <v>100.445199</v>
+        <v>100.3552</v>
       </c>
       <c r="O169" t="s">
         <v>884</v>
@@ -12956,10 +12956,10 @@
         <v>14</v>
       </c>
       <c r="M170" s="3">
-        <v>0.13828799999999999</v>
+        <v>0.13519999999999999</v>
       </c>
       <c r="N170" s="3">
-        <v>117.46337629999999</v>
+        <v>117.48520000000001</v>
       </c>
       <c r="O170" t="s">
         <v>885</v>
@@ -13012,10 +13012,10 @@
         <v>14</v>
       </c>
       <c r="M171" s="3">
-        <v>0.46439130000000001</v>
+        <v>0.5252</v>
       </c>
       <c r="N171" s="3">
-        <v>101.36961700000001</v>
+        <v>101.4452</v>
       </c>
       <c r="O171" t="s">
         <v>886</v>
@@ -13068,10 +13068,10 @@
         <v>14</v>
       </c>
       <c r="M172" s="3">
-        <v>0.50317080000000003</v>
+        <v>0.51519999999999999</v>
       </c>
       <c r="N172" s="3">
-        <v>101.42177649999999</v>
+        <v>101.4452</v>
       </c>
       <c r="O172" t="s">
         <v>887</v>
@@ -13124,10 +13124,10 @@
         <v>14</v>
       </c>
       <c r="M173" s="3">
-        <v>0.53524389999999999</v>
+        <v>0.50519999999999998</v>
       </c>
       <c r="N173" s="3">
-        <v>101.4353785</v>
+        <v>101.4552</v>
       </c>
       <c r="O173" t="s">
         <v>888</v>
@@ -13180,10 +13180,10 @@
         <v>14</v>
       </c>
       <c r="M174" s="3">
-        <v>0.53944000000000003</v>
+        <v>0.51819999999999999</v>
       </c>
       <c r="N174" s="3">
-        <v>101.43194</v>
+        <v>101.43519999999999</v>
       </c>
       <c r="O174" t="s">
         <v>889</v>
@@ -13236,10 +13236,10 @@
         <v>14</v>
       </c>
       <c r="M175" s="3">
-        <v>-2.1623999999999999</v>
+        <v>0.91520000000000001</v>
       </c>
       <c r="N175" s="3">
-        <v>115.9207</v>
+        <v>104.5552</v>
       </c>
       <c r="O175" t="s">
         <v>890</v>
@@ -13292,10 +13292,10 @@
         <v>14</v>
       </c>
       <c r="M176" s="3">
-        <v>-5.1576719999999998</v>
+        <v>0.91520000000000001</v>
       </c>
       <c r="N176" s="3">
-        <v>119.49603</v>
+        <v>104.4552</v>
       </c>
       <c r="O176" t="s">
         <v>891</v>
@@ -13348,10 +13348,10 @@
         <v>14</v>
       </c>
       <c r="M177" s="3">
-        <v>-6.9678800000000001</v>
+        <v>0.92520000000000002</v>
       </c>
       <c r="N177" s="3">
-        <v>110.426658</v>
+        <v>104.4552</v>
       </c>
       <c r="O177" t="s">
         <v>892</v>
@@ -13404,10 +13404,10 @@
         <v>14</v>
       </c>
       <c r="M178" s="3">
-        <v>0.53212890000000002</v>
+        <v>0.53520000000000001</v>
       </c>
       <c r="N178" s="3">
-        <v>101.4550909</v>
+        <v>101.4452</v>
       </c>
       <c r="O178" t="s">
         <v>893</v>
@@ -13460,10 +13460,10 @@
         <v>14</v>
       </c>
       <c r="M179" s="3">
-        <v>1.1012575250000001</v>
+        <v>1.0351999999999999</v>
       </c>
       <c r="N179" s="3">
-        <v>103.94777141874999</v>
+        <v>103.9552</v>
       </c>
       <c r="O179" t="s">
         <v>894</v>
@@ -13516,10 +13516,10 @@
         <v>14</v>
       </c>
       <c r="M180" s="3">
-        <v>1.0517665</v>
+        <v>1.0351999999999999</v>
       </c>
       <c r="N180" s="3">
-        <v>103.9695346</v>
+        <v>104.01519999999999</v>
       </c>
       <c r="O180" t="s">
         <v>895</v>
@@ -13572,10 +13572,10 @@
         <v>14</v>
       </c>
       <c r="M181" s="3">
-        <v>1.0666800000000001</v>
+        <v>1.1352</v>
       </c>
       <c r="N181" s="3">
-        <v>103.988912</v>
+        <v>104.01519999999999</v>
       </c>
       <c r="O181" t="s">
         <v>896</v>
@@ -13628,10 +13628,10 @@
         <v>14</v>
       </c>
       <c r="M182" s="3">
-        <v>1.1186100000000001</v>
+        <v>1.1252</v>
       </c>
       <c r="N182" s="3">
-        <v>104.05806</v>
+        <v>104.0552</v>
       </c>
       <c r="O182" t="s">
         <v>897</v>
@@ -13684,10 +13684,10 @@
         <v>14</v>
       </c>
       <c r="M183" s="3">
-        <v>1.0666800000000001</v>
+        <v>1.1452</v>
       </c>
       <c r="N183" s="3">
-        <v>103.988912</v>
+        <v>104.0082</v>
       </c>
       <c r="O183" t="s">
         <v>898</v>
@@ -13740,10 +13740,10 @@
         <v>14</v>
       </c>
       <c r="M184" s="3">
-        <v>0.4866393</v>
+        <v>1.1282000000000001</v>
       </c>
       <c r="N184" s="3">
-        <v>101.454866</v>
+        <v>104.01220000000001</v>
       </c>
       <c r="O184" t="s">
         <v>899</v>
@@ -13796,10 +13796,10 @@
         <v>14</v>
       </c>
       <c r="M185" s="3">
-        <v>1.1228400000000001</v>
+        <v>1.1452</v>
       </c>
       <c r="N185" s="3">
-        <v>104.01383</v>
+        <v>104.01519999999999</v>
       </c>
       <c r="O185" t="s">
         <v>900</v>
@@ -13852,10 +13852,10 @@
         <v>14</v>
       </c>
       <c r="M186" s="3">
-        <v>1.1068309999999999</v>
+        <v>1.1352</v>
       </c>
       <c r="N186" s="3">
-        <v>104.08190980000001</v>
+        <v>104.0252</v>
       </c>
       <c r="O186" t="s">
         <v>901</v>
@@ -13908,10 +13908,10 @@
         <v>14</v>
       </c>
       <c r="M187" s="3">
-        <v>1.1353195510638301</v>
+        <v>1.1252</v>
       </c>
       <c r="N187" s="3">
-        <v>104.0112395659575</v>
+        <v>104.04519999999999</v>
       </c>
       <c r="O187" t="s">
         <v>902</v>
@@ -13964,10 +13964,10 @@
         <v>14</v>
       </c>
       <c r="M188" s="3">
-        <v>1.0666800000000001</v>
+        <v>1.1552</v>
       </c>
       <c r="N188" s="3">
-        <v>103.988912</v>
+        <v>104.0352</v>
       </c>
       <c r="O188" t="s">
         <v>903</v>
@@ -14020,10 +14020,10 @@
         <v>14</v>
       </c>
       <c r="M189" s="3">
-        <v>1.4868062</v>
+        <v>1.4912000000000001</v>
       </c>
       <c r="N189" s="3">
-        <v>124.8386173</v>
+        <v>124.8421</v>
       </c>
       <c r="O189" t="s">
         <v>904</v>
@@ -14076,10 +14076,10 @@
         <v>14</v>
       </c>
       <c r="M190" s="3">
-        <v>1.5003886</v>
+        <v>1.4552</v>
       </c>
       <c r="N190" s="3">
-        <v>124.89865210000001</v>
+        <v>124.9182</v>
       </c>
       <c r="O190" t="s">
         <v>905</v>
@@ -14132,10 +14132,10 @@
         <v>14</v>
       </c>
       <c r="M191" s="3">
-        <v>1.7116926636363641</v>
+        <v>1.7552000000000001</v>
       </c>
       <c r="N191" s="3">
-        <v>100.4766108545455</v>
+        <v>100.43519999999999</v>
       </c>
       <c r="O191" t="s">
         <v>906</v>
@@ -14188,10 +14188,10 @@
         <v>14</v>
       </c>
       <c r="M192" s="3">
-        <v>1.659</v>
+        <v>1.6852</v>
       </c>
       <c r="N192" s="3">
-        <v>101.383</v>
+        <v>101.4452</v>
       </c>
       <c r="O192" t="s">
         <v>907</v>
@@ -14244,10 +14244,10 @@
         <v>14</v>
       </c>
       <c r="M193" s="3">
-        <v>0.53203999999999996</v>
+        <v>3.5851999999999999</v>
       </c>
       <c r="N193" s="3">
-        <v>101.448266</v>
+        <v>98.675200000000004</v>
       </c>
       <c r="O193" t="s">
         <v>908</v>
@@ -14300,10 +14300,10 @@
         <v>14</v>
       </c>
       <c r="M194" s="3">
-        <v>3.1177800000000002</v>
+        <v>3.1052</v>
       </c>
       <c r="N194" s="3">
-        <v>98.385000000000005</v>
+        <v>98.485200000000006</v>
       </c>
       <c r="O194" t="s">
         <v>909</v>
@@ -14356,10 +14356,10 @@
         <v>14</v>
       </c>
       <c r="M195" s="3">
-        <v>-6.2733509999999999</v>
+        <v>-6.2652000000000001</v>
       </c>
       <c r="N195" s="3">
-        <v>106.976947</v>
+        <v>106.98520000000001</v>
       </c>
       <c r="O195" t="s">
         <v>910</v>
@@ -14412,10 +14412,10 @@
         <v>14</v>
       </c>
       <c r="M196" s="3">
-        <v>3.5905900000000002</v>
+        <v>3.5952000000000002</v>
       </c>
       <c r="N196" s="3">
-        <v>98.676479999999998</v>
+        <v>98.655199999999994</v>
       </c>
       <c r="O196" t="s">
         <v>911</v>
@@ -14468,10 +14468,10 @@
         <v>14</v>
       </c>
       <c r="M197" s="3">
-        <v>3.6309846000000001</v>
+        <v>3.6751999999999998</v>
       </c>
       <c r="N197" s="3">
-        <v>98.648010200000002</v>
+        <v>98.665199999999999</v>
       </c>
       <c r="O197" t="s">
         <v>912</v>
@@ -14524,10 +14524,10 @@
         <v>14</v>
       </c>
       <c r="M198" s="3">
-        <v>3.5291700000000001</v>
+        <v>3.5352000000000001</v>
       </c>
       <c r="N198" s="3">
-        <v>98.669719999999998</v>
+        <v>98.655199999999994</v>
       </c>
       <c r="O198" t="s">
         <v>913</v>
@@ -14580,10 +14580,10 @@
         <v>14</v>
       </c>
       <c r="M199" s="3">
-        <v>3.5742352999999998</v>
+        <v>3.5552000000000001</v>
       </c>
       <c r="N199" s="3">
-        <v>98.626040900000007</v>
+        <v>98.635199999999998</v>
       </c>
       <c r="O199" t="s">
         <v>914</v>
@@ -14636,10 +14636,10 @@
         <v>14</v>
       </c>
       <c r="M200" s="3">
-        <v>3.5751759999999999</v>
+        <v>3.6152000000000002</v>
       </c>
       <c r="N200" s="3">
-        <v>98.695500999999993</v>
+        <v>98.6952</v>
       </c>
       <c r="O200" t="s">
         <v>915</v>
@@ -14692,10 +14692,10 @@
         <v>14</v>
       </c>
       <c r="M201" s="3">
-        <v>3.5837566000000001</v>
+        <v>3.5851999999999999</v>
       </c>
       <c r="N201" s="3">
-        <v>98.672223900000006</v>
+        <v>98.682100000000005</v>
       </c>
       <c r="O201" t="s">
         <v>916</v>
@@ -14748,10 +14748,10 @@
         <v>14</v>
       </c>
       <c r="M202" s="3">
-        <v>3.5810686</v>
+        <v>3.5811999999999999</v>
       </c>
       <c r="N202" s="3">
-        <v>98.667586299999996</v>
+        <v>98.665199999999999</v>
       </c>
       <c r="O202" t="s">
         <v>917</v>
@@ -14804,10 +14804,10 @@
         <v>14</v>
       </c>
       <c r="M203" s="3">
-        <v>3.5631016999999998</v>
+        <v>3.5781999999999998</v>
       </c>
       <c r="N203" s="3">
-        <v>98.693543000000005</v>
+        <v>98.685199999999995</v>
       </c>
       <c r="O203" t="s">
         <v>918</v>
@@ -14860,10 +14860,10 @@
         <v>14</v>
       </c>
       <c r="M204" s="3">
-        <v>3.62209</v>
+        <v>3.5811999999999999</v>
       </c>
       <c r="N204" s="3">
-        <v>98.689914000000002</v>
+        <v>98.675200000000004</v>
       </c>
       <c r="O204" t="s">
         <v>919</v>
@@ -14916,10 +14916,10 @@
         <v>14</v>
       </c>
       <c r="M205" s="3">
-        <v>3.678639</v>
+        <v>4.1452</v>
       </c>
       <c r="N205" s="3">
-        <v>98.6571</v>
+        <v>96.135199999999998</v>
       </c>
       <c r="O205" t="s">
         <v>920</v>
@@ -14972,10 +14972,10 @@
         <v>14</v>
       </c>
       <c r="M206" s="3">
-        <v>4.4797067999999998</v>
+        <v>4.4752000000000001</v>
       </c>
       <c r="N206" s="3">
-        <v>97.955706800000002</v>
+        <v>97.965199999999996</v>
       </c>
       <c r="O206" t="s">
         <v>921</v>
@@ -15028,10 +15028,10 @@
         <v>14</v>
       </c>
       <c r="M207" s="3">
-        <v>5.1760143999999997</v>
+        <v>5.1852</v>
       </c>
       <c r="N207" s="3">
-        <v>97.140679000000006</v>
+        <v>97.145200000000003</v>
       </c>
       <c r="O207" t="s">
         <v>922</v>
@@ -15084,10 +15084,10 @@
         <v>14</v>
       </c>
       <c r="M208" s="3">
-        <v>5.1944135999999999</v>
+        <v>5.2051999999999996</v>
       </c>
       <c r="N208" s="3">
-        <v>96.721269000000007</v>
+        <v>96.705200000000005</v>
       </c>
       <c r="O208" t="s">
         <v>923</v>
@@ -15140,10 +15140,10 @@
         <v>14</v>
       </c>
       <c r="M209" s="3">
-        <v>5.5551903999999999</v>
+        <v>5.5552000000000001</v>
       </c>
       <c r="N209" s="3">
-        <v>95.321732699999998</v>
+        <v>95.315200000000004</v>
       </c>
       <c r="O209" t="s">
         <v>924</v>
@@ -15196,10 +15196,10 @@
         <v>14</v>
       </c>
       <c r="M210" s="3">
-        <v>1.1353195510638301</v>
+        <v>1.1452</v>
       </c>
       <c r="N210" s="3">
-        <v>104.0112395659575</v>
+        <v>104.0082</v>
       </c>
       <c r="O210" t="s">
         <v>925</v>
@@ -15252,10 +15252,10 @@
         <v>14</v>
       </c>
       <c r="M211" s="3">
-        <v>-6.1639169999999996</v>
+        <v>3.5851999999999999</v>
       </c>
       <c r="N211" s="3">
-        <v>106.8334381</v>
+        <v>98.675200000000004</v>
       </c>
       <c r="O211" t="s">
         <v>926</v>
@@ -15308,10 +15308,10 @@
         <v>14</v>
       </c>
       <c r="M212" s="3">
-        <v>-6.1453369999999996</v>
+        <v>-6.1551999999999998</v>
       </c>
       <c r="N212" s="3">
-        <v>106.9258129</v>
+        <v>106.8152</v>
       </c>
       <c r="O212" t="s">
         <v>927</v>
@@ -15364,10 +15364,10 @@
         <v>14</v>
       </c>
       <c r="M213" s="3">
-        <v>-6.3833089999999997</v>
+        <v>-6.3752000000000004</v>
       </c>
       <c r="N213" s="3">
-        <v>106.938772</v>
+        <v>106.9452</v>
       </c>
       <c r="O213" t="s">
         <v>928</v>
@@ -15420,10 +15420,10 @@
         <v>14</v>
       </c>
       <c r="M214" s="3">
-        <v>-6.1435529987261148</v>
+        <v>-6.1452</v>
       </c>
       <c r="N214" s="3">
-        <v>106.73284931273879</v>
+        <v>106.73520000000001</v>
       </c>
       <c r="O214" t="s">
         <v>929</v>
@@ -15476,10 +15476,10 @@
         <v>14</v>
       </c>
       <c r="M215" s="3">
-        <v>-1.7112200000000001E-2</v>
+        <v>-2.52E-2</v>
       </c>
       <c r="N215" s="3">
-        <v>109.3411574</v>
+        <v>109.3352</v>
       </c>
       <c r="O215" t="s">
         <v>930</v>
@@ -15532,10 +15532,10 @@
         <v>14</v>
       </c>
       <c r="M216" s="3">
-        <v>1.1509210000000001</v>
+        <v>1.0451999999999999</v>
       </c>
       <c r="N216" s="3">
-        <v>104.11216899999999</v>
+        <v>104.0352</v>
       </c>
       <c r="O216" t="s">
         <v>931</v>
@@ -15588,10 +15588,10 @@
         <v>14</v>
       </c>
       <c r="M217" s="3">
-        <v>-6.2586050000000002</v>
+        <v>-6.2552000000000003</v>
       </c>
       <c r="N217" s="3">
-        <v>107.02167</v>
+        <v>107.01519999999999</v>
       </c>
       <c r="O217" t="s">
         <v>932</v>
@@ -15644,10 +15644,10 @@
         <v>14</v>
       </c>
       <c r="M218" s="3">
-        <v>-6.1601239999999997</v>
+        <v>-6.1551999999999998</v>
       </c>
       <c r="N218" s="3">
-        <v>106.906481</v>
+        <v>106.90519999999999</v>
       </c>
       <c r="O218" t="s">
         <v>933</v>
@@ -15700,10 +15700,10 @@
         <v>14</v>
       </c>
       <c r="M219" s="3">
-        <v>-5.1529790999999996</v>
+        <v>-5.1524999999999999</v>
       </c>
       <c r="N219" s="3">
-        <v>119.403638</v>
+        <v>119.40819999999999</v>
       </c>
       <c r="O219" t="s">
         <v>934</v>
@@ -15756,10 +15756,10 @@
         <v>14</v>
       </c>
       <c r="M220" s="3">
-        <v>-5.4604255000000004</v>
+        <v>-3.4651999999999998</v>
       </c>
       <c r="N220" s="3">
-        <v>122.620175</v>
+        <v>122.62520000000001</v>
       </c>
       <c r="O220" t="s">
         <v>935</v>
@@ -15812,10 +15812,10 @@
         <v>14</v>
       </c>
       <c r="M221" s="3">
-        <v>-7.7201797000000001</v>
+        <v>-7.7282000000000002</v>
       </c>
       <c r="N221" s="3">
-        <v>110.361913</v>
+        <v>110.3552</v>
       </c>
       <c r="O221" t="s">
         <v>936</v>
@@ -15868,10 +15868,10 @@
         <v>14</v>
       </c>
       <c r="M222" s="3">
-        <v>-7.8074242500000004</v>
+        <v>-7.8011999999999997</v>
       </c>
       <c r="N222" s="3">
-        <v>110.3707273</v>
+        <v>110.3682</v>
       </c>
       <c r="O222" t="s">
         <v>937</v>
@@ -15924,10 +15924,10 @@
         <v>14</v>
       </c>
       <c r="M223" s="3">
-        <v>-7.5277799999999999</v>
+        <v>-6.8925000000000001</v>
       </c>
       <c r="N223" s="3">
-        <v>110.36417</v>
+        <v>107.6082</v>
       </c>
       <c r="O223" t="s">
         <v>938</v>
@@ -15980,10 +15980,10 @@
         <v>14</v>
       </c>
       <c r="M224" s="3">
-        <v>-6.9267310000000002</v>
+        <v>-6.9252000000000002</v>
       </c>
       <c r="N224" s="3">
-        <v>107.6059089</v>
+        <v>107.6052</v>
       </c>
       <c r="O224" t="s">
         <v>939</v>
@@ -16036,10 +16036,10 @@
         <v>14</v>
       </c>
       <c r="M225" s="3">
-        <v>-7.3269234000000001</v>
+        <v>-6.9211999999999998</v>
       </c>
       <c r="N225" s="3">
-        <v>110.5049942</v>
+        <v>107.6082</v>
       </c>
       <c r="O225" t="s">
         <v>940</v>
@@ -16092,10 +16092,10 @@
         <v>14</v>
       </c>
       <c r="M226" s="3">
-        <v>-6.9153231999999996</v>
+        <v>-6.9151999999999996</v>
       </c>
       <c r="N226" s="3">
-        <v>107.63409299999999</v>
+        <v>107.6352</v>
       </c>
       <c r="O226" t="s">
         <v>941</v>
@@ -16148,10 +16148,10 @@
         <v>14</v>
       </c>
       <c r="M227" s="3">
-        <v>-6.9415209999999998</v>
+        <v>-6.9252000000000002</v>
       </c>
       <c r="N227" s="3">
-        <v>106.9545294</v>
+        <v>106.9282</v>
       </c>
       <c r="O227" t="s">
         <v>942</v>
@@ -16204,10 +16204,10 @@
         <v>14</v>
       </c>
       <c r="M228" s="3">
-        <v>7.8957299999999994E-2</v>
+        <v>-7.2182000000000004</v>
       </c>
       <c r="N228" s="3">
-        <v>111.484825</v>
+        <v>107.90519999999999</v>
       </c>
       <c r="O228" t="s">
         <v>943</v>
@@ -16260,10 +16260,10 @@
         <v>14</v>
       </c>
       <c r="M229" s="3">
-        <v>-7.8333089999999999</v>
+        <v>-7.8182</v>
       </c>
       <c r="N229" s="3">
-        <v>112.016654</v>
+        <v>112.01519999999999</v>
       </c>
       <c r="O229" t="s">
         <v>944</v>
@@ -16316,10 +16316,10 @@
         <v>14</v>
       </c>
       <c r="M230" s="3">
-        <v>-7.6247069999999999</v>
+        <v>-7.6252000000000004</v>
       </c>
       <c r="N230" s="3">
-        <v>111.520747</v>
+        <v>111.5312</v>
       </c>
       <c r="O230" t="s">
         <v>945</v>
@@ -16372,10 +16372,10 @@
         <v>14</v>
       </c>
       <c r="M231" s="3">
-        <v>-8.2109100000000002</v>
+        <v>-8.2181999999999995</v>
       </c>
       <c r="N231" s="3">
-        <v>114.37748999999999</v>
+        <v>114.3652</v>
       </c>
       <c r="O231" t="s">
         <v>946</v>
@@ -16428,10 +16428,10 @@
         <v>14</v>
       </c>
       <c r="M232" s="3">
-        <v>-7.2549143000000003</v>
+        <v>-7.2481999999999998</v>
       </c>
       <c r="N232" s="3">
-        <v>112.7334286</v>
+        <v>112.73820000000001</v>
       </c>
       <c r="O232" t="s">
         <v>947</v>
@@ -16484,10 +16484,10 @@
         <v>14</v>
       </c>
       <c r="M233" s="3">
-        <v>-7.2550763500000004</v>
+        <v>-1.8552</v>
       </c>
       <c r="N233" s="3">
-        <v>112.7248373</v>
+        <v>109.65519999999999</v>
       </c>
       <c r="O233" t="s">
         <v>948</v>
@@ -16540,10 +16540,10 @@
         <v>14</v>
       </c>
       <c r="M234" s="3">
-        <v>-7.3202049999999996</v>
+        <v>-7.2552000000000003</v>
       </c>
       <c r="N234" s="3">
-        <v>112.73196299999999</v>
+        <v>112.7452</v>
       </c>
       <c r="O234" t="s">
         <v>949</v>
@@ -16596,10 +16596,10 @@
         <v>14</v>
       </c>
       <c r="M235" s="3">
-        <v>-10.1746246</v>
+        <v>-10.1652</v>
       </c>
       <c r="N235" s="3">
-        <v>123.6131673</v>
+        <v>123.6082</v>
       </c>
       <c r="O235" t="s">
         <v>950</v>
@@ -16652,10 +16652,10 @@
         <v>14</v>
       </c>
       <c r="M236" s="3">
-        <v>-8.5907599000000001</v>
+        <v>-8.5852000000000004</v>
       </c>
       <c r="N236" s="3">
-        <v>116.1257243</v>
+        <v>116.1152</v>
       </c>
       <c r="O236" t="s">
         <v>951</v>
@@ -16708,10 +16708,10 @@
         <v>14</v>
       </c>
       <c r="M237" s="3">
-        <v>-7.4500766</v>
+        <v>-7.4551999999999996</v>
       </c>
       <c r="N237" s="3">
-        <v>112.7103484</v>
+        <v>112.7152</v>
       </c>
       <c r="O237" t="s">
         <v>952</v>
@@ -16764,10 +16764,10 @@
         <v>14</v>
       </c>
       <c r="M238" s="3">
-        <v>-8.1795223571428561</v>
+        <v>-8.1752000000000002</v>
       </c>
       <c r="N238" s="3">
-        <v>113.69612815714289</v>
+        <v>113.7052</v>
       </c>
       <c r="O238" t="s">
         <v>953</v>
@@ -16820,10 +16820,10 @@
         <v>14</v>
       </c>
       <c r="M239" s="3">
-        <v>-7.8766036000000001</v>
+        <v>-7.8852000000000002</v>
       </c>
       <c r="N239" s="3">
-        <v>112.5320945</v>
+        <v>112.5252</v>
       </c>
       <c r="O239" t="s">
         <v>954</v>
@@ -16876,10 +16876,10 @@
         <v>14</v>
       </c>
       <c r="M240" s="3">
-        <v>-7.2744900000000001</v>
+        <v>-7.6012000000000004</v>
       </c>
       <c r="N240" s="3">
-        <v>112.782014</v>
+        <v>110.8124</v>
       </c>
       <c r="O240" t="s">
         <v>955</v>
@@ -16932,10 +16932,10 @@
         <v>14</v>
       </c>
       <c r="M241" s="3">
-        <v>-7.9695180611111107</v>
+        <v>-7.9752000000000001</v>
       </c>
       <c r="N241" s="3">
-        <v>112.6196578</v>
+        <v>112.62820000000001</v>
       </c>
       <c r="O241" t="s">
         <v>956</v>
@@ -16988,10 +16988,10 @@
         <v>14</v>
       </c>
       <c r="M242" s="3">
-        <v>-2.608026133333333</v>
+        <v>-2.5952000000000002</v>
       </c>
       <c r="N242" s="3">
-        <v>140.67375849999999</v>
+        <v>140.6652</v>
       </c>
       <c r="O242" t="s">
         <v>957</v>
@@ -17044,10 +17044,10 @@
         <v>14</v>
       </c>
       <c r="M243" s="3">
-        <v>-7.4559673000000002</v>
+        <v>-7.4551999999999996</v>
       </c>
       <c r="N243" s="3">
-        <v>112.7096712</v>
+        <v>112.7152</v>
       </c>
       <c r="O243" t="s">
         <v>958</v>
@@ -17100,10 +17100,10 @@
         <v>14</v>
       </c>
       <c r="M244" s="3">
-        <v>-6.2609820999999997</v>
+        <v>-6.2351999999999999</v>
       </c>
       <c r="N244" s="3">
-        <v>107.1434466</v>
+        <v>107.15519999999999</v>
       </c>
       <c r="O244" t="s">
         <v>959</v>
@@ -17156,10 +17156,10 @@
         <v>14</v>
       </c>
       <c r="M245" s="3">
-        <v>-6.5246949000000001</v>
+        <v>-6.5552000000000001</v>
       </c>
       <c r="N245" s="3">
-        <v>106.8320485</v>
+        <v>106.8582</v>
       </c>
       <c r="O245" t="s">
         <v>960</v>
@@ -17212,10 +17212,10 @@
         <v>14</v>
       </c>
       <c r="M246" s="3">
-        <v>-6.4804063000000003</v>
+        <v>-6.4851999999999999</v>
       </c>
       <c r="N246" s="3">
-        <v>106.86264679999999</v>
+        <v>106.8522</v>
       </c>
       <c r="O246" t="s">
         <v>961</v>
@@ -17268,10 +17268,10 @@
         <v>14</v>
       </c>
       <c r="M247" s="3">
-        <v>-6.1877168999999999</v>
+        <v>-6.1852</v>
       </c>
       <c r="N247" s="3">
-        <v>106.82375570000001</v>
+        <v>106.8222</v>
       </c>
       <c r="O247" t="s">
         <v>962</v>
@@ -17324,10 +17324,10 @@
         <v>14</v>
       </c>
       <c r="M248" s="3">
-        <v>-6.3837862999999997</v>
+        <v>-6.3724999999999996</v>
       </c>
       <c r="N248" s="3">
-        <v>106.81271649999999</v>
+        <v>106.8325</v>
       </c>
       <c r="O248" t="s">
         <v>963</v>
@@ -17380,10 +17380,10 @@
         <v>14</v>
       </c>
       <c r="M249" s="3">
-        <v>-6.3951700000000002</v>
+        <v>-6.4012000000000002</v>
       </c>
       <c r="N249" s="3">
-        <v>106.79304209999999</v>
+        <v>106.8082</v>
       </c>
       <c r="O249" t="s">
         <v>964</v>
@@ -17436,10 +17436,10 @@
         <v>14</v>
       </c>
       <c r="M250" s="3">
-        <v>-6.3790357000000002</v>
+        <v>-6.3912000000000004</v>
       </c>
       <c r="N250" s="3">
-        <v>106.84094690000001</v>
+        <v>106.8412</v>
       </c>
       <c r="O250" t="s">
         <v>965</v>
@@ -17492,10 +17492,10 @@
         <v>14</v>
       </c>
       <c r="M251" s="3">
-        <v>-6.3924833000000003</v>
+        <v>-6.3902000000000001</v>
       </c>
       <c r="N251" s="3">
-        <v>106.8230563</v>
+        <v>106.8222</v>
       </c>
       <c r="O251" t="s">
         <v>966</v>
@@ -17548,10 +17548,10 @@
         <v>14</v>
       </c>
       <c r="M252" s="3">
-        <v>-6.3506688999999996</v>
+        <v>-6.4024999999999999</v>
       </c>
       <c r="N252" s="3">
-        <v>106.81243689999999</v>
+        <v>106.8182</v>
       </c>
       <c r="O252" t="s">
         <v>967</v>
@@ -17604,10 +17604,10 @@
         <v>14</v>
       </c>
       <c r="M253" s="3">
-        <v>-6.2190810000000001</v>
+        <v>-6.1852</v>
       </c>
       <c r="N253" s="3">
-        <v>106.95247910000001</v>
+        <v>106.9552</v>
       </c>
       <c r="O253" t="s">
         <v>968</v>
@@ -17660,10 +17660,10 @@
         <v>14</v>
       </c>
       <c r="M254" s="3">
-        <v>-6.3125549999999997</v>
+        <v>-6.3151999999999999</v>
       </c>
       <c r="N254" s="3">
-        <v>106.8620153</v>
+        <v>106.8652</v>
       </c>
       <c r="O254" t="s">
         <v>969</v>
@@ -17716,10 +17716,10 @@
         <v>14</v>
       </c>
       <c r="M255" s="3">
-        <v>-6.1381080583333336</v>
+        <v>-6.1352000000000002</v>
       </c>
       <c r="N255" s="3">
-        <v>106.8341509166667</v>
+        <v>106.8352</v>
       </c>
       <c r="O255" t="s">
         <v>970</v>
@@ -17772,10 +17772,10 @@
         <v>14</v>
       </c>
       <c r="M256" s="3">
-        <v>-6.1226516000000002</v>
+        <v>-6.1151999999999997</v>
       </c>
       <c r="N256" s="3">
-        <v>106.915924</v>
+        <v>106.9152</v>
       </c>
       <c r="O256" t="s">
         <v>971</v>
@@ -17828,10 +17828,10 @@
         <v>14</v>
       </c>
       <c r="M257" s="3">
-        <v>-6.1208272690909089</v>
+        <v>-6.1151999999999997</v>
       </c>
       <c r="N257" s="3">
-        <v>106.78179958545461</v>
+        <v>106.7912</v>
       </c>
       <c r="O257" t="s">
         <v>972</v>
@@ -17884,10 +17884,10 @@
         <v>14</v>
       </c>
       <c r="M258" s="3">
-        <v>-6.128449008695652</v>
+        <v>-6.1382000000000003</v>
       </c>
       <c r="N258" s="3">
-        <v>106.8356417086956</v>
+        <v>106.8282</v>
       </c>
       <c r="O258" t="s">
         <v>973</v>
@@ -17940,10 +17940,10 @@
         <v>14</v>
       </c>
       <c r="M259" s="3">
-        <v>-6.128449008695652</v>
+        <v>-6.1391999999999998</v>
       </c>
       <c r="N259" s="3">
-        <v>106.8356417086956</v>
+        <v>106.8252</v>
       </c>
       <c r="O259" t="s">
         <v>974</v>
@@ -17996,10 +17996,10 @@
         <v>14</v>
       </c>
       <c r="M260" s="3">
-        <v>-6.1498730000000004</v>
+        <v>-6.1551999999999998</v>
       </c>
       <c r="N260" s="3">
-        <v>106.9029</v>
+        <v>106.8982</v>
       </c>
       <c r="O260" t="s">
         <v>975</v>
@@ -18052,10 +18052,10 @@
         <v>14</v>
       </c>
       <c r="M261" s="3">
-        <v>-6.1531060000000002</v>
+        <v>-6.1252000000000004</v>
       </c>
       <c r="N261" s="3">
-        <v>106.795376</v>
+        <v>106.7912</v>
       </c>
       <c r="O261" t="s">
         <v>976</v>
@@ -18108,10 +18108,10 @@
         <v>14</v>
       </c>
       <c r="M262" s="3">
-        <v>-6.1595677523809522</v>
+        <v>-6.1681999999999997</v>
       </c>
       <c r="N262" s="3">
-        <v>106.89754436071431</v>
+        <v>106.9012</v>
       </c>
       <c r="O262" t="s">
         <v>977</v>
@@ -18164,10 +18164,10 @@
         <v>14</v>
       </c>
       <c r="M263" s="3">
-        <v>-6.1159558000000001</v>
+        <v>-6.1252000000000004</v>
       </c>
       <c r="N263" s="3">
-        <v>106.7880296</v>
+        <v>106.7852</v>
       </c>
       <c r="O263" t="s">
         <v>978</v>
@@ -18220,10 +18220,10 @@
         <v>14</v>
       </c>
       <c r="M264" s="3">
-        <v>-6.2766849999999996</v>
+        <v>-6.2751999999999999</v>
       </c>
       <c r="N264" s="3">
-        <v>106.79687699999999</v>
+        <v>106.79519999999999</v>
       </c>
       <c r="O264" t="s">
         <v>979</v>
@@ -18276,10 +18276,10 @@
         <v>14</v>
       </c>
       <c r="M265" s="3">
-        <v>-6.25560838</v>
+        <v>-6.2851999999999997</v>
       </c>
       <c r="N265" s="3">
-        <v>106.66464338</v>
+        <v>106.65219999999999</v>
       </c>
       <c r="O265" t="s">
         <v>980</v>
@@ -18332,10 +18332,10 @@
         <v>14</v>
       </c>
       <c r="M266" s="3">
-        <v>-6.3484005999999997</v>
+        <v>-6.3452000000000002</v>
       </c>
       <c r="N266" s="3">
-        <v>106.6944503</v>
+        <v>106.68519999999999</v>
       </c>
       <c r="O266" t="s">
         <v>981</v>
@@ -18388,10 +18388,10 @@
         <v>14</v>
       </c>
       <c r="M267" s="3">
-        <v>-6.2956110000000001</v>
+        <v>-6.2952000000000004</v>
       </c>
       <c r="N267" s="3">
-        <v>106.629623</v>
+        <v>106.6382</v>
       </c>
       <c r="O267" t="s">
         <v>982</v>
@@ -18444,10 +18444,10 @@
         <v>14</v>
       </c>
       <c r="M268" s="3">
-        <v>-6.1530100000000001</v>
+        <v>-6.1551999999999998</v>
       </c>
       <c r="N268" s="3">
-        <v>106.79866</v>
+        <v>106.7912</v>
       </c>
       <c r="O268" t="s">
         <v>983</v>
@@ -18500,10 +18500,10 @@
         <v>14</v>
       </c>
       <c r="M269" s="3">
-        <v>-6.1798080000000004</v>
+        <v>-6.1782000000000004</v>
       </c>
       <c r="N269" s="3">
-        <v>106.79215000000001</v>
+        <v>106.79219999999999</v>
       </c>
       <c r="O269" t="s">
         <v>984</v>
@@ -18556,10 +18556,10 @@
         <v>14</v>
       </c>
       <c r="M270" s="3">
-        <v>-4.0119199999999999</v>
+        <v>-6.2552000000000003</v>
       </c>
       <c r="N270" s="3">
-        <v>131.42986999999999</v>
+        <v>106.62520000000001</v>
       </c>
       <c r="O270" t="s">
         <v>985</v>
@@ -18612,10 +18612,10 @@
         <v>14</v>
       </c>
       <c r="M271" s="3">
-        <v>-6.1499649999999999</v>
+        <v>0.78520000000000001</v>
       </c>
       <c r="N271" s="3">
-        <v>106.846473</v>
+        <v>127.3852</v>
       </c>
       <c r="O271" t="s">
         <v>986</v>
@@ -18668,10 +18668,10 @@
         <v>14</v>
       </c>
       <c r="M272" s="3">
-        <v>-5.1319109999999997</v>
+        <v>-5.1325000000000003</v>
       </c>
       <c r="N272" s="3">
-        <v>119.413161</v>
+        <v>119.41249999999999</v>
       </c>
       <c r="O272" t="s">
         <v>987</v>
@@ -18724,10 +18724,10 @@
         <v>14</v>
       </c>
       <c r="M273" s="3">
-        <v>-5.1399699999999999</v>
+        <v>-5.1382000000000003</v>
       </c>
       <c r="N273" s="3">
-        <v>119.4780336</v>
+        <v>119.48520000000001</v>
       </c>
       <c r="O273" t="s">
         <v>988</v>
@@ -18780,10 +18780,10 @@
         <v>14</v>
       </c>
       <c r="M274" s="3">
-        <v>-1.6033827</v>
+        <v>-1.6152</v>
       </c>
       <c r="N274" s="3">
-        <v>103.581906</v>
+        <v>103.6152</v>
       </c>
       <c r="O274" t="s">
         <v>989</v>
@@ -18836,10 +18836,10 @@
         <v>14</v>
       </c>
       <c r="M275" s="3">
-        <v>-6.1968439999999996</v>
+        <v>1.1452</v>
       </c>
       <c r="N275" s="3">
-        <v>106.59227300000001</v>
+        <v>104.01519999999999</v>
       </c>
       <c r="O275" t="s">
         <v>990</v>
@@ -18892,10 +18892,10 @@
         <v>14</v>
       </c>
       <c r="M276" s="3">
-        <v>1.1353826899999999</v>
+        <v>1.1452</v>
       </c>
       <c r="N276" s="3">
-        <v>104.0136742466667</v>
+        <v>104.01519999999999</v>
       </c>
       <c r="O276" t="s">
         <v>991</v>
@@ -18948,10 +18948,10 @@
         <v>14</v>
       </c>
       <c r="M277" s="3">
-        <v>1.110668</v>
+        <v>1.1352</v>
       </c>
       <c r="N277" s="3">
-        <v>104.078385</v>
+        <v>104.04819999999999</v>
       </c>
       <c r="O277" t="s">
         <v>992</v>
@@ -19004,10 +19004,10 @@
         <v>14</v>
       </c>
       <c r="M278" s="3">
-        <v>-6.3608039999999999</v>
+        <v>1.0551999999999999</v>
       </c>
       <c r="N278" s="3">
-        <v>106.906538</v>
+        <v>104.01819999999999</v>
       </c>
       <c r="O278" t="s">
         <v>993</v>
@@ -19060,10 +19060,10 @@
         <v>14</v>
       </c>
       <c r="M279" s="3">
-        <v>1.108115</v>
+        <v>1.1252</v>
       </c>
       <c r="N279" s="3">
-        <v>104.086229</v>
+        <v>104.0852</v>
       </c>
       <c r="O279" t="s">
         <v>994</v>
@@ -19116,10 +19116,10 @@
         <v>14</v>
       </c>
       <c r="M280" s="3">
-        <v>0.93102499999999999</v>
+        <v>3.5851999999999999</v>
       </c>
       <c r="N280" s="3">
-        <v>104.50969000000001</v>
+        <v>98.675200000000004</v>
       </c>
       <c r="O280" t="s">
         <v>995</v>
@@ -19172,10 +19172,10 @@
         <v>14</v>
       </c>
       <c r="M281" s="3">
-        <v>1.0518874</v>
+        <v>1.1252</v>
       </c>
       <c r="N281" s="3">
-        <v>103.96459249999999</v>
+        <v>104.0652</v>
       </c>
       <c r="O281" t="s">
         <v>996</v>
@@ -19228,10 +19228,10 @@
         <v>14</v>
       </c>
       <c r="M282" s="3">
-        <v>1.1573433</v>
+        <v>1.1252</v>
       </c>
       <c r="N282" s="3">
-        <v>104.1031232</v>
+        <v>104.0852</v>
       </c>
       <c r="O282" t="s">
         <v>997</v>
@@ -19284,10 +19284,10 @@
         <v>14</v>
       </c>
       <c r="M283" s="3">
-        <v>1.0666800000000001</v>
+        <v>-6.2214999999999998</v>
       </c>
       <c r="N283" s="3">
-        <v>103.988912</v>
+        <v>106.8015</v>
       </c>
       <c r="O283" t="s">
         <v>998</v>
@@ -19340,10 +19340,10 @@
         <v>14</v>
       </c>
       <c r="M284" s="3">
-        <v>1.0374855000000001</v>
+        <v>1.0351999999999999</v>
       </c>
       <c r="N284" s="3">
-        <v>104.00041280000001</v>
+        <v>103.98520000000001</v>
       </c>
       <c r="O284" t="s">
         <v>999</v>
@@ -19396,10 +19396,10 @@
         <v>14</v>
       </c>
       <c r="M285" s="3">
-        <v>-1.6170359999999999</v>
+        <v>-1.6152</v>
       </c>
       <c r="N285" s="3">
-        <v>103.576891</v>
+        <v>103.6152</v>
       </c>
       <c r="O285" t="s">
         <v>1000</v>
@@ -19452,10 +19452,10 @@
         <v>14</v>
       </c>
       <c r="M286" s="3">
-        <v>2.9886417000000001</v>
+        <v>2.9851999999999999</v>
       </c>
       <c r="N286" s="3">
-        <v>99.611108599999994</v>
+        <v>99.625200000000007</v>
       </c>
       <c r="O286" t="s">
         <v>1001</v>
@@ -19508,10 +19508,10 @@
         <v>14</v>
       </c>
       <c r="M287" s="3">
-        <v>3.5268989999999998</v>
+        <v>3.5152000000000001</v>
       </c>
       <c r="N287" s="3">
-        <v>98.796487999999997</v>
+        <v>98.785200000000003</v>
       </c>
       <c r="O287" t="s">
         <v>1002</v>
@@ -19543,6 +19543,7 @@
       <c r="N291" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
